--- a/research/traditional_assets/database/data/india/india_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/india/india_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ32"/>
+  <dimension ref="A1:AQ29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.114</v>
+        <v>0.156</v>
       </c>
       <c r="E2">
-        <v>0.13665</v>
+        <v>0.201</v>
       </c>
       <c r="F2">
-        <v>0.266</v>
+        <v>0.228</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,34 +603,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-0.0008681954876351158</v>
+        <v>0.0003525660625398181</v>
       </c>
       <c r="J2">
-        <v>-0.0007683995079504228</v>
+        <v>0.000297508451947853</v>
       </c>
       <c r="K2">
-        <v>18094.9</v>
+        <v>24404.76</v>
       </c>
       <c r="L2">
-        <v>0.1947289975087034</v>
+        <v>0.2680519172408339</v>
       </c>
       <c r="M2">
-        <v>1348.22</v>
+        <v>2355.161</v>
       </c>
       <c r="N2">
-        <v>0.003550885258750925</v>
+        <v>0.005642313741508659</v>
       </c>
       <c r="O2">
-        <v>0.07450828686535985</v>
+        <v>0.09650416558081293</v>
       </c>
       <c r="P2">
-        <v>1348.22</v>
+        <v>2355.161</v>
       </c>
       <c r="Q2">
-        <v>0.003550885258750925</v>
+        <v>0.005642313741508659</v>
       </c>
       <c r="R2">
-        <v>0.07450828686535985</v>
+        <v>0.09650416558081293</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>238246.9</v>
+        <v>126697.7</v>
       </c>
       <c r="V2">
-        <v>0.6274846873307811</v>
+        <v>0.3035326135782401</v>
       </c>
       <c r="W2">
-        <v>0.07020732173198066</v>
+        <v>0.1141267700606878</v>
       </c>
       <c r="X2">
-        <v>0.07562348221032408</v>
+        <v>0.1008590715102836</v>
       </c>
       <c r="Y2">
-        <v>-0.005416160478343424</v>
+        <v>0.01326769855040418</v>
       </c>
       <c r="Z2">
-        <v>0.4191844759980035</v>
+        <v>0.4077628177862778</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05446463549112089</v>
+        <v>0.08407293767764612</v>
       </c>
       <c r="AC2">
-        <v>-0.05404266734316083</v>
+        <v>-0.08401830274282189</v>
       </c>
       <c r="AD2">
-        <v>211611.8</v>
+        <v>217754.5</v>
       </c>
       <c r="AE2">
-        <v>3309.203816976308</v>
+        <v>2760.643290463343</v>
       </c>
       <c r="AF2">
-        <v>214921.0038169763</v>
+        <v>220515.1432904633</v>
       </c>
       <c r="AG2">
-        <v>-23325.89618302369</v>
+        <v>93817.44329046334</v>
       </c>
       <c r="AH2">
-        <v>0.3614507515344218</v>
+        <v>0.3456753081017898</v>
       </c>
       <c r="AI2">
-        <v>0.4948268181628916</v>
+        <v>0.5223367642029446</v>
       </c>
       <c r="AJ2">
-        <v>-0.06545604324276716</v>
+        <v>0.1835139188335785</v>
       </c>
       <c r="AK2">
-        <v>-0.1189557171720202</v>
+        <v>0.3175164052212981</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>364.1165589806681</v>
+        <v>372.7217798530711</v>
       </c>
       <c r="AP2">
-        <v>-40.13644349371297</v>
+        <v>160.5836134017256</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Suryoday Small Finance Bank Limited (BSE:543279)</t>
+          <t>Equitas Small Finance Bank Limited (NSEI:EQUITASBNK)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -718,6 +718,12 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.229</v>
+      </c>
+      <c r="E3">
+        <v>0.412</v>
+      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -725,16 +731,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.01519783786529482</v>
+        <v>0.00908403900894305</v>
       </c>
       <c r="J3">
-        <v>0.01519783786529482</v>
+        <v>0.008201373218574084</v>
       </c>
       <c r="K3">
-        <v>-12.4</v>
+        <v>54.2</v>
       </c>
       <c r="L3">
-        <v>-0.3657817109144543</v>
+        <v>0.1550786838340487</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +749,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,55 +758,61 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>18.7</v>
+        <v>155.4</v>
       </c>
       <c r="V3">
-        <v>0.09038182696955051</v>
+        <v>0.1757322175732218</v>
+      </c>
+      <c r="W3">
+        <v>0.115985448320137</v>
       </c>
       <c r="X3">
-        <v>0.08015548019999212</v>
+        <v>0.09261182846420479</v>
+      </c>
+      <c r="Y3">
+        <v>0.02337361985593217</v>
       </c>
       <c r="Z3">
-        <v>31.56523092057382</v>
+        <v>0.7800892792005749</v>
       </c>
       <c r="AA3">
-        <v>0.4797232617114717</v>
+        <v>0.006397803322532357</v>
       </c>
       <c r="AB3">
-        <v>0.05623080902321147</v>
+        <v>0.08331257399036757</v>
       </c>
       <c r="AC3">
-        <v>0.4234924526882602</v>
+        <v>-0.07691477066783521</v>
       </c>
       <c r="AD3">
-        <v>230.1</v>
+        <v>287.5</v>
       </c>
       <c r="AE3">
-        <v>1.073966481832528</v>
+        <v>28.92564183187202</v>
       </c>
       <c r="AF3">
-        <v>231.1739664818325</v>
+        <v>316.425641831872</v>
       </c>
       <c r="AG3">
-        <v>212.4739664818325</v>
+        <v>161.025641831872</v>
       </c>
       <c r="AH3">
-        <v>0.527705328710556</v>
+        <v>0.2635286786656119</v>
       </c>
       <c r="AI3">
-        <v>0.5254264663211117</v>
+        <v>0.3656723278903502</v>
       </c>
       <c r="AJ3">
-        <v>0.5066455799922358</v>
+        <v>0.1540435203997139</v>
       </c>
       <c r="AK3">
-        <v>0.5043605429888236</v>
+        <v>0.2268204334983112</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -809,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>315.2054794520548</v>
+        <v>32.08705357142857</v>
       </c>
       <c r="AP3">
-        <v>291.0602280573048</v>
+        <v>17.97161181159286</v>
       </c>
     </row>
     <row r="4">
@@ -823,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bank of Baroda (BSE:532134)</t>
+          <t>IndusInd Bank Limited (NSEI:INDUSINDBK)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -831,11 +843,8 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.525</v>
-      </c>
       <c r="F4">
-        <v>1.528</v>
+        <v>0.189</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -844,88 +853,91 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.001808068129772391</v>
+        <v>0.007424675500465108</v>
       </c>
       <c r="J4">
-        <v>0.001500281393508682</v>
+        <v>0.006910332169010013</v>
       </c>
       <c r="K4">
-        <v>513.6</v>
+        <v>747</v>
       </c>
       <c r="L4">
-        <v>0.1303520215222964</v>
+        <v>0.3619887575111456</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>81</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.007085684293399817</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.108433734939759</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>81</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.007085684293399817</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.108433734939759</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>20295.6</v>
+        <v>7278</v>
       </c>
       <c r="V4">
-        <v>3.568331663062398</v>
+        <v>0.6366618553995539</v>
       </c>
       <c r="W4">
-        <v>0.04867600507989461</v>
+        <v>0.1222405864929879</v>
       </c>
       <c r="X4">
-        <v>0.1120095269406496</v>
+        <v>0.09547934727126572</v>
       </c>
       <c r="Y4">
-        <v>-0.06333352186075497</v>
+        <v>0.02676123922172222</v>
       </c>
       <c r="Z4">
-        <v>8.896537733988213</v>
+        <v>0.5925811575947199</v>
       </c>
       <c r="AA4">
-        <v>0.01334731002895041</v>
+        <v>0.004094932636075984</v>
       </c>
       <c r="AB4">
-        <v>0.05626650528321881</v>
+        <v>0.08358346881475663</v>
       </c>
       <c r="AC4">
-        <v>-0.04291919525426841</v>
+        <v>-0.07948853617868065</v>
       </c>
       <c r="AD4">
-        <v>13370.3</v>
+        <v>4998.3</v>
       </c>
       <c r="AE4">
-        <v>74.88015380941903</v>
+        <v>180.392198186201</v>
       </c>
       <c r="AF4">
-        <v>13445.18015380942</v>
+        <v>5178.692198186201</v>
       </c>
       <c r="AG4">
-        <v>-6850.41984619058</v>
+        <v>-2099.307801813799</v>
       </c>
       <c r="AH4">
-        <v>0.7027264084509743</v>
+        <v>0.3117779816389905</v>
       </c>
       <c r="AI4">
-        <v>0.5355390877132553</v>
+        <v>0.4530079018588062</v>
       </c>
       <c r="AJ4">
-        <v>5.891720063637527</v>
+        <v>-0.2249533397117366</v>
       </c>
       <c r="AK4">
-        <v>-1.42412076368681</v>
+        <v>-0.5053954799978881</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -934,10 +946,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>604.9909502262443</v>
+        <v>97.24319066147861</v>
       </c>
       <c r="AP4">
-        <v>-309.9737486964063</v>
+        <v>-40.84256423762254</v>
       </c>
     </row>
     <row r="5">
@@ -948,7 +960,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Indian Overseas Bank (BSE:532388)</t>
+          <t>RBL Bank Limited (NSEI:RBLBANK)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -956,6 +968,9 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="F5">
+        <v>0.3</v>
+      </c>
       <c r="G5">
         <v>0</v>
       </c>
@@ -963,16 +978,16 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.009050130287362531</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>0.006596923815027944</v>
       </c>
       <c r="K5">
-        <v>170.6</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="L5">
-        <v>0.1800527704485488</v>
+        <v>0.1231650029359953</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -996,61 +1011,67 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1497.4</v>
+        <v>642.5</v>
       </c>
       <c r="V5">
-        <v>0.2893358839101115</v>
+        <v>0.4943828870421669</v>
       </c>
       <c r="W5">
-        <v>0.07644396648295022</v>
+        <v>0.05087623552240617</v>
       </c>
       <c r="X5">
-        <v>0.0539141993251985</v>
+        <v>0.1146998849830565</v>
       </c>
       <c r="Y5">
-        <v>0.02252976715775173</v>
+        <v>-0.06382364946065033</v>
       </c>
       <c r="Z5">
-        <v>0.5202613661322205</v>
+        <v>0.6937603534288134</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>0.004576684197456743</v>
       </c>
       <c r="AB5">
-        <v>0.05215439690976915</v>
+        <v>0.08476251888702729</v>
       </c>
       <c r="AC5">
-        <v>-0.05215439690976915</v>
+        <v>-0.08018583468957055</v>
       </c>
       <c r="AD5">
-        <v>467.8</v>
+        <v>1324.8</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>93.17525624124322</v>
       </c>
       <c r="AF5">
-        <v>467.8</v>
+        <v>1417.975256241243</v>
       </c>
       <c r="AG5">
-        <v>-1029.6</v>
+        <v>775.4752562412432</v>
       </c>
       <c r="AH5">
-        <v>0.08289769807375379</v>
+        <v>0.5217795727955242</v>
       </c>
       <c r="AI5">
-        <v>0.1386649276737017</v>
+        <v>0.4706854221495649</v>
       </c>
       <c r="AJ5">
-        <v>-0.2483537158984008</v>
+        <v>0.373709461335839</v>
       </c>
       <c r="AK5">
-        <v>-0.5487687879756956</v>
+        <v>0.3271943598411669</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>53.41935483870967</v>
+      </c>
+      <c r="AP5">
+        <v>31.26916355811464</v>
       </c>
     </row>
     <row r="6">
@@ -1061,7 +1082,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>City Union Bank Limited (BSE:532210)</t>
+          <t>The Federal Bank Limited (NSEI:FEDERALBNK)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1069,11 +1090,8 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.08039999999999999</v>
-      </c>
-      <c r="E6">
-        <v>0.0613</v>
+      <c r="F6">
+        <v>0.228</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1082,34 +1100,34 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>0.0003669552211611642</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>0.000274203457387111</v>
       </c>
       <c r="K6">
-        <v>85.8</v>
+        <v>306.6</v>
       </c>
       <c r="L6">
-        <v>0.3455497382198953</v>
+        <v>0.3018905080740449</v>
       </c>
       <c r="M6">
-        <v>0.31</v>
+        <v>46.5</v>
       </c>
       <c r="N6">
-        <v>0.0002306376013689458</v>
+        <v>0.01309564041906049</v>
       </c>
       <c r="O6">
-        <v>0.003613053613053613</v>
+        <v>0.1516634050880626</v>
       </c>
       <c r="P6">
-        <v>0.31</v>
+        <v>46.5</v>
       </c>
       <c r="Q6">
-        <v>0.0002306376013689458</v>
+        <v>0.01309564041906049</v>
       </c>
       <c r="R6">
-        <v>0.003613053613053613</v>
+        <v>0.1516634050880626</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1118,61 +1136,67 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>836.2</v>
+        <v>1856.5</v>
       </c>
       <c r="V6">
-        <v>0.6221263298861692</v>
+        <v>0.5228399233975441</v>
       </c>
       <c r="W6">
-        <v>0.1132374290616339</v>
+        <v>0.1255014326647565</v>
       </c>
       <c r="X6">
-        <v>0.05688577353531539</v>
+        <v>0.1084238894760745</v>
       </c>
       <c r="Y6">
-        <v>0.05635165552631849</v>
+        <v>0.01707754318868202</v>
       </c>
       <c r="Z6">
-        <v>0.4235755714773115</v>
+        <v>0.7556341835869487</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>0.0002071975056594283</v>
       </c>
       <c r="AB6">
-        <v>0.05218709209755538</v>
+        <v>0.0819382474033669</v>
       </c>
       <c r="AC6">
-        <v>-0.05218709209755538</v>
+        <v>-0.08173104989770748</v>
       </c>
       <c r="AD6">
-        <v>277.8</v>
+        <v>3133.4</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.036601386943608</v>
       </c>
       <c r="AF6">
-        <v>277.8</v>
+        <v>3134.436601386943</v>
       </c>
       <c r="AG6">
-        <v>-558.4000000000001</v>
+        <v>1277.936601386943</v>
       </c>
       <c r="AH6">
-        <v>0.1712805968308774</v>
+        <v>0.4688594866988944</v>
       </c>
       <c r="AI6">
-        <v>0.2503604902667628</v>
+        <v>0.5531680911119418</v>
       </c>
       <c r="AJ6">
-        <v>-0.7107038309787453</v>
+        <v>0.2646523732563681</v>
       </c>
       <c r="AK6">
-        <v>-2.042428675932701</v>
+        <v>0.3354308163561975</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
         <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>5402.413793103448</v>
+      </c>
+      <c r="AP6">
+        <v>2203.338967908524</v>
       </c>
     </row>
     <row r="7">
@@ -1183,7 +1207,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Equitas Small Finance Bank Limited (BSE:543243)</t>
+          <t>City Union Bank Limited (NSEI:CUB)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1192,10 +1216,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.41</v>
+        <v>0.0931</v>
       </c>
       <c r="E7">
-        <v>0.218</v>
+        <v>0.109</v>
+      </c>
+      <c r="F7">
+        <v>0.21</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1204,100 +1231,97 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0.004642725894587862</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>0.004642725894587862</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>37.3</v>
+        <v>111.4</v>
       </c>
       <c r="L7">
-        <v>0.1124510099487489</v>
+        <v>0.3965824136703454</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>8.4</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.005206719147089816</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0.07540394973070018</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>8.4</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.005206719147089816</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0.07540394973070018</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>470.2</v>
+        <v>670.2</v>
       </c>
       <c r="V7">
-        <v>0.512535426204491</v>
+        <v>0.415421806235666</v>
       </c>
       <c r="W7">
-        <v>0.09440647937231079</v>
+        <v>0.1339264246213032</v>
       </c>
       <c r="X7">
-        <v>0.06437262753605111</v>
+        <v>0.09421982108182313</v>
       </c>
       <c r="Y7">
-        <v>0.03003385183625969</v>
+        <v>0.03970660353948009</v>
       </c>
       <c r="Z7">
-        <v>0.3275402263176893</v>
+        <v>1.027432333577177</v>
       </c>
       <c r="AA7">
-        <v>0.001520679490244305</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.05381488916578751</v>
+        <v>0.08189840801607781</v>
       </c>
       <c r="AC7">
-        <v>-0.05229420967554321</v>
+        <v>-0.08189840801607781</v>
       </c>
       <c r="AD7">
-        <v>422</v>
+        <v>663.4</v>
       </c>
       <c r="AE7">
-        <v>36.40003910382603</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>458.400039103826</v>
+        <v>663.4</v>
       </c>
       <c r="AG7">
-        <v>-11.79996089617396</v>
+        <v>-6.800000000000068</v>
       </c>
       <c r="AH7">
-        <v>0.333187982319306</v>
+        <v>0.2913866561250933</v>
       </c>
       <c r="AI7">
-        <v>0.4951928483740856</v>
+        <v>0.4349308332786992</v>
       </c>
       <c r="AJ7">
-        <v>-0.01302999159303383</v>
+        <v>-0.004232804232804276</v>
       </c>
       <c r="AK7">
-        <v>-0.02590551017161228</v>
+        <v>-0.007952286282306244</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
         <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>47.84580498866213</v>
-      </c>
-      <c r="AP7">
-        <v>-1.337864047185256</v>
       </c>
     </row>
     <row r="8">
@@ -1317,13 +1341,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.185</v>
+        <v>0.162</v>
       </c>
       <c r="E8">
-        <v>0.185</v>
+        <v>0.201</v>
       </c>
       <c r="F8">
-        <v>0.207</v>
+        <v>0.17</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1332,34 +1356,34 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.00096982488160491</v>
+        <v>0.003031515965542103</v>
       </c>
       <c r="J8">
-        <v>0.000723245575862566</v>
+        <v>0.002287401724764371</v>
       </c>
       <c r="K8">
-        <v>1346.3</v>
+        <v>1678.4</v>
       </c>
       <c r="L8">
-        <v>0.2265926112934444</v>
+        <v>0.2816958141720654</v>
       </c>
       <c r="M8">
-        <v>24.1</v>
+        <v>4.91</v>
       </c>
       <c r="N8">
-        <v>0.0005039669096581808</v>
+        <v>0.000112021427805498</v>
       </c>
       <c r="O8">
-        <v>0.01790091361509322</v>
+        <v>0.002925405147759771</v>
       </c>
       <c r="P8">
-        <v>24.1</v>
+        <v>4.91</v>
       </c>
       <c r="Q8">
-        <v>0.0005039669096581808</v>
+        <v>0.000112021427805498</v>
       </c>
       <c r="R8">
-        <v>0.01790091361509322</v>
+        <v>0.002925405147759771</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1368,55 +1392,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>5878.4</v>
+        <v>5061.4</v>
       </c>
       <c r="V8">
-        <v>0.1229261029765415</v>
+        <v>0.1154756119541237</v>
       </c>
       <c r="W8">
-        <v>0.1246851152107876</v>
+        <v>0.1388748686464168</v>
       </c>
       <c r="X8">
-        <v>0.05592029149512806</v>
+        <v>0.08599955389115931</v>
       </c>
       <c r="Y8">
-        <v>0.06876482371565951</v>
+        <v>0.05287531475525754</v>
       </c>
       <c r="Z8">
-        <v>0.4177303878418405</v>
+        <v>0.4223011731644723</v>
       </c>
       <c r="AA8">
-        <v>0.000302121654909965</v>
+        <v>0.0009659724318664311</v>
       </c>
       <c r="AB8">
-        <v>0.05303195301436657</v>
+        <v>0.08301705496130242</v>
       </c>
       <c r="AC8">
-        <v>-0.05272983135945661</v>
+        <v>-0.08205108252943599</v>
       </c>
       <c r="AD8">
-        <v>7734.1</v>
+        <v>5785.4</v>
       </c>
       <c r="AE8">
-        <v>342.6889273297221</v>
+        <v>277.1881078705352</v>
       </c>
       <c r="AF8">
-        <v>8076.788927329722</v>
+        <v>6062.588107870535</v>
       </c>
       <c r="AG8">
-        <v>2198.388927329723</v>
+        <v>1001.188107870536</v>
       </c>
       <c r="AH8">
-        <v>0.1444931343363834</v>
+        <v>0.121510608654242</v>
       </c>
       <c r="AI8">
-        <v>0.4005849157036286</v>
+        <v>0.3225263306979452</v>
       </c>
       <c r="AJ8">
-        <v>0.04395108686670297</v>
+        <v>0.0223319535209151</v>
       </c>
       <c r="AK8">
-        <v>0.1539047354377323</v>
+        <v>0.07288901808967627</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1425,10 +1449,10 @@
         <v>0</v>
       </c>
       <c r="AN8">
-        <v>104.092866756393</v>
+        <v>78.71292517006802</v>
       </c>
       <c r="AP8">
-        <v>29.58800709730448</v>
+        <v>13.62160690980321</v>
       </c>
     </row>
     <row r="9">
@@ -1439,7 +1463,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IDBI Bank Limited (BSE:500116)</t>
+          <t>Tamilnad Mercantile Bank Limited (NSEI:TMB)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1454,34 +1478,34 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>5.628682840759142e-05</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>5.628682840759142e-05</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>297.8</v>
+        <v>113.8</v>
       </c>
       <c r="L9">
-        <v>0.2691125971444063</v>
+        <v>0.389592605272167</v>
       </c>
       <c r="M9">
-        <v>2.03</v>
+        <v>17.5</v>
       </c>
       <c r="N9">
-        <v>0.0003031705969324512</v>
+        <v>0.01911106257507917</v>
       </c>
       <c r="O9">
-        <v>0.006816655473472128</v>
+        <v>0.1537785588752197</v>
       </c>
       <c r="P9">
-        <v>2.03</v>
+        <v>17.5</v>
       </c>
       <c r="Q9">
-        <v>0.0003031705969324512</v>
+        <v>0.01911106257507917</v>
       </c>
       <c r="R9">
-        <v>0.006816655473472128</v>
+        <v>0.1537785588752197</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1490,67 +1514,61 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>4457.6</v>
+        <v>370.5</v>
       </c>
       <c r="V9">
-        <v>0.6657208142296033</v>
+        <v>0.4046084962323905</v>
       </c>
       <c r="W9">
-        <v>0.06193070748242731</v>
+        <v>0.1817891373801917</v>
       </c>
       <c r="X9">
-        <v>0.05952072054558347</v>
+        <v>0.08296133851278328</v>
       </c>
       <c r="Y9">
-        <v>0.002409986936843841</v>
+        <v>0.09882779886740842</v>
       </c>
       <c r="Z9">
-        <v>0.2331660690581684</v>
+        <v>0.6485346358792186</v>
       </c>
       <c r="AA9">
-        <v>1.312417851954973e-05</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.05317358961282269</v>
+        <v>0.08213174940561048</v>
       </c>
       <c r="AC9">
-        <v>-0.05316046543430314</v>
+        <v>-0.08213174940561048</v>
       </c>
       <c r="AD9">
-        <v>2074.3</v>
+        <v>34.3</v>
       </c>
       <c r="AE9">
-        <v>0.07356497842079672</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>2074.373564978421</v>
+        <v>34.3</v>
       </c>
       <c r="AG9">
-        <v>-2383.226435021579</v>
+        <v>-336.2</v>
       </c>
       <c r="AH9">
-        <v>0.2365232452111686</v>
+        <v>0.03610526315789473</v>
       </c>
       <c r="AI9">
-        <v>0.2832074176845997</v>
+        <v>0.04141011710732826</v>
       </c>
       <c r="AJ9">
-        <v>-0.5526099759496877</v>
+        <v>-0.5801553062985332</v>
       </c>
       <c r="AK9">
-        <v>-0.831269065098449</v>
+        <v>-0.7343818261249454</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
         <v>0</v>
-      </c>
-      <c r="AN9">
-        <v>26938.96103896104</v>
-      </c>
-      <c r="AP9">
-        <v>-30950.99266261791</v>
       </c>
     </row>
     <row r="10">
@@ -1561,7 +1579,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Karur Vysya Bank Limited (NSEI:KARURVYSYA)</t>
+          <t>Indian Overseas Bank (NSEI:IOB)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1570,10 +1588,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0255</v>
-      </c>
-      <c r="E10">
-        <v>-0.0601</v>
+        <v>0.325</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1588,85 +1603,82 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>55.7</v>
+        <v>233</v>
       </c>
       <c r="L10">
-        <v>0.1550668151447662</v>
+        <v>0.2490114352890884</v>
       </c>
       <c r="M10">
-        <v>5.44</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.0111338518215309</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>0.09766606822262118</v>
+        <v>-0</v>
       </c>
       <c r="P10">
-        <v>5.44</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.0111338518215309</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.09766606822262118</v>
+        <v>-0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>829</v>
+        <v>1948.3</v>
       </c>
       <c r="V10">
-        <v>1.696684404420794</v>
+        <v>0.2657400840198592</v>
       </c>
       <c r="W10">
-        <v>0.06004743423889608</v>
+        <v>0.08018445866886915</v>
       </c>
       <c r="X10">
-        <v>0.05976824496942528</v>
+        <v>0.08757978864303957</v>
       </c>
       <c r="Y10">
-        <v>0.000279189269470799</v>
+        <v>-0.007395329974170417</v>
       </c>
       <c r="Z10">
-        <v>0.4883088635127787</v>
+        <v>0.4987208186760473</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.05321077385223168</v>
+        <v>0.08273250515421895</v>
       </c>
       <c r="AC10">
-        <v>-0.05321077385223168</v>
+        <v>-0.08273250515421895</v>
       </c>
       <c r="AD10">
-        <v>156.1</v>
+        <v>1398.7</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>156.1</v>
+        <v>1398.7</v>
       </c>
       <c r="AG10">
-        <v>-672.9</v>
+        <v>-549.5999999999999</v>
       </c>
       <c r="AH10">
-        <v>0.2421281216069489</v>
+        <v>0.1602121347490922</v>
       </c>
       <c r="AI10">
-        <v>0.1386323268206039</v>
+        <v>0.32254865787289</v>
       </c>
       <c r="AJ10">
-        <v>3.651112316874662</v>
+        <v>-0.08103804187555293</v>
       </c>
       <c r="AK10">
-        <v>-2.265656565656565</v>
+        <v>-0.2301411163686612</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1683,7 +1695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Central Bank of India (BSE:532885)</t>
+          <t>The Karur Vysya Bank Limited (NSEI:KARURVYSYA)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1691,6 +1703,12 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D11">
+        <v>0.0806</v>
+      </c>
+      <c r="E11">
+        <v>0.0953</v>
+      </c>
       <c r="G11">
         <v>0</v>
       </c>
@@ -1704,82 +1722,85 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>-111.2</v>
+        <v>107.9</v>
       </c>
       <c r="L11">
-        <v>-0.1265361857077834</v>
+        <v>0.2798236514522822</v>
       </c>
       <c r="M11">
-        <v>-0</v>
+        <v>15.7</v>
       </c>
       <c r="N11">
-        <v>-0</v>
+        <v>0.01432743201314108</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>0.1455050973123262</v>
       </c>
       <c r="P11">
-        <v>-0</v>
+        <v>15.7</v>
       </c>
       <c r="Q11">
-        <v>-0</v>
+        <v>0.01432743201314108</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>0.1455050973123262</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
       <c r="U11">
-        <v>7294.1</v>
+        <v>730.1</v>
       </c>
       <c r="V11">
-        <v>2.946158817351967</v>
+        <v>0.6662712173754335</v>
       </c>
       <c r="W11">
-        <v>-0.03705184592829535</v>
+        <v>0.1112485823280751</v>
       </c>
       <c r="X11">
-        <v>0.06024736219562802</v>
+        <v>0.0895383304834198</v>
       </c>
       <c r="Y11">
-        <v>-0.09729920812392337</v>
+        <v>0.02171025184465526</v>
       </c>
       <c r="Z11">
-        <v>-0.7277786519366297</v>
+        <v>1.298316498316498</v>
       </c>
       <c r="AA11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.05328121958924561</v>
+        <v>0.08297661976851696</v>
       </c>
       <c r="AC11">
-        <v>-0.05328121958924561</v>
+        <v>-0.08297661976851696</v>
       </c>
       <c r="AD11">
-        <v>837.4</v>
+        <v>280.3</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>837.4</v>
+        <v>280.3</v>
       </c>
       <c r="AG11">
-        <v>-6456.700000000001</v>
+        <v>-449.8</v>
       </c>
       <c r="AH11">
-        <v>0.2527465893999759</v>
+        <v>0.2036915921808008</v>
       </c>
       <c r="AI11">
-        <v>0.187015655358778</v>
+        <v>0.2229735104605839</v>
       </c>
       <c r="AJ11">
-        <v>1.621919666407094</v>
+        <v>-0.6962848297213623</v>
       </c>
       <c r="AK11">
-        <v>2.292536571509729</v>
+        <v>-0.8535104364326376</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1796,7 +1817,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UCO Bank (BSE:532505)</t>
+          <t>IDBI Bank Limited (NSEI:IDBI)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1811,94 +1832,103 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>7.534943412478363e-05</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>6.806736668350376e-05</v>
       </c>
       <c r="K12">
-        <v>57</v>
+        <v>355.3</v>
       </c>
       <c r="L12">
-        <v>0.09174311926605505</v>
+        <v>0.2879954608089487</v>
       </c>
       <c r="M12">
-        <v>-0</v>
+        <v>1.43</v>
       </c>
       <c r="N12">
-        <v>-0</v>
+        <v>0.0002025151532317453</v>
       </c>
       <c r="O12">
-        <v>-0</v>
+        <v>0.004024767801857585</v>
       </c>
       <c r="P12">
-        <v>-0</v>
+        <v>1.43</v>
       </c>
       <c r="Q12">
-        <v>-0</v>
+        <v>0.0002025151532317453</v>
       </c>
       <c r="R12">
-        <v>-0</v>
+        <v>0.004024767801857585</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
       <c r="U12">
-        <v>3466.4</v>
+        <v>1596.3</v>
       </c>
       <c r="V12">
-        <v>1.661744966442953</v>
+        <v>0.2260663909817028</v>
       </c>
       <c r="W12">
-        <v>0.02169775409212029</v>
+        <v>0.06787788476234144</v>
       </c>
       <c r="X12">
-        <v>0.07785332280374471</v>
+        <v>0.09320522251068189</v>
       </c>
       <c r="Y12">
-        <v>-0.05615556871162442</v>
+        <v>-0.02532733774834045</v>
       </c>
       <c r="Z12">
-        <v>0.1918243848220075</v>
+        <v>0.4326828338247746</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.945158110760845e-05</v>
       </c>
       <c r="AB12">
-        <v>0.05332817224937365</v>
+        <v>0.08337170421581624</v>
       </c>
       <c r="AC12">
-        <v>-0.05332817224937365</v>
+        <v>-0.08334225263470864</v>
       </c>
       <c r="AD12">
-        <v>2142.8</v>
+        <v>2665.6</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>0.1802070156012722</v>
       </c>
       <c r="AF12">
-        <v>2142.8</v>
+        <v>2665.780207015601</v>
       </c>
       <c r="AG12">
-        <v>-1323.6</v>
+        <v>1069.480207015601</v>
       </c>
       <c r="AH12">
-        <v>0.5067158531971245</v>
+        <v>0.2740604124076353</v>
       </c>
       <c r="AI12">
-        <v>0.4092749637099855</v>
+        <v>0.3287969109473377</v>
       </c>
       <c r="AJ12">
-        <v>-1.736096537250787</v>
+        <v>0.1315363757749068</v>
       </c>
       <c r="AK12">
-        <v>-0.748134750169568</v>
+        <v>0.1642478511488707</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
         <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>20663.56589147287</v>
+      </c>
+      <c r="AP12">
+        <v>8290.544240431018</v>
       </c>
     </row>
     <row r="13">
@@ -1909,7 +1939,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ICICI Bank Limited (NSEI:ICICIBANK)</t>
+          <t>Punjab &amp; Sind Bank (BSE:533295)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1918,13 +1948,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.112</v>
+        <v>0.151</v>
       </c>
       <c r="E13">
-        <v>0.187</v>
-      </c>
-      <c r="F13">
-        <v>0.211</v>
+        <v>0.5529999999999999</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1933,34 +1960,34 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0.0002892882942524916</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>0.0002743894792828269</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>2863.4</v>
+        <v>138.8</v>
       </c>
       <c r="L13">
-        <v>0.209436874172573</v>
+        <v>0.3279773156899811</v>
       </c>
       <c r="M13">
-        <v>186.8</v>
+        <v>25.8</v>
       </c>
       <c r="N13">
-        <v>0.002708423952443092</v>
+        <v>0.009292943846126139</v>
       </c>
       <c r="O13">
-        <v>0.06523713068380248</v>
+        <v>0.185878962536023</v>
       </c>
       <c r="P13">
-        <v>186.8</v>
+        <v>25.8</v>
       </c>
       <c r="Q13">
-        <v>0.002708423952443092</v>
+        <v>0.009292943846126139</v>
       </c>
       <c r="R13">
-        <v>0.06523713068380248</v>
+        <v>0.185878962536023</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -1969,67 +1996,61 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>22050.9</v>
+        <v>679.6</v>
       </c>
       <c r="V13">
-        <v>0.3197172683775555</v>
+        <v>0.2447862262723769</v>
       </c>
       <c r="W13">
-        <v>0.1441814327507465</v>
+        <v>0.1175872585564215</v>
       </c>
       <c r="X13">
-        <v>0.0580093143288954</v>
+        <v>0.09301618226403355</v>
       </c>
       <c r="Y13">
-        <v>0.0861721184218511</v>
+        <v>0.024571076292388</v>
       </c>
       <c r="Z13">
-        <v>0.5342626070009545</v>
+        <v>1.913200723327305</v>
       </c>
       <c r="AA13">
-        <v>0.0001465960385352775</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.05358444086736851</v>
+        <v>0.0833530512324963</v>
       </c>
       <c r="AC13">
-        <v>-0.05343784482883323</v>
+        <v>-0.0833530512324963</v>
       </c>
       <c r="AD13">
-        <v>17259.5</v>
+        <v>1030.7</v>
       </c>
       <c r="AE13">
-        <v>27.8243968490468</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>17287.32439684905</v>
+        <v>1030.7</v>
       </c>
       <c r="AG13">
-        <v>-4763.575603150955</v>
+        <v>351.1</v>
       </c>
       <c r="AH13">
-        <v>0.2004157272177173</v>
+        <v>0.2707381140005254</v>
       </c>
       <c r="AI13">
-        <v>0.4239570251601674</v>
+        <v>0.369956927494616</v>
       </c>
       <c r="AJ13">
-        <v>-0.07419157269540662</v>
+        <v>0.1122657798810514</v>
       </c>
       <c r="AK13">
-        <v>-0.2543935123123298</v>
+        <v>0.1666824914546145</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
         <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>1812.97268907563</v>
-      </c>
-      <c r="AP13">
-        <v>-500.3755885662769</v>
       </c>
     </row>
     <row r="14">
@@ -2040,7 +2061,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Punjab &amp; Sind Bank (BSE:533295)</t>
+          <t>UCO Bank (NSEI:UCOBANK)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2048,9 +2069,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D14">
-        <v>-0.331</v>
-      </c>
       <c r="G14">
         <v>0</v>
       </c>
@@ -2064,10 +2082,10 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>-245.7</v>
+        <v>154.3</v>
       </c>
       <c r="L14">
-        <v>-7.205278592375365</v>
+        <v>0.1967861242188496</v>
       </c>
       <c r="M14">
         <v>-0</v>
@@ -2076,7 +2094,7 @@
         <v>-0</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P14">
         <v>-0</v>
@@ -2085,61 +2103,61 @@
         <v>-0</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
       <c r="U14">
-        <v>1313.8</v>
+        <v>3650</v>
       </c>
       <c r="V14">
-        <v>1.500285485896997</v>
+        <v>0.8020920318199797</v>
       </c>
       <c r="W14">
-        <v>-0.3557775847089487</v>
+        <v>0.04989006725297465</v>
       </c>
       <c r="X14">
-        <v>0.06195173085537251</v>
+        <v>0.09775641642416028</v>
       </c>
       <c r="Y14">
-        <v>-0.4177293155643212</v>
+        <v>-0.04786634917118562</v>
       </c>
       <c r="Z14">
-        <v>0.1201973916108565</v>
+        <v>0.4431946642550305</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.05351657544290633</v>
+        <v>0.08377454988215931</v>
       </c>
       <c r="AC14">
-        <v>-0.05351657544290633</v>
+        <v>-0.08377454988215931</v>
       </c>
       <c r="AD14">
-        <v>354.6</v>
+        <v>2405.5</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>354.6</v>
+        <v>2405.5</v>
       </c>
       <c r="AG14">
-        <v>-959.1999999999999</v>
+        <v>-1244.5</v>
       </c>
       <c r="AH14">
-        <v>0.2882223847841989</v>
+        <v>0.3458115898276333</v>
       </c>
       <c r="AI14">
-        <v>0.2310097719869707</v>
+        <v>0.4469029836881804</v>
       </c>
       <c r="AJ14">
-        <v>11.48742514970061</v>
+        <v>-0.3764253954810804</v>
       </c>
       <c r="AK14">
-        <v>-4.336347197106687</v>
+        <v>-0.7182846588941476</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2156,7 +2174,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Karnataka Bank Limited (NSEI:KTKBANK)</t>
+          <t>ICICI Bank Limited (NSEI:ICICIBANK)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2165,10 +2183,13 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.0563</v>
+        <v>0.106</v>
       </c>
       <c r="E15">
-        <v>-0.0238</v>
+        <v>0.259</v>
+      </c>
+      <c r="F15">
+        <v>0.192</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2177,34 +2198,34 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>0.0002677723818507505</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>0.0002546118737911289</v>
       </c>
       <c r="K15">
-        <v>53.7</v>
+        <v>3643.3</v>
       </c>
       <c r="L15">
-        <v>0.1834642979159549</v>
+        <v>0.2731682811984524</v>
       </c>
       <c r="M15">
-        <v>7.54</v>
+        <v>427.6</v>
       </c>
       <c r="N15">
-        <v>0.029349941611522</v>
+        <v>0.005693908476679743</v>
       </c>
       <c r="O15">
-        <v>0.1404096834264432</v>
+        <v>0.1173661241182444</v>
       </c>
       <c r="P15">
-        <v>7.54</v>
+        <v>427.6</v>
       </c>
       <c r="Q15">
-        <v>0.029349941611522</v>
+        <v>0.005693908476679743</v>
       </c>
       <c r="R15">
-        <v>0.1404096834264432</v>
+        <v>0.1173661241182444</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2213,61 +2234,67 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>547.2</v>
+        <v>17025.7</v>
       </c>
       <c r="V15">
-        <v>2.130011677695602</v>
+        <v>0.2267136986702673</v>
       </c>
       <c r="W15">
-        <v>0.06097422504825706</v>
+        <v>0.1602753887776873</v>
       </c>
       <c r="X15">
-        <v>0.0951411882015927</v>
+        <v>0.09082407997444419</v>
       </c>
       <c r="Y15">
-        <v>-0.03416696315333564</v>
+        <v>0.06945130880324316</v>
       </c>
       <c r="Z15">
-        <v>0.3868111536936698</v>
+        <v>0.7423105473328093</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>0.0001890010793913251</v>
       </c>
       <c r="AB15">
-        <v>0.05374805851533945</v>
+        <v>0.08407293767764612</v>
       </c>
       <c r="AC15">
-        <v>-0.05374805851533945</v>
+        <v>-0.0838839365982548</v>
       </c>
       <c r="AD15">
-        <v>437.7</v>
+        <v>22388</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>27.04333094390086</v>
       </c>
       <c r="AF15">
-        <v>437.7</v>
+        <v>22415.0433309439</v>
       </c>
       <c r="AG15">
-        <v>-109.5000000000001</v>
+        <v>5389.343330943899</v>
       </c>
       <c r="AH15">
-        <v>0.6301468471062482</v>
+        <v>0.2298676006694894</v>
       </c>
       <c r="AI15">
-        <v>0.3225735131549856</v>
+        <v>0.4751643463157951</v>
       </c>
       <c r="AJ15">
-        <v>-0.7428765264586168</v>
+        <v>0.06695905840246071</v>
       </c>
       <c r="AK15">
-        <v>-0.1352352723230827</v>
+        <v>0.1787655886843753</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
         <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>2493.095768374165</v>
+      </c>
+      <c r="AP15">
+        <v>600.1495914191423</v>
       </c>
     </row>
     <row r="16">
@@ -2278,7 +2305,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IndusInd Bank Limited (BSE:532187)</t>
+          <t>Fino Payments Bank Limited (NSEI:FINOPB)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2286,15 +2313,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D16">
-        <v>0.114</v>
-      </c>
-      <c r="E16">
-        <v>0.0883</v>
-      </c>
-      <c r="F16">
-        <v>0.266</v>
-      </c>
       <c r="G16">
         <v>0</v>
       </c>
@@ -2302,103 +2320,94 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0.002611976080751472</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>0.001957407688369136</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>528.4</v>
+        <v>6.84</v>
       </c>
       <c r="L16">
-        <v>0.2809890986439776</v>
+        <v>0.04949348769898698</v>
       </c>
       <c r="M16">
-        <v>52.2</v>
+        <v>-0</v>
       </c>
       <c r="N16">
-        <v>0.005657126136572996</v>
+        <v>-0</v>
       </c>
       <c r="O16">
-        <v>0.09878879636638911</v>
+        <v>-0</v>
       </c>
       <c r="P16">
-        <v>52.2</v>
+        <v>-0</v>
       </c>
       <c r="Q16">
-        <v>0.005657126136572996</v>
+        <v>-0</v>
       </c>
       <c r="R16">
-        <v>0.09878879636638911</v>
+        <v>-0</v>
       </c>
       <c r="S16">
         <v>0</v>
       </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
       <c r="U16">
-        <v>9050.5</v>
+        <v>85</v>
       </c>
       <c r="V16">
-        <v>0.9808394654991168</v>
+        <v>0.3341194968553459</v>
       </c>
       <c r="W16">
-        <v>0.09792983301517875</v>
+        <v>0.3123287671232877</v>
       </c>
       <c r="X16">
-        <v>0.069460949411636</v>
+        <v>0.09264368434427811</v>
       </c>
       <c r="Y16">
-        <v>0.02846888360354276</v>
+        <v>0.2196850827790096</v>
       </c>
       <c r="Z16">
-        <v>0.2896802257618959</v>
+        <v>5.595141700404858</v>
       </c>
       <c r="AA16">
-        <v>0.0005670223010748421</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.05433343228258597</v>
+        <v>0.08401830274282189</v>
       </c>
       <c r="AC16">
-        <v>-0.05376640998151113</v>
+        <v>-0.08401830274282189</v>
       </c>
       <c r="AD16">
-        <v>6241.6</v>
+        <v>91.3</v>
       </c>
       <c r="AE16">
-        <v>206.4408949007343</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>6448.040894900734</v>
+        <v>91.3</v>
       </c>
       <c r="AG16">
-        <v>-2602.459105099266</v>
+        <v>6.299999999999997</v>
       </c>
       <c r="AH16">
-        <v>0.4113493249131388</v>
+        <v>0.2641018223893549</v>
       </c>
       <c r="AI16">
-        <v>0.5134223457902259</v>
+        <v>0.594014313597918</v>
       </c>
       <c r="AJ16">
-        <v>-0.3928334500987681</v>
+        <v>0.0241657077100115</v>
       </c>
       <c r="AK16">
-        <v>-0.7417708272873437</v>
+        <v>0.09170305676855893</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
         <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>135.0995670995671</v>
-      </c>
-      <c r="AP16">
-        <v>-56.33028366015726</v>
       </c>
     </row>
     <row r="17">
@@ -2409,7 +2418,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Jammu and Kashmir Bank Limited (BSE:532209)</t>
+          <t>IDFC First Bank Limited (BSE:539437)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2417,6 +2426,9 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="F17">
+        <v>1.643</v>
+      </c>
       <c r="G17">
         <v>0</v>
       </c>
@@ -2424,16 +2436,16 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>0.006030550313973731</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>0.004584010862976745</v>
       </c>
       <c r="K17">
-        <v>80.3</v>
+        <v>208.3</v>
       </c>
       <c r="L17">
-        <v>0.15878979632193</v>
+        <v>0.1305383217396754</v>
       </c>
       <c r="M17">
         <v>-0</v>
@@ -2457,61 +2469,67 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>1330.5</v>
+        <v>1825</v>
       </c>
       <c r="V17">
-        <v>2.701522842639594</v>
+        <v>0.4118709095012413</v>
       </c>
       <c r="W17">
-        <v>0.09205548549810845</v>
+        <v>0.07570141008867569</v>
       </c>
       <c r="X17">
-        <v>0.06569106549420109</v>
+        <v>0.1302854681852327</v>
       </c>
       <c r="Y17">
-        <v>0.02636442000390736</v>
+        <v>-0.05458405809655699</v>
       </c>
       <c r="Z17">
-        <v>0.9636051829268295</v>
+        <v>0.2067803197030456</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>0.0009478832317685654</v>
       </c>
       <c r="AB17">
-        <v>0.05396202729353887</v>
+        <v>0.08529508473142791</v>
       </c>
       <c r="AC17">
-        <v>-0.05396202729353887</v>
+        <v>-0.08434720149965935</v>
       </c>
       <c r="AD17">
-        <v>271.5</v>
+        <v>6960.8</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>166.3852543199606</v>
       </c>
       <c r="AF17">
-        <v>271.5</v>
+        <v>7127.185254319961</v>
       </c>
       <c r="AG17">
-        <v>-1059</v>
+        <v>5302.185254319961</v>
       </c>
       <c r="AH17">
-        <v>0.3553664921465969</v>
+        <v>0.616635319256206</v>
       </c>
       <c r="AI17">
-        <v>0.2073943930944924</v>
+        <v>0.7236099217666216</v>
       </c>
       <c r="AJ17">
-        <v>1.8693733451015</v>
+        <v>0.5447533480333838</v>
       </c>
       <c r="AK17">
-        <v>49.48598130841101</v>
+        <v>0.6607508252900761</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
         <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>162.2564102564103</v>
+      </c>
+      <c r="AP17">
+        <v>123.5940618722602</v>
       </c>
     </row>
     <row r="18">
@@ -2522,7 +2540,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bank of Maharashtra (BSE:532525)</t>
+          <t>HDFC Bank Limited (NSEI:HDFCBANK)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2530,6 +2548,15 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D18">
+        <v>0.161</v>
+      </c>
+      <c r="E18">
+        <v>0.197</v>
+      </c>
+      <c r="F18">
+        <v>0.204</v>
+      </c>
       <c r="G18">
         <v>0</v>
       </c>
@@ -2537,94 +2564,103 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>-0.001921008608349937</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>-0.001444363575620856</v>
       </c>
       <c r="K18">
-        <v>109.6</v>
+        <v>5129.2</v>
       </c>
       <c r="L18">
-        <v>0.1605860805860806</v>
+        <v>0.4140191140384864</v>
       </c>
       <c r="M18">
-        <v>-0</v>
+        <v>1057.4</v>
       </c>
       <c r="N18">
-        <v>-0</v>
+        <v>0.009638031486302221</v>
       </c>
       <c r="O18">
-        <v>-0</v>
+        <v>0.2061530063167746</v>
       </c>
       <c r="P18">
-        <v>-0</v>
+        <v>1057.4</v>
       </c>
       <c r="Q18">
-        <v>-0</v>
+        <v>0.009638031486302221</v>
       </c>
       <c r="R18">
-        <v>-0</v>
+        <v>0.2061530063167746</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
       <c r="U18">
-        <v>1872.8</v>
+        <v>12869.3</v>
       </c>
       <c r="V18">
-        <v>1.07985930923139</v>
+        <v>0.1173016063993466</v>
       </c>
       <c r="W18">
-        <v>0.06723101459943565</v>
+        <v>0.1625551442624613</v>
       </c>
       <c r="X18">
-        <v>0.0672445271900044</v>
+        <v>0.09060072290403065</v>
       </c>
       <c r="Y18">
-        <v>-1.351259056875387e-05</v>
+        <v>0.07195442135843069</v>
       </c>
       <c r="Z18">
-        <v>0.4268826619964973</v>
+        <v>0.2238067655908471</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>-0.0003232583401969348</v>
       </c>
       <c r="AB18">
-        <v>0.05412330739278279</v>
+        <v>0.08402983773450776</v>
       </c>
       <c r="AC18">
-        <v>-0.05412330739278279</v>
+        <v>-0.08435309607470469</v>
       </c>
       <c r="AD18">
-        <v>1061.5</v>
+        <v>30936.4</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>996.4949572356285</v>
       </c>
       <c r="AF18">
-        <v>1061.5</v>
+        <v>31932.89495723563</v>
       </c>
       <c r="AG18">
-        <v>-811.3</v>
+        <v>19063.59495723563</v>
       </c>
       <c r="AH18">
-        <v>0.3796766578439087</v>
+        <v>0.2254445903083826</v>
       </c>
       <c r="AI18">
-        <v>0.3736228925416212</v>
+        <v>0.496892524460323</v>
       </c>
       <c r="AJ18">
-        <v>-0.8789815817984832</v>
+        <v>0.1480382474191972</v>
       </c>
       <c r="AK18">
-        <v>-0.8378601673035216</v>
+        <v>0.3709166845542363</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
         <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>176.2757834757835</v>
+      </c>
+      <c r="AP18">
+        <v>108.6244726908013</v>
       </c>
     </row>
     <row r="19">
@@ -2635,7 +2671,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Federal Bank Limited (NSEI:FEDERALBNK)</t>
+          <t>DCB Bank Limited (NSEI:DCBBANK)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2643,8 +2679,11 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="F19">
-        <v>0.284</v>
+      <c r="D19">
+        <v>0.0998</v>
+      </c>
+      <c r="E19">
+        <v>0.118</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2653,34 +2692,34 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0.0003547842222807584</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>0.0002644557239700131</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>240.2</v>
+        <v>48.9</v>
       </c>
       <c r="L19">
-        <v>0.2708615245827695</v>
+        <v>0.2334128878281623</v>
       </c>
       <c r="M19">
-        <v>18.8</v>
+        <v>3.82</v>
       </c>
       <c r="N19">
-        <v>0.00803281490343531</v>
+        <v>0.008018471872376155</v>
       </c>
       <c r="O19">
-        <v>0.07826810990840967</v>
+        <v>0.07811860940695296</v>
       </c>
       <c r="P19">
-        <v>18.8</v>
+        <v>3.82</v>
       </c>
       <c r="Q19">
-        <v>0.00803281490343531</v>
+        <v>0.008018471872376155</v>
       </c>
       <c r="R19">
-        <v>0.07826810990840967</v>
+        <v>0.07811860940695296</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -2689,67 +2728,61 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>3019.9</v>
+        <v>286.9</v>
       </c>
       <c r="V19">
-        <v>1.290334985472569</v>
+        <v>0.602225020990764</v>
       </c>
       <c r="W19">
-        <v>0.113532164295505</v>
+        <v>0.09402038069601999</v>
       </c>
       <c r="X19">
-        <v>0.0725878791482323</v>
+        <v>0.109142329571603</v>
       </c>
       <c r="Y19">
-        <v>0.04094428514727275</v>
+        <v>-0.01512194887558303</v>
       </c>
       <c r="Z19">
-        <v>0.702100584930957</v>
+        <v>0.3826484018264841</v>
       </c>
       <c r="AA19">
-        <v>0.0001856745184876859</v>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.05459583869965581</v>
+        <v>0.08450270378388475</v>
       </c>
       <c r="AC19">
-        <v>-0.05441016418116813</v>
+        <v>-0.08450270378388475</v>
       </c>
       <c r="AD19">
-        <v>1919.9</v>
+        <v>431.9</v>
       </c>
       <c r="AE19">
-        <v>1.966886758407117</v>
+        <v>0</v>
       </c>
       <c r="AF19">
-        <v>1921.866886758407</v>
+        <v>431.9</v>
       </c>
       <c r="AG19">
-        <v>-1098.033113241593</v>
+        <v>145</v>
       </c>
       <c r="AH19">
-        <v>0.4509025215499937</v>
+        <v>0.4755036882087416</v>
       </c>
       <c r="AI19">
-        <v>0.4365332625697983</v>
+        <v>0.4538194809288641</v>
       </c>
       <c r="AJ19">
-        <v>-0.8838235507923018</v>
+        <v>0.2333440617959447</v>
       </c>
       <c r="AK19">
-        <v>-0.7941414694727205</v>
+        <v>0.2181107099879663</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
         <v>0</v>
-      </c>
-      <c r="AN19">
-        <v>2711.723163841808</v>
-      </c>
-      <c r="AP19">
-        <v>-1550.894227742363</v>
       </c>
     </row>
     <row r="20">
@@ -2760,7 +2793,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HDFC Bank Limited (NSEI:HDFCBANK)</t>
+          <t>Canara Bank (NSEI:CANBK)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2768,15 +2801,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D20">
-        <v>0.157</v>
-      </c>
-      <c r="E20">
-        <v>0.2</v>
-      </c>
-      <c r="F20">
-        <v>0.197</v>
-      </c>
       <c r="G20">
         <v>0</v>
       </c>
@@ -2784,103 +2808,94 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>-0.00516054588256604</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>-0.003840336639834734</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>4613.8</v>
+        <v>1039.8</v>
       </c>
       <c r="L20">
-        <v>0.4087458029536575</v>
+        <v>0.243415970222628</v>
       </c>
       <c r="M20">
-        <v>484.3</v>
+        <v>-0</v>
       </c>
       <c r="N20">
-        <v>0.004400946889667362</v>
+        <v>-0</v>
       </c>
       <c r="O20">
-        <v>0.1049677055789154</v>
+        <v>-0</v>
       </c>
       <c r="P20">
-        <v>484.3</v>
+        <v>-0</v>
       </c>
       <c r="Q20">
-        <v>0.004400946889667362</v>
+        <v>-0</v>
       </c>
       <c r="R20">
-        <v>0.1049677055789154</v>
+        <v>-0</v>
       </c>
       <c r="S20">
         <v>0</v>
       </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
       <c r="U20">
-        <v>23112.7</v>
+        <v>6806.4</v>
       </c>
       <c r="V20">
-        <v>0.2100304876663532</v>
+        <v>0.9311717627744716</v>
       </c>
       <c r="W20">
-        <v>0.16818675590356</v>
+        <v>0.1143466690126905</v>
       </c>
       <c r="X20">
-        <v>0.0578649998400072</v>
+        <v>0.1134821341685787</v>
       </c>
       <c r="Y20">
-        <v>0.1103217560635528</v>
+        <v>0.00086453484411185</v>
       </c>
       <c r="Z20">
-        <v>0.2271845654474973</v>
+        <v>0.3310266265769816</v>
       </c>
       <c r="AA20">
-        <v>-0.0008724652106929562</v>
+        <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.05354860682222683</v>
+        <v>0.08470958876437033</v>
       </c>
       <c r="AC20">
-        <v>-0.05442107203291979</v>
+        <v>-0.08470958876437033</v>
       </c>
       <c r="AD20">
-        <v>25829.4</v>
+        <v>7679.8</v>
       </c>
       <c r="AE20">
-        <v>1131.753468793203</v>
+        <v>0</v>
       </c>
       <c r="AF20">
-        <v>26961.1534687932</v>
+        <v>7679.8</v>
       </c>
       <c r="AG20">
-        <v>3848.453468793203</v>
+        <v>873.4000000000005</v>
       </c>
       <c r="AH20">
-        <v>0.1967886199304494</v>
+        <v>0.5123521445297646</v>
       </c>
       <c r="AI20">
-        <v>0.4696087110752674</v>
+        <v>0.4524022714955584</v>
       </c>
       <c r="AJ20">
-        <v>0.03379009281595005</v>
+        <v>0.1067347761795941</v>
       </c>
       <c r="AK20">
-        <v>0.1122022516406859</v>
+        <v>0.08588679542146879</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
         <v>0</v>
-      </c>
-      <c r="AN20">
-        <v>153.6549672813802</v>
-      </c>
-      <c r="AP20">
-        <v>22.89383384172042</v>
       </c>
     </row>
     <row r="21">
@@ -2891,7 +2906,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RBL Bank Limited (BSE:540065)</t>
+          <t>Bank of Maharashtra (NSEI:MAHABANK)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2899,9 +2914,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="F21">
-        <v>0.215</v>
-      </c>
       <c r="G21">
         <v>0</v>
       </c>
@@ -2909,100 +2921,97 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>0.006696422741637071</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>0.006696422741637071</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>-31</v>
+        <v>203.1</v>
       </c>
       <c r="L21">
-        <v>-0.07370423204945316</v>
+        <v>0.2986325540361711</v>
       </c>
       <c r="M21">
-        <v>-0</v>
+        <v>82.7</v>
       </c>
       <c r="N21">
-        <v>-0</v>
+        <v>0.03323287120755476</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>0.4071885770556377</v>
       </c>
       <c r="P21">
-        <v>-0</v>
+        <v>82.7</v>
       </c>
       <c r="Q21">
-        <v>-0</v>
+        <v>0.03323287120755476</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>0.4071885770556377</v>
       </c>
       <c r="S21">
         <v>0</v>
       </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
       <c r="U21">
-        <v>2499.4</v>
+        <v>1783.4</v>
       </c>
       <c r="V21">
-        <v>2.445357597104002</v>
+        <v>0.7166566204540888</v>
       </c>
       <c r="W21">
-        <v>-0.02095869109593672</v>
+        <v>0.1141267700606878</v>
       </c>
       <c r="X21">
-        <v>0.09741594654507246</v>
+        <v>0.1159144044531887</v>
       </c>
       <c r="Y21">
-        <v>-0.1183746376410092</v>
+        <v>-0.001787634392500861</v>
       </c>
       <c r="Z21">
-        <v>0.1843211000531161</v>
+        <v>0.7023649695342353</v>
       </c>
       <c r="AA21">
-        <v>0.001234292006159249</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.05586320538881996</v>
+        <v>0.08481330871760595</v>
       </c>
       <c r="AC21">
-        <v>-0.05462891338266071</v>
+        <v>-0.08481330871760595</v>
       </c>
       <c r="AD21">
-        <v>1744.5</v>
+        <v>2815.5</v>
       </c>
       <c r="AE21">
-        <v>87.91742297433723</v>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <v>1832.417422974337</v>
+        <v>2815.5</v>
       </c>
       <c r="AG21">
-        <v>-666.982577025663</v>
+        <v>1032.1</v>
       </c>
       <c r="AH21">
-        <v>0.6419359742653115</v>
+        <v>0.5308257918552036</v>
       </c>
       <c r="AI21">
-        <v>0.5263272304433457</v>
+        <v>0.6035499153250874</v>
       </c>
       <c r="AJ21">
-        <v>-1.878202909446837</v>
+        <v>0.2931602567744134</v>
       </c>
       <c r="AK21">
-        <v>-0.679127120060359</v>
+        <v>0.3581815026895714</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21">
         <v>0</v>
-      </c>
-      <c r="AN21">
-        <v>85.51470588235294</v>
-      </c>
-      <c r="AP21">
-        <v>-32.69522436400309</v>
       </c>
     </row>
     <row r="22">
@@ -3013,7 +3022,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IDFC First Bank Limited (BSE:539437)</t>
+          <t>The Karnataka Bank Limited (NSEI:KTKBANK)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3022,7 +3031,10 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.243</v>
+        <v>0.108</v>
+      </c>
+      <c r="E22">
+        <v>0.131</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3031,100 +3043,97 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>0.00515823892638478</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>0.00515823892638478</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>-31.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="L22">
-        <v>-0.02942264988897113</v>
+        <v>0.264626945786366</v>
       </c>
       <c r="M22">
-        <v>-0</v>
+        <v>15.3</v>
       </c>
       <c r="N22">
-        <v>-0</v>
+        <v>0.02667829119442023</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>0.1551724137931035</v>
       </c>
       <c r="P22">
-        <v>-0</v>
+        <v>15.3</v>
       </c>
       <c r="Q22">
-        <v>-0</v>
+        <v>0.02667829119442023</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>0.1551724137931035</v>
       </c>
       <c r="S22">
         <v>0</v>
       </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
       <c r="U22">
-        <v>2293.1</v>
+        <v>616.5</v>
       </c>
       <c r="V22">
-        <v>0.568696989236645</v>
+        <v>1.074978204010462</v>
       </c>
       <c r="W22">
-        <v>-0.01327599883104413</v>
+        <v>0.1072671888598781</v>
       </c>
       <c r="X22">
-        <v>0.09744579729121933</v>
+        <v>0.120197270376677</v>
       </c>
       <c r="Y22">
-        <v>-0.1107217961222635</v>
+        <v>-0.01293008151679888</v>
       </c>
       <c r="Z22">
-        <v>0.130001896383486</v>
+        <v>0.4601704334938866</v>
       </c>
       <c r="AA22">
-        <v>0.0006705808424291383</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.0558641986059098</v>
+        <v>0.08497803685029348</v>
       </c>
       <c r="AC22">
-        <v>-0.05519361776348066</v>
+        <v>-0.08497803685029348</v>
       </c>
       <c r="AD22">
-        <v>7092</v>
+        <v>730.4</v>
       </c>
       <c r="AE22">
-        <v>141.6248768418166</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>7233.624876841816</v>
+        <v>730.4</v>
       </c>
       <c r="AG22">
-        <v>4940.524876841817</v>
+        <v>113.9</v>
       </c>
       <c r="AH22">
-        <v>0.6420856844412125</v>
+        <v>0.5601656568755272</v>
       </c>
       <c r="AI22">
-        <v>0.7244328461363314</v>
+        <v>0.4403979499547784</v>
       </c>
       <c r="AJ22">
-        <v>0.5506158881114342</v>
+        <v>0.1656968286296188</v>
       </c>
       <c r="AK22">
-        <v>0.6422834985058467</v>
+        <v>0.1093090211132437</v>
       </c>
       <c r="AL22">
         <v>0</v>
       </c>
       <c r="AM22">
         <v>0</v>
-      </c>
-      <c r="AN22">
-        <v>209.2035398230089</v>
-      </c>
-      <c r="AP22">
-        <v>145.7381969569857</v>
       </c>
     </row>
     <row r="23">
@@ -3135,7 +3144,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Punjab National Bank (BSE:532461)</t>
+          <t>Bank of Baroda (NSEI:BANKBARODA)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3143,8 +3152,14 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D23">
+        <v>0.237</v>
+      </c>
+      <c r="E23">
+        <v>0.474</v>
+      </c>
       <c r="F23">
-        <v>0.42</v>
+        <v>0.278</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3153,94 +3168,103 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>-7.721671577331875e-05</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>-6.945612678809639e-05</v>
       </c>
       <c r="K23">
-        <v>501.6</v>
+        <v>1209.2</v>
       </c>
       <c r="L23">
-        <v>0.1599336798137933</v>
+        <v>0.258785258742456</v>
       </c>
       <c r="M23">
-        <v>-0</v>
+        <v>180.1</v>
       </c>
       <c r="N23">
-        <v>-0</v>
+        <v>0.01552104519287118</v>
       </c>
       <c r="O23">
-        <v>-0</v>
+        <v>0.1489414488918293</v>
       </c>
       <c r="P23">
-        <v>-0</v>
+        <v>180.1</v>
       </c>
       <c r="Q23">
-        <v>-0</v>
+        <v>0.01552104519287118</v>
       </c>
       <c r="R23">
-        <v>-0</v>
+        <v>0.1489414488918293</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
       <c r="U23">
-        <v>20075</v>
+        <v>6408</v>
       </c>
       <c r="V23">
-        <v>3.641921555821632</v>
+        <v>0.552242407528698</v>
       </c>
       <c r="W23">
-        <v>0.04174573055028463</v>
+        <v>0.1042647489954645</v>
       </c>
       <c r="X23">
-        <v>0.08308988455838037</v>
+        <v>0.1194222391990772</v>
       </c>
       <c r="Y23">
-        <v>-0.04134415400809574</v>
+        <v>-0.01515749020361272</v>
       </c>
       <c r="Z23">
-        <v>0.542171590575138</v>
+        <v>0.9935985734930044</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>-6.901150849700182e-05</v>
       </c>
       <c r="AB23">
-        <v>0.0552665660788533</v>
+        <v>0.08494977177469459</v>
       </c>
       <c r="AC23">
-        <v>-0.0552665660788533</v>
+        <v>-0.0850187832831916</v>
       </c>
       <c r="AD23">
-        <v>6791.9</v>
+        <v>14418.8</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>60.80401413061205</v>
       </c>
       <c r="AF23">
-        <v>6791.9</v>
+        <v>14479.60401413061</v>
       </c>
       <c r="AG23">
-        <v>-13283.1</v>
+        <v>8071.604014130611</v>
       </c>
       <c r="AH23">
-        <v>0.5520029908729611</v>
+        <v>0.5551313407005621</v>
       </c>
       <c r="AI23">
-        <v>0.3396170751098821</v>
+        <v>0.5449400408968467</v>
       </c>
       <c r="AJ23">
-        <v>1.709338686638613</v>
+        <v>0.4102424558512142</v>
       </c>
       <c r="AK23">
-        <v>174.0904325032741</v>
+        <v>0.4003175324705525</v>
       </c>
       <c r="AL23">
         <v>0</v>
       </c>
       <c r="AM23">
         <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>1221.93220338983</v>
+      </c>
+      <c r="AP23">
+        <v>684.034238485645</v>
       </c>
     </row>
     <row r="24">
@@ -3251,7 +3275,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Canara Bank (BSE:532483)</t>
+          <t>Suryoday Small Finance Bank Limited (NSEI:SURYODAY)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3259,9 +3283,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D24">
-        <v>0.51</v>
-      </c>
       <c r="G24">
         <v>0</v>
       </c>
@@ -3269,16 +3290,16 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>0.001039697267459076</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>0.0005198486337295381</v>
       </c>
       <c r="K24">
-        <v>605.9</v>
+        <v>-2.78</v>
       </c>
       <c r="L24">
-        <v>0.1227860414217971</v>
+        <v>-0.05063752276867031</v>
       </c>
       <c r="M24">
         <v>-0</v>
@@ -3287,7 +3308,7 @@
         <v>-0</v>
       </c>
       <c r="O24">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P24">
         <v>-0</v>
@@ -3296,67 +3317,73 @@
         <v>-0</v>
       </c>
       <c r="R24">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S24">
         <v>0</v>
       </c>
       <c r="U24">
-        <v>6329.3</v>
+        <v>51.1</v>
       </c>
       <c r="V24">
-        <v>1.300425304596166</v>
+        <v>0.3271446862996159</v>
       </c>
       <c r="W24">
-        <v>0.07720930232558139</v>
+        <v>-0.01331417624521073</v>
       </c>
       <c r="X24">
-        <v>0.1048427297353251</v>
+        <v>0.137549080760154</v>
       </c>
       <c r="Y24">
-        <v>-0.02763342740974375</v>
+        <v>-0.1508632570053647</v>
       </c>
       <c r="Z24">
-        <v>-1.372628650904033</v>
+        <v>0.1306180006240006</v>
       </c>
       <c r="AA24">
-        <v>-0</v>
+        <v>6.790158916487064e-05</v>
       </c>
       <c r="AB24">
-        <v>0.05608711641492119</v>
+        <v>0.08547721782579321</v>
       </c>
       <c r="AC24">
-        <v>-0.05608711641492119</v>
+        <v>-0.08540931623662834</v>
       </c>
       <c r="AD24">
-        <v>10140.3</v>
+        <v>288.8</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>0.1096031000824836</v>
       </c>
       <c r="AF24">
-        <v>10140.3</v>
+        <v>288.9096031000825</v>
       </c>
       <c r="AG24">
-        <v>3810.999999999999</v>
+        <v>237.8096031000825</v>
       </c>
       <c r="AH24">
-        <v>0.6756866612471181</v>
+        <v>0.6490751965086707</v>
       </c>
       <c r="AI24">
-        <v>0.5249091530266795</v>
+        <v>0.6061766301410734</v>
       </c>
       <c r="AJ24">
-        <v>0.4391514271557138</v>
+        <v>0.6035629619912498</v>
       </c>
       <c r="AK24">
-        <v>0.2934043683452794</v>
+        <v>0.5588818709789453</v>
       </c>
       <c r="AL24">
         <v>0</v>
       </c>
       <c r="AM24">
         <v>0</v>
+      </c>
+      <c r="AN24">
+        <v>3655.696202531646</v>
+      </c>
+      <c r="AP24">
+        <v>3010.248140507374</v>
       </c>
     </row>
     <row r="25">
@@ -3367,7 +3394,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The South Indian Bank Limited (BSE:532218)</t>
+          <t>Yes Bank Limited (NSEI:YESBANK)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3375,9 +3402,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D25">
-        <v>-0.0092</v>
-      </c>
       <c r="G25">
         <v>0</v>
       </c>
@@ -3385,16 +3409,16 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>-0.004621823770611334</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>-0.003433067575125113</v>
       </c>
       <c r="K25">
-        <v>-35.3</v>
+        <v>136.7</v>
       </c>
       <c r="L25">
-        <v>-0.1570284697508897</v>
+        <v>0.1170476924394212</v>
       </c>
       <c r="M25">
         <v>-0</v>
@@ -3403,7 +3427,7 @@
         <v>-0</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P25">
         <v>-0</v>
@@ -3412,67 +3436,73 @@
         <v>-0</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S25">
         <v>0</v>
       </c>
       <c r="U25">
-        <v>1756.7</v>
+        <v>3858.9</v>
       </c>
       <c r="V25">
-        <v>7.066371681415929</v>
+        <v>0.5391784267151041</v>
       </c>
       <c r="W25">
-        <v>-0.04589780262644649</v>
+        <v>0.03022664455500276</v>
       </c>
       <c r="X25">
-        <v>0.1123110369112195</v>
+        <v>0.1225304898967624</v>
       </c>
       <c r="Y25">
-        <v>-0.158208839537666</v>
+        <v>-0.09230384534175967</v>
       </c>
       <c r="Z25">
-        <v>0.2056912800805197</v>
+        <v>0.1177486014922054</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>-0.0004042389057992187</v>
       </c>
       <c r="AB25">
-        <v>0.0562733988325942</v>
+        <v>0.08505939383734587</v>
       </c>
       <c r="AC25">
-        <v>-0.0562733988325942</v>
+        <v>-0.08546363274314508</v>
       </c>
       <c r="AD25">
-        <v>590.6</v>
+        <v>9447.4</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>221.9891399084849</v>
       </c>
       <c r="AF25">
-        <v>590.6</v>
+        <v>9669.389139908484</v>
       </c>
       <c r="AG25">
-        <v>-1166.1</v>
+        <v>5810.489139908485</v>
       </c>
       <c r="AH25">
-        <v>0.703765490943756</v>
+        <v>0.5746562176536633</v>
       </c>
       <c r="AI25">
-        <v>0.4374814814814815</v>
+        <v>0.6958302771037386</v>
       </c>
       <c r="AJ25">
-        <v>1.270953678474114</v>
+        <v>0.4480812805947328</v>
       </c>
       <c r="AK25">
-        <v>2.867223998032948</v>
+        <v>0.5788902819194329</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
         <v>0</v>
+      </c>
+      <c r="AN25">
+        <v>242.2410256410256</v>
+      </c>
+      <c r="AP25">
+        <v>148.9869010232945</v>
       </c>
     </row>
     <row r="26">
@@ -3483,7 +3513,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>State Bank of India (NSEI:SBIN)</t>
+          <t>Indian Bank (NSEI:INDIANB)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3491,15 +3521,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D26">
-        <v>0.189</v>
-      </c>
-      <c r="E26">
-        <v>0.515</v>
-      </c>
-      <c r="F26">
-        <v>0.328</v>
-      </c>
       <c r="G26">
         <v>0</v>
       </c>
@@ -3507,34 +3528,34 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>0.0003032492421052409</v>
+        <v>0</v>
       </c>
       <c r="J26">
-        <v>0.0002830767265052665</v>
+        <v>0</v>
       </c>
       <c r="K26">
-        <v>3863</v>
+        <v>535.1</v>
       </c>
       <c r="L26">
-        <v>0.1426529836002614</v>
+        <v>0.2662189054726368</v>
       </c>
       <c r="M26">
-        <v>481.3</v>
+        <v>189.7</v>
       </c>
       <c r="N26">
-        <v>0.008726886352839637</v>
+        <v>0.04417689387764607</v>
       </c>
       <c r="O26">
-        <v>0.1245922857882475</v>
+        <v>0.3545131751074565</v>
       </c>
       <c r="P26">
-        <v>481.3</v>
+        <v>189.7</v>
       </c>
       <c r="Q26">
-        <v>0.008726886352839637</v>
+        <v>0.04417689387764607</v>
       </c>
       <c r="R26">
-        <v>0.1245922857882475</v>
+        <v>0.3545131751074565</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -3543,67 +3564,61 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>54004.8</v>
+        <v>3083.4</v>
       </c>
       <c r="V26">
-        <v>0.9792099565922171</v>
+        <v>0.7180550057055028</v>
       </c>
       <c r="W26">
-        <v>0.1066643840911852</v>
+        <v>0.09125948665472841</v>
       </c>
       <c r="X26">
-        <v>0.07898773819629692</v>
+        <v>0.1008590715102836</v>
       </c>
       <c r="Y26">
-        <v>0.02767664589488827</v>
+        <v>-0.009599584855555218</v>
       </c>
       <c r="Z26">
-        <v>0.5453125900794251</v>
+        <v>0.6345498168960727</v>
       </c>
       <c r="AA26">
-        <v>0.000154365302921792</v>
+        <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.0567149722296367</v>
+        <v>0.08560517111726795</v>
       </c>
       <c r="AC26">
-        <v>-0.05656060692671491</v>
+        <v>-0.08560517111726795</v>
       </c>
       <c r="AD26">
-        <v>59059.1</v>
+        <v>2712.2</v>
       </c>
       <c r="AE26">
-        <v>42.44050749281354</v>
+        <v>0</v>
       </c>
       <c r="AF26">
-        <v>59101.54050749281</v>
+        <v>2712.2</v>
       </c>
       <c r="AG26">
-        <v>5096.74050749281</v>
+        <v>-371.2000000000003</v>
       </c>
       <c r="AH26">
-        <v>0.5172868220719176</v>
+        <v>0.3871087449866548</v>
       </c>
       <c r="AI26">
-        <v>0.5913676206286264</v>
+        <v>0.3167828819042947</v>
       </c>
       <c r="AJ26">
-        <v>0.08459581431992826</v>
+        <v>-0.09462387519437158</v>
       </c>
       <c r="AK26">
-        <v>0.1109539445011429</v>
+        <v>-0.06775824617125757</v>
       </c>
       <c r="AL26">
         <v>0</v>
       </c>
       <c r="AM26">
         <v>0</v>
-      </c>
-      <c r="AN26">
-        <v>3536.473053892216</v>
-      </c>
-      <c r="AP26">
-        <v>305.1940423648389</v>
       </c>
     </row>
     <row r="27">
@@ -3614,7 +3629,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Indian Bank (BSE:532814)</t>
+          <t>Axis Bank Limited (BSE:532215)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3622,6 +3637,9 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="F27">
+        <v>0.273</v>
+      </c>
       <c r="G27">
         <v>0</v>
       </c>
@@ -3629,34 +3647,34 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>-0.0008991446329888266</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>-0.0008327180294904683</v>
       </c>
       <c r="K27">
-        <v>626.4</v>
+        <v>2257.2</v>
       </c>
       <c r="L27">
-        <v>0.3349553499812844</v>
+        <v>0.3881551795295088</v>
       </c>
       <c r="M27">
-        <v>85.40000000000001</v>
+        <v>37.7</v>
       </c>
       <c r="N27">
-        <v>0.03662406724418904</v>
+        <v>0.001086552400934954</v>
       </c>
       <c r="O27">
-        <v>0.1363346104725415</v>
+        <v>0.01670210880737197</v>
       </c>
       <c r="P27">
-        <v>85.40000000000001</v>
+        <v>37.7</v>
       </c>
       <c r="Q27">
-        <v>0.03662406724418904</v>
+        <v>0.001086552400934954</v>
       </c>
       <c r="R27">
-        <v>0.1363346104725415</v>
+        <v>0.01670210880737197</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -3665,61 +3683,67 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>5526.6</v>
+        <v>8963.9</v>
       </c>
       <c r="V27">
-        <v>2.370100351659662</v>
+        <v>0.2583487285607648</v>
       </c>
       <c r="W27">
-        <v>0.1229295863097574</v>
+        <v>0.1527622682882261</v>
       </c>
       <c r="X27">
-        <v>0.08262474464765807</v>
+        <v>0.1036717143870875</v>
       </c>
       <c r="Y27">
-        <v>0.04030484166209936</v>
+        <v>0.04909055390113859</v>
       </c>
       <c r="Z27">
-        <v>0.3176228812119977</v>
+        <v>0.2314107407226287</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>-0.0001926998960174771</v>
       </c>
       <c r="AB27">
-        <v>0.05702156101465276</v>
+        <v>0.08592844635785718</v>
       </c>
       <c r="AC27">
-        <v>-0.05702156101465276</v>
+        <v>-0.08612114625387465</v>
       </c>
       <c r="AD27">
-        <v>2830.7</v>
+        <v>24509</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>645.6435293487832</v>
       </c>
       <c r="AF27">
-        <v>2830.7</v>
+        <v>25154.64352934878</v>
       </c>
       <c r="AG27">
-        <v>-2695.900000000001</v>
+        <v>16190.74352934879</v>
       </c>
       <c r="AH27">
-        <v>0.548319612590799</v>
+        <v>0.4202839567038729</v>
       </c>
       <c r="AI27">
-        <v>0.3254650815186148</v>
+        <v>0.6136784138611479</v>
       </c>
       <c r="AJ27">
-        <v>7.404284537215045</v>
+        <v>0.318166501854443</v>
       </c>
       <c r="AK27">
-        <v>-0.8502270720322951</v>
+        <v>0.5055492888002706</v>
       </c>
       <c r="AL27">
         <v>0</v>
       </c>
       <c r="AM27">
         <v>0</v>
+      </c>
+      <c r="AN27">
+        <v>197.8127522195319</v>
+      </c>
+      <c r="AP27">
+        <v>130.675896120652</v>
       </c>
     </row>
     <row r="28">
@@ -3730,7 +3754,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bank of India Limited (BSE:532149)</t>
+          <t>State Bank of India (NSEI:SBIN)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3738,6 +3762,15 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D28">
+        <v>0.192</v>
+      </c>
+      <c r="E28">
+        <v>0.59</v>
+      </c>
+      <c r="F28">
+        <v>1.165</v>
+      </c>
       <c r="G28">
         <v>0</v>
       </c>
@@ -3745,94 +3778,103 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>0.0003893983645240406</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>0.0003721725639166213</v>
       </c>
       <c r="K28">
-        <v>337.3</v>
+        <v>5060.7</v>
       </c>
       <c r="L28">
-        <v>0.1699073141245215</v>
+        <v>0.1886687643532464</v>
       </c>
       <c r="M28">
-        <v>-0</v>
+        <v>0.001</v>
       </c>
       <c r="N28">
-        <v>-0</v>
+        <v>1.511053355293976e-08</v>
       </c>
       <c r="O28">
-        <v>-0</v>
+        <v>1.976011223743751e-07</v>
       </c>
       <c r="P28">
-        <v>-0</v>
+        <v>0.001</v>
       </c>
       <c r="Q28">
-        <v>-0</v>
+        <v>1.511053355293976e-08</v>
       </c>
       <c r="R28">
-        <v>-0</v>
+        <v>1.976011223743751e-07</v>
       </c>
       <c r="S28">
         <v>0</v>
       </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
       <c r="U28">
-        <v>15832.1</v>
+        <v>28768.8</v>
       </c>
       <c r="V28">
-        <v>5.597150533832992</v>
+        <v>0.4347119176778132</v>
       </c>
       <c r="W28">
-        <v>0.05343450985362145</v>
+        <v>0.1283454602171426</v>
       </c>
       <c r="X28">
-        <v>0.08024710477398442</v>
+        <v>0.1107083096487222</v>
       </c>
       <c r="Y28">
-        <v>-0.02681259492036297</v>
+        <v>0.01763715056842043</v>
       </c>
       <c r="Z28">
-        <v>-0.372052925521946</v>
+        <v>0.6021477797813979</v>
       </c>
       <c r="AA28">
-        <v>-0</v>
+        <v>0.0002241028830579439</v>
       </c>
       <c r="AB28">
-        <v>0.0575070261923574</v>
+        <v>0.08660219254412367</v>
       </c>
       <c r="AC28">
-        <v>-0.0575070261923574</v>
+        <v>-0.08637808966106572</v>
       </c>
       <c r="AD28">
-        <v>3170.6</v>
+        <v>63376.4</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>61.27544894349377</v>
       </c>
       <c r="AF28">
-        <v>3170.6</v>
+        <v>63437.6754489435</v>
       </c>
       <c r="AG28">
-        <v>-12661.5</v>
+        <v>34668.87544894349</v>
       </c>
       <c r="AH28">
-        <v>0.5285038005067342</v>
+        <v>0.489425262831493</v>
       </c>
       <c r="AI28">
-        <v>0.3013248180038395</v>
+        <v>0.5992087413622215</v>
       </c>
       <c r="AJ28">
-        <v>1.287666914135199</v>
+        <v>0.3437739793189336</v>
       </c>
       <c r="AK28">
-        <v>2.384508182828302</v>
+        <v>0.4496595537055058</v>
       </c>
       <c r="AL28">
         <v>0</v>
       </c>
       <c r="AM28">
         <v>0</v>
+      </c>
+      <c r="AN28">
+        <v>2791.911894273128</v>
+      </c>
+      <c r="AP28">
+        <v>1527.263235636277</v>
       </c>
     </row>
     <row r="29">
@@ -3843,7 +3885,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Yes Bank Limited (NSEI:YESBANK)</t>
+          <t>Union Bank of India (NSEI:UNIONBANK)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3858,463 +3900,97 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>-0.03911471880188125</v>
+        <v>0</v>
       </c>
       <c r="J29">
-        <v>-0.03911471880188125</v>
+        <v>0</v>
       </c>
       <c r="K29">
-        <v>-433.7</v>
+        <v>746</v>
       </c>
       <c r="L29">
-        <v>-1.633521657250471</v>
+        <v>0.2403427945487935</v>
       </c>
       <c r="M29">
-        <v>-0</v>
+        <v>159.6</v>
       </c>
       <c r="N29">
-        <v>-0</v>
+        <v>0.02403686858037892</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>0.213941018766756</v>
       </c>
       <c r="P29">
-        <v>-0</v>
+        <v>159.6</v>
       </c>
       <c r="Q29">
-        <v>-0</v>
+        <v>0.02403686858037892</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>0.213941018766756</v>
       </c>
       <c r="S29">
         <v>0</v>
       </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
       <c r="U29">
-        <v>3440.8</v>
+        <v>9626.6</v>
       </c>
       <c r="V29">
-        <v>0.7468958930276982</v>
+        <v>1.449832826289948</v>
       </c>
       <c r="W29">
-        <v>-0.08679902333586838</v>
+        <v>0.07943945137794438</v>
       </c>
       <c r="X29">
-        <v>0.1009590866676517</v>
+        <v>0.1134083079843638</v>
       </c>
       <c r="Y29">
-        <v>-0.1877581100035201</v>
+        <v>-0.03396885660641942</v>
       </c>
       <c r="Z29">
-        <v>0.02201323734623848</v>
+        <v>0.2822445713454334</v>
       </c>
       <c r="AA29">
-        <v>-0.0008610415887171888</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>0.05738074713048068</v>
+        <v>0.0875722170948449</v>
       </c>
       <c r="AC29">
-        <v>-0.05824178871919786</v>
+        <v>-0.0875722170948449</v>
       </c>
       <c r="AD29">
-        <v>8614.9</v>
+        <v>6959.9</v>
       </c>
       <c r="AE29">
-        <v>282.9247892094974</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>8897.824789209497</v>
+        <v>6959.9</v>
       </c>
       <c r="AG29">
-        <v>5457.024789209497</v>
+        <v>-2666.700000000001</v>
       </c>
       <c r="AH29">
-        <v>0.6588724180118696</v>
+        <v>0.5117686419553372</v>
       </c>
       <c r="AI29">
-        <v>0.6630111363894651</v>
+        <v>0.4318359496184153</v>
       </c>
       <c r="AJ29">
-        <v>0.5422416331274523</v>
+        <v>-0.6711887443054545</v>
       </c>
       <c r="AK29">
-        <v>0.5468221087150344</v>
+        <v>-0.4108683594231481</v>
       </c>
       <c r="AL29">
         <v>0</v>
       </c>
       <c r="AM29">
         <v>0</v>
-      </c>
-      <c r="AN29">
-        <v>186.4696969696969</v>
-      </c>
-      <c r="AP29">
-        <v>118.1174196798592</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Axis Bank Limited (BSE:532215)</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="F30">
-        <v>0.458</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>-0.01111193814224019</v>
-      </c>
-      <c r="J30">
-        <v>-0.01018519350365659</v>
-      </c>
-      <c r="K30">
-        <v>1348.7</v>
-      </c>
-      <c r="L30">
-        <v>0.3024126642450334</v>
-      </c>
-      <c r="M30">
-        <v>-0</v>
-      </c>
-      <c r="N30">
-        <v>-0</v>
-      </c>
-      <c r="O30">
-        <v>-0</v>
-      </c>
-      <c r="P30">
-        <v>-0</v>
-      </c>
-      <c r="Q30">
-        <v>-0</v>
-      </c>
-      <c r="R30">
-        <v>-0</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="U30">
-        <v>13232.2</v>
-      </c>
-      <c r="V30">
-        <v>0.4736578346374954</v>
-      </c>
-      <c r="W30">
-        <v>0.09997331475249432</v>
-      </c>
-      <c r="X30">
-        <v>0.07339364161690345</v>
-      </c>
-      <c r="Y30">
-        <v>0.02657967313559087</v>
-      </c>
-      <c r="Z30">
-        <v>0.1697226672528214</v>
-      </c>
-      <c r="AA30">
-        <v>-0.001728658207926706</v>
-      </c>
-      <c r="AB30">
-        <v>0.0567447126083914</v>
-      </c>
-      <c r="AC30">
-        <v>-0.05847337081631811</v>
-      </c>
-      <c r="AD30">
-        <v>22940</v>
-      </c>
-      <c r="AE30">
-        <v>881.2851086338139</v>
-      </c>
-      <c r="AF30">
-        <v>23821.28510863381</v>
-      </c>
-      <c r="AG30">
-        <v>10589.08510863381</v>
-      </c>
-      <c r="AH30">
-        <v>0.460248117902856</v>
-      </c>
-      <c r="AI30">
-        <v>0.6167261515098555</v>
-      </c>
-      <c r="AJ30">
-        <v>0.2748606552495238</v>
-      </c>
-      <c r="AK30">
-        <v>0.4170049981257951</v>
-      </c>
-      <c r="AL30">
-        <v>0</v>
-      </c>
-      <c r="AM30">
-        <v>0</v>
-      </c>
-      <c r="AN30">
-        <v>181.0576164167324</v>
-      </c>
-      <c r="AP30">
-        <v>83.57604663483671</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Union Bank of India (BSE:532477)</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>622.8</v>
-      </c>
-      <c r="L31">
-        <v>0.1710566068829135</v>
-      </c>
-      <c r="M31">
-        <v>-0</v>
-      </c>
-      <c r="N31">
-        <v>-0</v>
-      </c>
-      <c r="O31">
-        <v>-0</v>
-      </c>
-      <c r="P31">
-        <v>-0</v>
-      </c>
-      <c r="Q31">
-        <v>-0</v>
-      </c>
-      <c r="R31">
-        <v>-0</v>
-      </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="U31">
-        <v>5397.4</v>
-      </c>
-      <c r="V31">
-        <v>1.355790002511932</v>
-      </c>
-      <c r="W31">
-        <v>0.07318362886452567</v>
-      </c>
-      <c r="X31">
-        <v>0.09656017543386967</v>
-      </c>
-      <c r="Y31">
-        <v>-0.023376546569344</v>
-      </c>
-      <c r="Z31">
-        <v>0.5308517773306504</v>
-      </c>
-      <c r="AA31">
-        <v>0</v>
-      </c>
-      <c r="AB31">
-        <v>0.05872535679077544</v>
-      </c>
-      <c r="AC31">
-        <v>-0.05872535679077544</v>
-      </c>
-      <c r="AD31">
-        <v>7003.8</v>
-      </c>
-      <c r="AE31">
-        <v>0</v>
-      </c>
-      <c r="AF31">
-        <v>7003.8</v>
-      </c>
-      <c r="AG31">
-        <v>1606.400000000001</v>
-      </c>
-      <c r="AH31">
-        <v>0.6375901245357222</v>
-      </c>
-      <c r="AI31">
-        <v>0.4268371463744622</v>
-      </c>
-      <c r="AJ31">
-        <v>0.2875040269177078</v>
-      </c>
-      <c r="AK31">
-        <v>0.1458878233071782</v>
-      </c>
-      <c r="AL31">
-        <v>0</v>
-      </c>
-      <c r="AM31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>DCB Bank Limited (NSEI:DCBBANK)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D32">
-        <v>0.0924</v>
-      </c>
-      <c r="E32">
-        <v>0.0576</v>
-      </c>
-      <c r="F32">
-        <v>0.173</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
-      <c r="I32">
-        <v>-0.01876010644428614</v>
-      </c>
-      <c r="J32">
-        <v>-0.0139187886522123</v>
-      </c>
-      <c r="K32">
-        <v>36.8</v>
-      </c>
-      <c r="L32">
-        <v>0.2110091743119266</v>
-      </c>
-      <c r="M32">
-        <v>-0</v>
-      </c>
-      <c r="N32">
-        <v>-0</v>
-      </c>
-      <c r="O32">
-        <v>-0</v>
-      </c>
-      <c r="P32">
-        <v>-0</v>
-      </c>
-      <c r="Q32">
-        <v>-0</v>
-      </c>
-      <c r="R32">
-        <v>-0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>517.6</v>
-      </c>
-      <c r="V32">
-        <v>1.579493439121147</v>
-      </c>
-      <c r="W32">
-        <v>0.07550266721378744</v>
-      </c>
-      <c r="X32">
-        <v>0.09799370718873157</v>
-      </c>
-      <c r="Y32">
-        <v>-0.02249103997494413</v>
-      </c>
-      <c r="Z32">
-        <v>0.292269858016625</v>
-      </c>
-      <c r="AA32">
-        <v>-0.004068042383145499</v>
-      </c>
-      <c r="AB32">
-        <v>0.05588228268054036</v>
-      </c>
-      <c r="AC32">
-        <v>-0.05995032506368586</v>
-      </c>
-      <c r="AD32">
-        <v>545</v>
-      </c>
-      <c r="AE32">
-        <v>49.90881281941752</v>
-      </c>
-      <c r="AF32">
-        <v>594.9088128194176</v>
-      </c>
-      <c r="AG32">
-        <v>77.30881281941754</v>
-      </c>
-      <c r="AH32">
-        <v>0.64481154369361</v>
-      </c>
-      <c r="AI32">
-        <v>0.5335462876881913</v>
-      </c>
-      <c r="AJ32">
-        <v>0.1908818039816024</v>
-      </c>
-      <c r="AK32">
-        <v>0.1294068837963161</v>
-      </c>
-      <c r="AL32">
-        <v>0</v>
-      </c>
-      <c r="AM32">
-        <v>0</v>
-      </c>
-      <c r="AN32">
-        <v>81.2220566318927</v>
-      </c>
-      <c r="AP32">
-        <v>11.52143261094151</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/india/india_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/india/india_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ29"/>
+  <dimension ref="A1:AQ36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.156</v>
+        <v>0.228</v>
       </c>
       <c r="E2">
-        <v>0.201</v>
+        <v>0.2855</v>
       </c>
       <c r="F2">
-        <v>0.228</v>
+        <v>0.2865</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,34 +603,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0003525660625398181</v>
+        <v>0.0002259746156405529</v>
       </c>
       <c r="J2">
-        <v>0.000297508451947853</v>
+        <v>0.0001869039845261858</v>
       </c>
       <c r="K2">
-        <v>24404.76</v>
+        <v>35838.46</v>
       </c>
       <c r="L2">
-        <v>0.2680519172408339</v>
+        <v>0.2744385216746064</v>
       </c>
       <c r="M2">
-        <v>2355.161</v>
+        <v>4621.72</v>
       </c>
       <c r="N2">
-        <v>0.005642313741508659</v>
+        <v>0.008560145238644712</v>
       </c>
       <c r="O2">
-        <v>0.09650416558081293</v>
+        <v>0.1289597823120748</v>
       </c>
       <c r="P2">
-        <v>2355.161</v>
+        <v>4621.72</v>
       </c>
       <c r="Q2">
-        <v>0.005642313741508659</v>
+        <v>0.008560145238644712</v>
       </c>
       <c r="R2">
-        <v>0.09650416558081293</v>
+        <v>0.1289597823120748</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>126697.7</v>
+        <v>186213.7</v>
       </c>
       <c r="V2">
-        <v>0.3035326135782401</v>
+        <v>0.3448967738039982</v>
       </c>
       <c r="W2">
-        <v>0.1141267700606878</v>
+        <v>0.1550448724257819</v>
       </c>
       <c r="X2">
-        <v>0.1008590715102836</v>
+        <v>0.08243900930832021</v>
       </c>
       <c r="Y2">
-        <v>0.01326769855040418</v>
+        <v>0.07260586311746164</v>
       </c>
       <c r="Z2">
-        <v>0.4077628177862778</v>
+        <v>0.4187101230789579</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08407293767764612</v>
+        <v>0.07125765349997813</v>
       </c>
       <c r="AC2">
-        <v>-0.08401830274282189</v>
+        <v>-0.070836798543934</v>
       </c>
       <c r="AD2">
-        <v>217754.5</v>
+        <v>308944.3</v>
       </c>
       <c r="AE2">
-        <v>2760.643290463343</v>
+        <v>3236.946795501734</v>
       </c>
       <c r="AF2">
-        <v>220515.1432904633</v>
+        <v>312181.2467955017</v>
       </c>
       <c r="AG2">
-        <v>93817.44329046334</v>
+        <v>125967.5467955017</v>
       </c>
       <c r="AH2">
-        <v>0.3456753081017898</v>
+        <v>0.3663700748616175</v>
       </c>
       <c r="AI2">
-        <v>0.5223367642029446</v>
+        <v>0.5345370245344881</v>
       </c>
       <c r="AJ2">
-        <v>0.1835139188335785</v>
+        <v>0.1891748453704869</v>
       </c>
       <c r="AK2">
-        <v>0.3175164052212981</v>
+        <v>0.3166540943809941</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>372.7217798530711</v>
+        <v>456.4112223537041</v>
       </c>
       <c r="AP2">
-        <v>160.5836134017256</v>
+        <v>186.0950404646804</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Equitas Small Finance Bank Limited (NSEI:EQUITASBNK)</t>
+          <t>Utkarsh Small Finance Bank Limited (NSEI:UTKARSHBNK)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.229</v>
+        <v>0.419</v>
       </c>
       <c r="E3">
-        <v>0.412</v>
+        <v>0.8140000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,16 +731,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.00908403900894305</v>
+        <v>0.005011369538999921</v>
       </c>
       <c r="J3">
-        <v>0.008201373218574084</v>
+        <v>0.003781242567083622</v>
       </c>
       <c r="K3">
-        <v>54.2</v>
+        <v>54.1</v>
       </c>
       <c r="L3">
-        <v>0.1550786838340487</v>
+        <v>0.260597302504817</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,55 +764,49 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>155.4</v>
+        <v>197</v>
       </c>
       <c r="V3">
-        <v>0.1757322175732218</v>
-      </c>
-      <c r="W3">
-        <v>0.115985448320137</v>
+        <v>0.2799090650753055</v>
       </c>
       <c r="X3">
-        <v>0.09261182846420479</v>
-      </c>
-      <c r="Y3">
-        <v>0.02337361985593217</v>
+        <v>0.07756691922096055</v>
       </c>
       <c r="Z3">
-        <v>0.7800892792005749</v>
+        <v>6.348973645056518</v>
       </c>
       <c r="AA3">
-        <v>0.006397803322532357</v>
+        <v>0.02400700940397977</v>
       </c>
       <c r="AB3">
-        <v>0.08331257399036757</v>
+        <v>0.07124086602164983</v>
       </c>
       <c r="AC3">
-        <v>-0.07691477066783521</v>
+        <v>-0.04723385661767007</v>
       </c>
       <c r="AD3">
-        <v>287.5</v>
+        <v>229</v>
       </c>
       <c r="AE3">
-        <v>28.92564183187202</v>
+        <v>32.69819841851808</v>
       </c>
       <c r="AF3">
-        <v>316.425641831872</v>
+        <v>261.6981984185181</v>
       </c>
       <c r="AG3">
-        <v>161.025641831872</v>
+        <v>64.69819841851807</v>
       </c>
       <c r="AH3">
-        <v>0.2635286786656119</v>
+        <v>0.2710499085831321</v>
       </c>
       <c r="AI3">
-        <v>0.3656723278903502</v>
+        <v>0.4471958374543021</v>
       </c>
       <c r="AJ3">
-        <v>0.1540435203997139</v>
+        <v>0.08418783355856867</v>
       </c>
       <c r="AK3">
-        <v>0.2268204334983112</v>
+        <v>0.1666627992661797</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -821,10 +815,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>32.08705357142857</v>
+        <v>30.21108179419525</v>
       </c>
       <c r="AP3">
-        <v>17.97161181159286</v>
+        <v>8.535382377113203</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IndusInd Bank Limited (NSEI:INDUSINDBK)</t>
+          <t>Fino Payments Bank Limited (NSEI:FINOPB)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -843,9 +837,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="F4">
-        <v>0.189</v>
-      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -853,91 +844,88 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.007424675500465108</v>
+        <v>0.002870908171333285</v>
       </c>
       <c r="J4">
-        <v>0.006910332169010013</v>
+        <v>0.002870908171333285</v>
       </c>
       <c r="K4">
-        <v>747</v>
+        <v>9.56</v>
       </c>
       <c r="L4">
-        <v>0.3619887575111456</v>
+        <v>0.06195722618276085</v>
       </c>
       <c r="M4">
-        <v>81</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.007085684293399817</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.108433734939759</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>81</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.007085684293399817</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.108433734939759</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>7278</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="V4">
-        <v>0.6366618553995539</v>
+        <v>0.339292364990689</v>
       </c>
       <c r="W4">
-        <v>0.1222405864929879</v>
+        <v>0.1532051282051282</v>
       </c>
       <c r="X4">
-        <v>0.09547934727126572</v>
+        <v>0.0797078893639688</v>
       </c>
       <c r="Y4">
-        <v>0.02676123922172222</v>
+        <v>0.07349723884115941</v>
       </c>
       <c r="Z4">
-        <v>0.5925811575947199</v>
+        <v>2.139042048801992</v>
       </c>
       <c r="AA4">
-        <v>0.004094932636075984</v>
+        <v>0.006140993296731131</v>
       </c>
       <c r="AB4">
-        <v>0.08358346881475663</v>
+        <v>0.07094784489995209</v>
       </c>
       <c r="AC4">
-        <v>-0.07948853617868065</v>
+        <v>-0.06480685160322096</v>
       </c>
       <c r="AD4">
-        <v>4998.3</v>
+        <v>123.1</v>
       </c>
       <c r="AE4">
-        <v>180.392198186201</v>
+        <v>3.43509434581637</v>
       </c>
       <c r="AF4">
-        <v>5178.692198186201</v>
+        <v>126.5350943458164</v>
       </c>
       <c r="AG4">
-        <v>-2099.307801813799</v>
+        <v>35.43509434581637</v>
       </c>
       <c r="AH4">
-        <v>0.3117779816389905</v>
+        <v>0.3203135522816277</v>
       </c>
       <c r="AI4">
-        <v>0.4530079018588062</v>
+        <v>0.6395988273174255</v>
       </c>
       <c r="AJ4">
-        <v>-0.2249533397117366</v>
+        <v>0.1165877024569543</v>
       </c>
       <c r="AK4">
-        <v>-0.5053954799978881</v>
+        <v>0.3319910340923898</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -946,10 +934,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>97.24319066147861</v>
+        <v>108.9380530973451</v>
       </c>
       <c r="AP4">
-        <v>-40.84256423762254</v>
+        <v>31.35849057151891</v>
       </c>
     </row>
     <row r="5">
@@ -960,7 +948,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RBL Bank Limited (NSEI:RBLBANK)</t>
+          <t>Equitas Small Finance Bank Limited (NSEI:EQUITASBNK)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -968,8 +956,14 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.245</v>
+      </c>
+      <c r="E5">
+        <v>0.547</v>
+      </c>
       <c r="F5">
-        <v>0.3</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -978,88 +972,91 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.009050130287362531</v>
+        <v>0.009077646359215666</v>
       </c>
       <c r="J5">
-        <v>0.006596923815027944</v>
+        <v>0.008360697554926593</v>
       </c>
       <c r="K5">
-        <v>83.90000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="L5">
-        <v>0.1231650029359953</v>
+        <v>0.2077383694150161</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>13.4</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.009161766716805689</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.1485587583148559</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>13.4</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.009161766716805689</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.1485587583148559</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>642.5</v>
+        <v>159.3</v>
       </c>
       <c r="V5">
-        <v>0.4943828870421669</v>
+        <v>0.1089156297005333</v>
       </c>
       <c r="W5">
-        <v>0.05087623552240617</v>
+        <v>0.1643286573146293</v>
       </c>
       <c r="X5">
-        <v>0.1146998849830565</v>
+        <v>0.07436188096311902</v>
       </c>
       <c r="Y5">
-        <v>-0.06382364946065033</v>
+        <v>0.08996677635151026</v>
       </c>
       <c r="Z5">
-        <v>0.6937603534288134</v>
+        <v>0.6128073376645392</v>
       </c>
       <c r="AA5">
-        <v>0.004576684197456743</v>
+        <v>0.005123496809652987</v>
       </c>
       <c r="AB5">
-        <v>0.08476251888702729</v>
+        <v>0.07035018296351489</v>
       </c>
       <c r="AC5">
-        <v>-0.08018583468957055</v>
+        <v>-0.0652266861538619</v>
       </c>
       <c r="AD5">
-        <v>1324.8</v>
+        <v>298.6</v>
       </c>
       <c r="AE5">
-        <v>93.17525624124322</v>
+        <v>27.54242975414279</v>
       </c>
       <c r="AF5">
-        <v>1417.975256241243</v>
+        <v>326.1424297541428</v>
       </c>
       <c r="AG5">
-        <v>775.4752562412432</v>
+        <v>166.8424297541428</v>
       </c>
       <c r="AH5">
-        <v>0.5217795727955242</v>
+        <v>0.1823305716513753</v>
       </c>
       <c r="AI5">
-        <v>0.4706854221495649</v>
+        <v>0.3309268276105612</v>
       </c>
       <c r="AJ5">
-        <v>0.373709461335839</v>
+        <v>0.1023923439745685</v>
       </c>
       <c r="AK5">
-        <v>0.3271943598411669</v>
+        <v>0.201929147845613</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1068,10 +1065,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>53.41935483870967</v>
+        <v>31.5978835978836</v>
       </c>
       <c r="AP5">
-        <v>31.26916355811464</v>
+        <v>17.65528357186697</v>
       </c>
     </row>
     <row r="6">
@@ -1082,7 +1079,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Federal Bank Limited (NSEI:FEDERALBNK)</t>
+          <t>IndusInd Bank Limited (NSEI:INDUSINDBK)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1091,7 +1088,7 @@
         </is>
       </c>
       <c r="F6">
-        <v>0.228</v>
+        <v>0.198</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1100,34 +1097,34 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.0003669552211611642</v>
+        <v>0.004122968091375413</v>
       </c>
       <c r="J6">
-        <v>0.000274203457387111</v>
+        <v>0.003093922636278273</v>
       </c>
       <c r="K6">
-        <v>306.6</v>
+        <v>1003.1</v>
       </c>
       <c r="L6">
-        <v>0.3018905080740449</v>
+        <v>0.35089376289922</v>
       </c>
       <c r="M6">
-        <v>46.5</v>
+        <v>130.8</v>
       </c>
       <c r="N6">
-        <v>0.01309564041906049</v>
+        <v>0.00875554752294315</v>
       </c>
       <c r="O6">
-        <v>0.1516634050880626</v>
+        <v>0.1303957731033795</v>
       </c>
       <c r="P6">
-        <v>46.5</v>
+        <v>130.8</v>
       </c>
       <c r="Q6">
-        <v>0.01309564041906049</v>
+        <v>0.00875554752294315</v>
       </c>
       <c r="R6">
-        <v>0.1516634050880626</v>
+        <v>0.1303957731033795</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1136,55 +1133,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>1856.5</v>
+        <v>4859.7</v>
       </c>
       <c r="V6">
-        <v>0.5228399233975441</v>
+        <v>0.3253007209269634</v>
       </c>
       <c r="W6">
-        <v>0.1255014326647565</v>
+        <v>0.1604164334490093</v>
       </c>
       <c r="X6">
-        <v>0.1084238894760745</v>
+        <v>0.07687647864231553</v>
       </c>
       <c r="Y6">
-        <v>0.01707754318868202</v>
+        <v>0.08353995480669377</v>
       </c>
       <c r="Z6">
-        <v>0.7556341835869487</v>
+        <v>0.6853804096047659</v>
       </c>
       <c r="AA6">
-        <v>0.0002071975056594283</v>
+        <v>0.00212051396373786</v>
       </c>
       <c r="AB6">
-        <v>0.0819382474033669</v>
+        <v>0.06962713534420421</v>
       </c>
       <c r="AC6">
-        <v>-0.08173104989770748</v>
+        <v>-0.06750662138046636</v>
       </c>
       <c r="AD6">
-        <v>3133.4</v>
+        <v>4878.3</v>
       </c>
       <c r="AE6">
-        <v>1.036601386943608</v>
+        <v>197.5683555859255</v>
       </c>
       <c r="AF6">
-        <v>3134.436601386943</v>
+        <v>5075.868355585926</v>
       </c>
       <c r="AG6">
-        <v>1277.936601386943</v>
+        <v>216.1683555859263</v>
       </c>
       <c r="AH6">
-        <v>0.4688594866988944</v>
+        <v>0.2536036163239456</v>
       </c>
       <c r="AI6">
-        <v>0.5531680911119418</v>
+        <v>0.4193453256712946</v>
       </c>
       <c r="AJ6">
-        <v>0.2646523732563681</v>
+        <v>0.01426357821676256</v>
       </c>
       <c r="AK6">
-        <v>0.3354308163561975</v>
+        <v>0.0298386798185498</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1193,10 +1190,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>5402.413793103448</v>
+        <v>95.09356725146199</v>
       </c>
       <c r="AP6">
-        <v>2203.338967908524</v>
+        <v>4.213808101090182</v>
       </c>
     </row>
     <row r="7">
@@ -1207,7 +1204,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>City Union Bank Limited (NSEI:CUB)</t>
+          <t>IDFC First Bank Limited (BSE:539437)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1215,14 +1212,8 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.0931</v>
-      </c>
-      <c r="E7">
-        <v>0.109</v>
-      </c>
       <c r="F7">
-        <v>0.21</v>
+        <v>0.32</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1231,97 +1222,100 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>0.006135715787492632</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>0.005848547592812704</v>
       </c>
       <c r="K7">
-        <v>111.4</v>
+        <v>350.4</v>
       </c>
       <c r="L7">
-        <v>0.3965824136703454</v>
+        <v>0.1700475589634087</v>
       </c>
       <c r="M7">
-        <v>8.4</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.005206719147089816</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.07540394973070018</v>
+        <v>-0</v>
       </c>
       <c r="P7">
-        <v>8.4</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.005206719147089816</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.07540394973070018</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>670.2</v>
+        <v>1570.7</v>
       </c>
       <c r="V7">
-        <v>0.415421806235666</v>
+        <v>0.2106625536480687</v>
       </c>
       <c r="W7">
-        <v>0.1339264246213032</v>
+        <v>0.1287146897843735</v>
       </c>
       <c r="X7">
-        <v>0.09421982108182313</v>
+        <v>0.08859290896648742</v>
       </c>
       <c r="Y7">
-        <v>0.03970660353948009</v>
+        <v>0.04012178081788609</v>
       </c>
       <c r="Z7">
-        <v>1.027432333577177</v>
+        <v>0.2565429367367675</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>0.001500403575104924</v>
       </c>
       <c r="AB7">
-        <v>0.08189840801607781</v>
+        <v>0.06968383766613481</v>
       </c>
       <c r="AC7">
-        <v>-0.08189840801607781</v>
+        <v>-0.06818343409102989</v>
       </c>
       <c r="AD7">
-        <v>663.4</v>
+        <v>6399.1</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>191.2837202414634</v>
       </c>
       <c r="AF7">
-        <v>663.4</v>
+        <v>6590.383720241463</v>
       </c>
       <c r="AG7">
-        <v>-6.800000000000068</v>
+        <v>5019.683720241464</v>
       </c>
       <c r="AH7">
-        <v>0.2913866561250933</v>
+        <v>0.4691872193940158</v>
       </c>
       <c r="AI7">
-        <v>0.4349308332786992</v>
+        <v>0.6635449222815494</v>
       </c>
       <c r="AJ7">
-        <v>-0.004232804232804276</v>
+        <v>0.4023574044360519</v>
       </c>
       <c r="AK7">
-        <v>-0.007952286282306244</v>
+        <v>0.6003412698414591</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
         <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>125.7190569744597</v>
+      </c>
+      <c r="AP7">
+        <v>98.61854067272031</v>
       </c>
     </row>
     <row r="8">
@@ -1341,13 +1335,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.162</v>
+        <v>0.183</v>
       </c>
       <c r="E8">
-        <v>0.201</v>
+        <v>0.206</v>
       </c>
       <c r="F8">
-        <v>0.17</v>
+        <v>0.09849999999999999</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1356,34 +1350,34 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.003031515965542103</v>
+        <v>0.005109486296342993</v>
       </c>
       <c r="J8">
-        <v>0.002287401724764371</v>
+        <v>0.003841686877377712</v>
       </c>
       <c r="K8">
-        <v>1678.4</v>
+        <v>2066.9</v>
       </c>
       <c r="L8">
-        <v>0.2816958141720654</v>
+        <v>0.2783966165160352</v>
       </c>
       <c r="M8">
-        <v>4.91</v>
+        <v>9.59</v>
       </c>
       <c r="N8">
-        <v>0.000112021427805498</v>
+        <v>0.0002101604582769034</v>
       </c>
       <c r="O8">
-        <v>0.002925405147759771</v>
+        <v>0.00463979873240118</v>
       </c>
       <c r="P8">
-        <v>4.91</v>
+        <v>9.59</v>
       </c>
       <c r="Q8">
-        <v>0.000112021427805498</v>
+        <v>0.0002101604582769034</v>
       </c>
       <c r="R8">
-        <v>0.002925405147759771</v>
+        <v>0.00463979873240118</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1392,55 +1386,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>5061.4</v>
+        <v>6076.2</v>
       </c>
       <c r="V8">
-        <v>0.1154756119541237</v>
+        <v>0.1331571404152367</v>
       </c>
       <c r="W8">
-        <v>0.1388748686464168</v>
+        <v>0.1623058439212853</v>
       </c>
       <c r="X8">
-        <v>0.08599955389115931</v>
+        <v>0.07321579170788774</v>
       </c>
       <c r="Y8">
-        <v>0.05287531475525754</v>
+        <v>0.08909005221339759</v>
       </c>
       <c r="Z8">
-        <v>0.4223011731644723</v>
+        <v>0.5419225480019874</v>
       </c>
       <c r="AA8">
-        <v>0.0009659724318664311</v>
+        <v>0.002081896741214328</v>
       </c>
       <c r="AB8">
-        <v>0.08301705496130242</v>
+        <v>0.07059710685191484</v>
       </c>
       <c r="AC8">
-        <v>-0.08205108252943599</v>
+        <v>-0.06851521011070051</v>
       </c>
       <c r="AD8">
-        <v>5785.4</v>
+        <v>7405.2</v>
       </c>
       <c r="AE8">
-        <v>277.1881078705352</v>
+        <v>341.3282044503036</v>
       </c>
       <c r="AF8">
-        <v>6062.588107870535</v>
+        <v>7746.528204450304</v>
       </c>
       <c r="AG8">
-        <v>1001.188107870536</v>
+        <v>1670.328204450304</v>
       </c>
       <c r="AH8">
-        <v>0.121510608654242</v>
+        <v>0.1451249685973577</v>
       </c>
       <c r="AI8">
-        <v>0.3225263306979452</v>
+        <v>0.3475629776260684</v>
       </c>
       <c r="AJ8">
-        <v>0.0223319535209151</v>
+        <v>0.0353119038794782</v>
       </c>
       <c r="AK8">
-        <v>0.07288901808967627</v>
+        <v>0.1030308167779688</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1449,10 +1443,10 @@
         <v>0</v>
       </c>
       <c r="AN8">
-        <v>78.71292517006802</v>
+        <v>69.72881355932203</v>
       </c>
       <c r="AP8">
-        <v>13.62160690980321</v>
+        <v>15.72813751836444</v>
       </c>
     </row>
     <row r="9">
@@ -1463,7 +1457,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tamilnad Mercantile Bank Limited (NSEI:TMB)</t>
+          <t>RBL Bank Limited (NSEI:RBLBANK)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1471,6 +1465,9 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="F9">
+        <v>0.307</v>
+      </c>
       <c r="G9">
         <v>0</v>
       </c>
@@ -1478,34 +1475,34 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>0.007568168747857233</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>0.007258865449404412</v>
       </c>
       <c r="K9">
-        <v>113.8</v>
+        <v>141.3</v>
       </c>
       <c r="L9">
-        <v>0.389592605272167</v>
+        <v>0.1755933888405617</v>
       </c>
       <c r="M9">
-        <v>17.5</v>
+        <v>10.8</v>
       </c>
       <c r="N9">
-        <v>0.01911106257507917</v>
+        <v>0.00526700804681785</v>
       </c>
       <c r="O9">
-        <v>0.1537785588752197</v>
+        <v>0.07643312101910828</v>
       </c>
       <c r="P9">
-        <v>17.5</v>
+        <v>10.8</v>
       </c>
       <c r="Q9">
-        <v>0.01911106257507917</v>
+        <v>0.00526700804681785</v>
       </c>
       <c r="R9">
-        <v>0.1537785588752197</v>
+        <v>0.07643312101910828</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1514,61 +1511,67 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>370.5</v>
+        <v>967.2</v>
       </c>
       <c r="V9">
-        <v>0.4046084962323905</v>
+        <v>0.4716898317483541</v>
       </c>
       <c r="W9">
-        <v>0.1817891373801917</v>
+        <v>0.08861156402859653</v>
       </c>
       <c r="X9">
-        <v>0.08296133851278328</v>
+        <v>0.08978903139587673</v>
       </c>
       <c r="Y9">
-        <v>0.09882779886740842</v>
+        <v>-0.001177467367280194</v>
       </c>
       <c r="Z9">
-        <v>0.6485346358792186</v>
+        <v>0.3414883320035088</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>0.002478817854555013</v>
       </c>
       <c r="AB9">
-        <v>0.08213174940561048</v>
+        <v>0.07165853219990875</v>
       </c>
       <c r="AC9">
-        <v>-0.08213174940561048</v>
+        <v>-0.06917971434535373</v>
       </c>
       <c r="AD9">
-        <v>34.3</v>
+        <v>1841.8</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>84.54947304299642</v>
       </c>
       <c r="AF9">
-        <v>34.3</v>
+        <v>1926.349473042996</v>
       </c>
       <c r="AG9">
-        <v>-336.2</v>
+        <v>959.1494730429963</v>
       </c>
       <c r="AH9">
-        <v>0.03610526315789473</v>
+        <v>0.4843908440841732</v>
       </c>
       <c r="AI9">
-        <v>0.04141011710732826</v>
+        <v>0.5309454550744657</v>
       </c>
       <c r="AJ9">
-        <v>-0.5801553062985332</v>
+        <v>0.3186914229161775</v>
       </c>
       <c r="AK9">
-        <v>-0.7343818261249454</v>
+        <v>0.3604538465535524</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
         <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>80.07826086956521</v>
+      </c>
+      <c r="AP9">
+        <v>41.7021510018694</v>
       </c>
     </row>
     <row r="10">
@@ -1579,7 +1582,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Indian Overseas Bank (NSEI:IOB)</t>
+          <t>The Federal Bank Limited (NSEI:FEDERALBNK)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1587,8 +1590,8 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D10">
-        <v>0.325</v>
+      <c r="F10">
+        <v>0.181</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1597,94 +1600,103 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>0.0003258512981200857</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>0.0002431799069317592</v>
       </c>
       <c r="K10">
-        <v>233</v>
+        <v>441.9</v>
       </c>
       <c r="L10">
-        <v>0.2490114352890884</v>
+        <v>0.3399492268636048</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>28.3</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.006183494657722814</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>0.06404163837972393</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>28.3</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.006183494657722814</v>
       </c>
       <c r="R10">
-        <v>-0</v>
+        <v>0.06404163837972393</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
       <c r="U10">
-        <v>1948.3</v>
+        <v>2517.8</v>
       </c>
       <c r="V10">
-        <v>0.2657400840198592</v>
+        <v>0.5501343762973322</v>
       </c>
       <c r="W10">
-        <v>0.08018445866886915</v>
+        <v>0.1773701533274464</v>
       </c>
       <c r="X10">
-        <v>0.08757978864303957</v>
+        <v>0.08448979518304568</v>
       </c>
       <c r="Y10">
-        <v>-0.007395329974170417</v>
+        <v>0.09288035814440072</v>
       </c>
       <c r="Z10">
-        <v>0.4987208186760473</v>
+        <v>0.344906991415063</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>8.38744500724281e-05</v>
       </c>
       <c r="AB10">
-        <v>0.08273250515421895</v>
+        <v>0.06966812667624112</v>
       </c>
       <c r="AC10">
-        <v>-0.08273250515421895</v>
+        <v>-0.06958425222616869</v>
       </c>
       <c r="AD10">
-        <v>1398.7</v>
+        <v>3172.7</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>0.5421294878685032</v>
       </c>
       <c r="AF10">
-        <v>1398.7</v>
+        <v>3173.242129487868</v>
       </c>
       <c r="AG10">
-        <v>-549.5999999999999</v>
+        <v>655.442129487868</v>
       </c>
       <c r="AH10">
-        <v>0.1602121347490922</v>
+        <v>0.4094536548103956</v>
       </c>
       <c r="AI10">
-        <v>0.32254865787289</v>
+        <v>0.4923005087297824</v>
       </c>
       <c r="AJ10">
-        <v>-0.08103804187555293</v>
+        <v>0.1252722332969238</v>
       </c>
       <c r="AK10">
-        <v>-0.2301411163686612</v>
+        <v>0.1668665443330566</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
         <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>5963.721804511278</v>
+      </c>
+      <c r="AP10">
+        <v>1232.034077984714</v>
       </c>
     </row>
     <row r="11">
@@ -1695,7 +1707,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Karur Vysya Bank Limited (NSEI:KARURVYSYA)</t>
+          <t>City Union Bank Limited (NSEI:CUB)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1704,10 +1716,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0806</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="E11">
-        <v>0.0953</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1722,28 +1734,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>107.9</v>
+        <v>113.6</v>
       </c>
       <c r="L11">
-        <v>0.2798236514522822</v>
+        <v>0.4047025293908087</v>
       </c>
       <c r="M11">
-        <v>15.7</v>
+        <v>9.67</v>
       </c>
       <c r="N11">
-        <v>0.01432743201314108</v>
+        <v>0.006950334219794437</v>
       </c>
       <c r="O11">
-        <v>0.1455050973123262</v>
+        <v>0.08512323943661972</v>
       </c>
       <c r="P11">
-        <v>15.7</v>
+        <v>9.67</v>
       </c>
       <c r="Q11">
-        <v>0.01432743201314108</v>
+        <v>0.006950334219794437</v>
       </c>
       <c r="R11">
-        <v>0.1455050973123262</v>
+        <v>0.08512323943661972</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1752,55 +1764,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>730.1</v>
+        <v>737.6</v>
       </c>
       <c r="V11">
-        <v>0.6662712173754335</v>
+        <v>0.5301516567239273</v>
       </c>
       <c r="W11">
-        <v>0.1112485823280751</v>
+        <v>0.1318018331592992</v>
       </c>
       <c r="X11">
-        <v>0.0895383304834198</v>
+        <v>0.0779687564532564</v>
       </c>
       <c r="Y11">
-        <v>0.02171025184465526</v>
+        <v>0.05383307670604282</v>
       </c>
       <c r="Z11">
-        <v>1.298316498316498</v>
+        <v>0.3282656999181383</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.08297661976851696</v>
+        <v>0.06963429722142042</v>
       </c>
       <c r="AC11">
-        <v>-0.08297661976851696</v>
+        <v>-0.06963429722142042</v>
       </c>
       <c r="AD11">
-        <v>280.3</v>
+        <v>543.3</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>280.3</v>
+        <v>543.3</v>
       </c>
       <c r="AG11">
-        <v>-449.8</v>
+        <v>-194.3000000000001</v>
       </c>
       <c r="AH11">
-        <v>0.2036915921808008</v>
+        <v>0.2808332471828802</v>
       </c>
       <c r="AI11">
-        <v>0.2229735104605839</v>
+        <v>0.3638738195700221</v>
       </c>
       <c r="AJ11">
-        <v>-0.6962848297213623</v>
+        <v>-0.1623224728487887</v>
       </c>
       <c r="AK11">
-        <v>-0.8535104364326376</v>
+        <v>-0.2571806750496362</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1817,7 +1829,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IDBI Bank Limited (NSEI:IDBI)</t>
+          <t>Tamilnad Mercantile Bank Limited (NSEI:TMB)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1832,34 +1844,34 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>7.534943412478363e-05</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>6.806736668350376e-05</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>355.3</v>
+        <v>128.5</v>
       </c>
       <c r="L12">
-        <v>0.2879954608089487</v>
+        <v>0.4069031032298923</v>
       </c>
       <c r="M12">
-        <v>1.43</v>
+        <v>19.1</v>
       </c>
       <c r="N12">
-        <v>0.0002025151532317453</v>
+        <v>0.01992696922274387</v>
       </c>
       <c r="O12">
-        <v>0.004024767801857585</v>
+        <v>0.1486381322957198</v>
       </c>
       <c r="P12">
-        <v>1.43</v>
+        <v>19.1</v>
       </c>
       <c r="Q12">
-        <v>0.0002025151532317453</v>
+        <v>0.01992696922274387</v>
       </c>
       <c r="R12">
-        <v>0.004024767801857585</v>
+        <v>0.1486381322957198</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1868,67 +1880,61 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>1596.3</v>
+        <v>397.5</v>
       </c>
       <c r="V12">
-        <v>0.2260663909817028</v>
+        <v>0.4147104851330203</v>
       </c>
       <c r="W12">
-        <v>0.06787788476234144</v>
+        <v>0.1618387909319899</v>
       </c>
       <c r="X12">
-        <v>0.09320522251068189</v>
+        <v>0.07131716350191486</v>
       </c>
       <c r="Y12">
-        <v>-0.02532733774834045</v>
+        <v>0.09052162743007505</v>
       </c>
       <c r="Z12">
-        <v>0.4326828338247746</v>
+        <v>0.689820882481433</v>
       </c>
       <c r="AA12">
-        <v>2.945158110760845e-05</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.08337170421581624</v>
+        <v>0.07002808807519123</v>
       </c>
       <c r="AC12">
-        <v>-0.08334225263470864</v>
+        <v>-0.07002808807519123</v>
       </c>
       <c r="AD12">
-        <v>2665.6</v>
+        <v>78.2</v>
       </c>
       <c r="AE12">
-        <v>0.1802070156012722</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>2665.780207015601</v>
+        <v>78.2</v>
       </c>
       <c r="AG12">
-        <v>1069.480207015601</v>
+        <v>-319.3</v>
       </c>
       <c r="AH12">
-        <v>0.2740604124076353</v>
+        <v>0.07543165814604032</v>
       </c>
       <c r="AI12">
-        <v>0.3287969109473377</v>
+        <v>0.08087702968249043</v>
       </c>
       <c r="AJ12">
-        <v>0.1315363757749068</v>
+        <v>-0.4995306633291615</v>
       </c>
       <c r="AK12">
-        <v>0.1642478511488707</v>
+        <v>-0.5607657182999648</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
         <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>20663.56589147287</v>
-      </c>
-      <c r="AP12">
-        <v>8290.544240431018</v>
       </c>
     </row>
     <row r="13">
@@ -1939,7 +1945,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Punjab &amp; Sind Bank (BSE:533295)</t>
+          <t>The Karur Vysya Bank Limited (NSEI:KARURVYSYA)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1948,10 +1954,13 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.151</v>
+        <v>0.166</v>
       </c>
       <c r="E13">
-        <v>0.5529999999999999</v>
+        <v>0.402</v>
+      </c>
+      <c r="F13">
+        <v>0.19</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1966,28 +1975,28 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>138.8</v>
+        <v>164.2</v>
       </c>
       <c r="L13">
-        <v>0.3279773156899811</v>
+        <v>0.3375822368421053</v>
       </c>
       <c r="M13">
-        <v>25.8</v>
+        <v>19.3</v>
       </c>
       <c r="N13">
-        <v>0.009292943846126139</v>
+        <v>0.01171898718805028</v>
       </c>
       <c r="O13">
-        <v>0.185878962536023</v>
+        <v>0.1175395858708892</v>
       </c>
       <c r="P13">
-        <v>25.8</v>
+        <v>19.3</v>
       </c>
       <c r="Q13">
-        <v>0.009292943846126139</v>
+        <v>0.01171898718805028</v>
       </c>
       <c r="R13">
-        <v>0.185878962536023</v>
+        <v>0.1175395858708892</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -1996,55 +2005,55 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>679.6</v>
+        <v>588.6</v>
       </c>
       <c r="V13">
-        <v>0.2447862262723769</v>
+        <v>0.3573987491650981</v>
       </c>
       <c r="W13">
-        <v>0.1175872585564215</v>
+        <v>0.1680999180999181</v>
       </c>
       <c r="X13">
-        <v>0.09301618226403355</v>
+        <v>0.07363312264092714</v>
       </c>
       <c r="Y13">
-        <v>0.024571076292388</v>
+        <v>0.09446679545899095</v>
       </c>
       <c r="Z13">
-        <v>1.913200723327305</v>
+        <v>0.9229601518026567</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.0833530512324963</v>
+        <v>0.07024938153042314</v>
       </c>
       <c r="AC13">
-        <v>-0.0833530512324963</v>
+        <v>-0.07024938153042314</v>
       </c>
       <c r="AD13">
-        <v>1030.7</v>
+        <v>311.5</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>1030.7</v>
+        <v>311.5</v>
       </c>
       <c r="AG13">
-        <v>351.1</v>
+        <v>-277.1</v>
       </c>
       <c r="AH13">
-        <v>0.2707381140005254</v>
+        <v>0.1590584150326797</v>
       </c>
       <c r="AI13">
-        <v>0.369956927494616</v>
+        <v>0.2202347285067873</v>
       </c>
       <c r="AJ13">
-        <v>0.1122657798810514</v>
+        <v>-0.2022923054460505</v>
       </c>
       <c r="AK13">
-        <v>0.1666824914546145</v>
+        <v>-0.3355534027609591</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2061,7 +2070,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UCO Bank (NSEI:UCOBANK)</t>
+          <t>Bank of Maharashtra (NSEI:MAHABANK)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2082,82 +2091,85 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>154.3</v>
+        <v>411.7</v>
       </c>
       <c r="L14">
-        <v>0.1967861242188496</v>
+        <v>0.4518217734855136</v>
       </c>
       <c r="M14">
-        <v>-0</v>
+        <v>105.3</v>
       </c>
       <c r="N14">
-        <v>-0</v>
+        <v>0.02711331977238201</v>
       </c>
       <c r="O14">
-        <v>-0</v>
+        <v>0.2557687636628613</v>
       </c>
       <c r="P14">
-        <v>-0</v>
+        <v>105.3</v>
       </c>
       <c r="Q14">
-        <v>-0</v>
+        <v>0.02711331977238201</v>
       </c>
       <c r="R14">
-        <v>-0</v>
+        <v>0.2557687636628613</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
       <c r="U14">
-        <v>3650</v>
+        <v>1777</v>
       </c>
       <c r="V14">
-        <v>0.8020920318199797</v>
+        <v>0.4575533640600459</v>
       </c>
       <c r="W14">
-        <v>0.04989006725297465</v>
+        <v>0.2226127392667892</v>
       </c>
       <c r="X14">
-        <v>0.09775641642416028</v>
+        <v>0.07533535055023571</v>
       </c>
       <c r="Y14">
-        <v>-0.04786634917118562</v>
+        <v>0.1472773887165535</v>
       </c>
       <c r="Z14">
-        <v>0.4431946642550305</v>
+        <v>0.3162241887905605</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.08377454988215931</v>
+        <v>0.07047643916660186</v>
       </c>
       <c r="AC14">
-        <v>-0.08377454988215931</v>
+        <v>-0.07047643916660186</v>
       </c>
       <c r="AD14">
-        <v>2405.5</v>
+        <v>1041.6</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>2405.5</v>
+        <v>1041.6</v>
       </c>
       <c r="AG14">
-        <v>-1244.5</v>
+        <v>-735.4000000000001</v>
       </c>
       <c r="AH14">
-        <v>0.3458115898276333</v>
+        <v>0.2114795037865714</v>
       </c>
       <c r="AI14">
-        <v>0.4469029836881804</v>
+        <v>0.3175997072813758</v>
       </c>
       <c r="AJ14">
-        <v>-0.3764253954810804</v>
+        <v>-0.2335863799510847</v>
       </c>
       <c r="AK14">
-        <v>-0.7182846588941476</v>
+        <v>-0.4894183415413285</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2174,7 +2186,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ICICI Bank Limited (NSEI:ICICIBANK)</t>
+          <t>Punjab &amp; Sind Bank (BSE:533295)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2183,13 +2195,7 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.106</v>
-      </c>
-      <c r="E15">
-        <v>0.259</v>
-      </c>
-      <c r="F15">
-        <v>0.192</v>
+        <v>0.772</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2198,34 +2204,34 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0.0002677723818507505</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>0.0002546118737911289</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>3643.3</v>
+        <v>141.1</v>
       </c>
       <c r="L15">
-        <v>0.2731682811984524</v>
+        <v>0.2929209051276728</v>
       </c>
       <c r="M15">
-        <v>427.6</v>
+        <v>39.2</v>
       </c>
       <c r="N15">
-        <v>0.005693908476679743</v>
+        <v>0.01098839490945787</v>
       </c>
       <c r="O15">
-        <v>0.1173661241182444</v>
+        <v>0.2778171509567683</v>
       </c>
       <c r="P15">
-        <v>427.6</v>
+        <v>39.2</v>
       </c>
       <c r="Q15">
-        <v>0.005693908476679743</v>
+        <v>0.01098839490945787</v>
       </c>
       <c r="R15">
-        <v>0.1173661241182444</v>
+        <v>0.2778171509567683</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2234,67 +2240,61 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>17025.7</v>
+        <v>809.7</v>
       </c>
       <c r="V15">
-        <v>0.2267136986702673</v>
+        <v>0.2269720244435724</v>
       </c>
       <c r="W15">
-        <v>0.1602753887776873</v>
+        <v>0.08038511935281718</v>
       </c>
       <c r="X15">
-        <v>0.09082407997444419</v>
+        <v>0.07534036622825521</v>
       </c>
       <c r="Y15">
-        <v>0.06945130880324316</v>
+        <v>0.005044753124561971</v>
       </c>
       <c r="Z15">
-        <v>0.7423105473328093</v>
+        <v>0.2361158766727121</v>
       </c>
       <c r="AA15">
-        <v>0.0001890010793913251</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.08407293767764612</v>
+        <v>0.07047706638017784</v>
       </c>
       <c r="AC15">
-        <v>-0.0838839365982548</v>
+        <v>-0.07047706638017784</v>
       </c>
       <c r="AD15">
-        <v>22388</v>
+        <v>957.6</v>
       </c>
       <c r="AE15">
-        <v>27.04333094390086</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>22415.0433309439</v>
+        <v>957.6</v>
       </c>
       <c r="AG15">
-        <v>5389.343330943899</v>
+        <v>147.9</v>
       </c>
       <c r="AH15">
-        <v>0.2298676006694894</v>
+        <v>0.2116243093922652</v>
       </c>
       <c r="AI15">
-        <v>0.4751643463157951</v>
+        <v>0.3447332421340629</v>
       </c>
       <c r="AJ15">
-        <v>0.06695905840246071</v>
+        <v>0.03980836002476246</v>
       </c>
       <c r="AK15">
-        <v>0.1787655886843753</v>
+        <v>0.07514862049692596</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
         <v>0</v>
-      </c>
-      <c r="AN15">
-        <v>2493.095768374165</v>
-      </c>
-      <c r="AP15">
-        <v>600.1495914191423</v>
       </c>
     </row>
     <row r="16">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fino Payments Bank Limited (NSEI:FINOPB)</t>
+          <t>The Jammu and Kashmir Bank Limited (NSEI:J&amp;KBANK)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2326,82 +2326,85 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>6.84</v>
+        <v>179.9</v>
       </c>
       <c r="L16">
-        <v>0.04949348769898698</v>
+        <v>0.274028941355674</v>
       </c>
       <c r="M16">
-        <v>-0</v>
+        <v>6.21</v>
       </c>
       <c r="N16">
-        <v>-0</v>
+        <v>0.003762724188075618</v>
       </c>
       <c r="O16">
-        <v>-0</v>
+        <v>0.03451917732073374</v>
       </c>
       <c r="P16">
-        <v>-0</v>
+        <v>6.21</v>
       </c>
       <c r="Q16">
-        <v>-0</v>
+        <v>0.003762724188075618</v>
       </c>
       <c r="R16">
-        <v>-0</v>
+        <v>0.03451917732073374</v>
       </c>
       <c r="S16">
         <v>0</v>
       </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
       <c r="U16">
-        <v>85</v>
+        <v>898.5</v>
       </c>
       <c r="V16">
-        <v>0.3341194968553459</v>
+        <v>0.5444134755210858</v>
       </c>
       <c r="W16">
-        <v>0.3123287671232877</v>
+        <v>0.1726818967172202</v>
       </c>
       <c r="X16">
-        <v>0.09264368434427811</v>
+        <v>0.07550060372468713</v>
       </c>
       <c r="Y16">
-        <v>0.2196850827790096</v>
+        <v>0.09718129299253307</v>
       </c>
       <c r="Z16">
-        <v>5.595141700404858</v>
+        <v>0.9645900675874232</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.08401830274282189</v>
+        <v>0.0704969836443174</v>
       </c>
       <c r="AC16">
-        <v>-0.08401830274282189</v>
+        <v>-0.0704969836443174</v>
       </c>
       <c r="AD16">
-        <v>91.3</v>
+        <v>455.3</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>91.3</v>
+        <v>455.3</v>
       </c>
       <c r="AG16">
-        <v>6.299999999999997</v>
+        <v>-443.2</v>
       </c>
       <c r="AH16">
-        <v>0.2641018223893549</v>
+        <v>0.2162226338034857</v>
       </c>
       <c r="AI16">
-        <v>0.594014313597918</v>
+        <v>0.2627994227994228</v>
       </c>
       <c r="AJ16">
-        <v>0.0241657077100115</v>
+        <v>-0.3671305500331345</v>
       </c>
       <c r="AK16">
-        <v>0.09170305676855893</v>
+        <v>-0.5314148681055155</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2418,7 +2421,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IDFC First Bank Limited (BSE:539437)</t>
+          <t>IDBI Bank Limited (NSEI:IDBI)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2426,9 +2429,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="F17">
-        <v>1.643</v>
-      </c>
       <c r="G17">
         <v>0</v>
       </c>
@@ -2436,88 +2436,91 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0.006030550313973731</v>
+        <v>5.886259700489634e-05</v>
       </c>
       <c r="J17">
-        <v>0.004584010862976745</v>
+        <v>5.179048050773429e-05</v>
       </c>
       <c r="K17">
-        <v>208.3</v>
+        <v>574.9</v>
       </c>
       <c r="L17">
-        <v>0.1305383217396754</v>
+        <v>0.3622330035914561</v>
       </c>
       <c r="M17">
-        <v>-0</v>
+        <v>130.8</v>
       </c>
       <c r="N17">
-        <v>-0</v>
+        <v>0.01497852848554252</v>
       </c>
       <c r="O17">
-        <v>-0</v>
+        <v>0.2275178291876848</v>
       </c>
       <c r="P17">
-        <v>-0</v>
+        <v>130.8</v>
       </c>
       <c r="Q17">
-        <v>-0</v>
+        <v>0.01497852848554252</v>
       </c>
       <c r="R17">
-        <v>-0</v>
+        <v>0.2275178291876848</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
       <c r="U17">
-        <v>1825</v>
+        <v>1673.4</v>
       </c>
       <c r="V17">
-        <v>0.4118709095012413</v>
+        <v>0.1916289722301746</v>
       </c>
       <c r="W17">
-        <v>0.07570141008867569</v>
+        <v>0.1059469620183182</v>
       </c>
       <c r="X17">
-        <v>0.1302854681852327</v>
+        <v>0.07569419386806324</v>
       </c>
       <c r="Y17">
-        <v>-0.05458405809655699</v>
+        <v>0.03025276815025495</v>
       </c>
       <c r="Z17">
-        <v>0.2067803197030456</v>
+        <v>0.2442606257351894</v>
       </c>
       <c r="AA17">
-        <v>0.0009478832317685654</v>
+        <v>1.265037517594531e-05</v>
       </c>
       <c r="AB17">
-        <v>0.08529508473142791</v>
+        <v>0.07052073884252671</v>
       </c>
       <c r="AC17">
-        <v>-0.08434720149965935</v>
+        <v>-0.07050808846735077</v>
       </c>
       <c r="AD17">
-        <v>6960.8</v>
+        <v>2485.6</v>
       </c>
       <c r="AE17">
-        <v>166.3852543199606</v>
+        <v>1.967895861467645</v>
       </c>
       <c r="AF17">
-        <v>7127.185254319961</v>
+        <v>2487.567895861468</v>
       </c>
       <c r="AG17">
-        <v>5302.185254319961</v>
+        <v>814.1678958614675</v>
       </c>
       <c r="AH17">
-        <v>0.616635319256206</v>
+        <v>0.2217070269939284</v>
       </c>
       <c r="AI17">
-        <v>0.7236099217666216</v>
+        <v>0.3007880767579445</v>
       </c>
       <c r="AJ17">
-        <v>0.5447533480333838</v>
+        <v>0.0852829390047614</v>
       </c>
       <c r="AK17">
-        <v>0.6607508252900761</v>
+        <v>0.1234192120617495</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2526,10 +2529,10 @@
         <v>0</v>
       </c>
       <c r="AN17">
-        <v>162.2564102564103</v>
+        <v>5103.901437371664</v>
       </c>
       <c r="AP17">
-        <v>123.5940618722602</v>
+        <v>1671.802660906504</v>
       </c>
     </row>
     <row r="18">
@@ -2540,7 +2543,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HDFC Bank Limited (NSEI:HDFCBANK)</t>
+          <t>Indian Overseas Bank (NSEI:IOB)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2548,15 +2551,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D18">
-        <v>0.161</v>
-      </c>
-      <c r="E18">
-        <v>0.197</v>
-      </c>
-      <c r="F18">
-        <v>0.204</v>
-      </c>
       <c r="G18">
         <v>0</v>
       </c>
@@ -2564,103 +2558,94 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>-0.001921008608349937</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>-0.001444363575620856</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>5129.2</v>
+        <v>281.9</v>
       </c>
       <c r="L18">
-        <v>0.4140191140384864</v>
+        <v>0.2420365759423027</v>
       </c>
       <c r="M18">
-        <v>1057.4</v>
+        <v>-0</v>
       </c>
       <c r="N18">
-        <v>0.009638031486302221</v>
+        <v>-0</v>
       </c>
       <c r="O18">
-        <v>0.2061530063167746</v>
+        <v>-0</v>
       </c>
       <c r="P18">
-        <v>1057.4</v>
+        <v>-0</v>
       </c>
       <c r="Q18">
-        <v>0.009638031486302221</v>
+        <v>-0</v>
       </c>
       <c r="R18">
-        <v>0.2061530063167746</v>
+        <v>-0</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
       <c r="U18">
-        <v>12869.3</v>
+        <v>2296</v>
       </c>
       <c r="V18">
-        <v>0.1173016063993466</v>
+        <v>0.2318887418823791</v>
       </c>
       <c r="W18">
-        <v>0.1625551442624613</v>
+        <v>0.09595942403921436</v>
       </c>
       <c r="X18">
-        <v>0.09060072290403065</v>
+        <v>0.07728951498627558</v>
       </c>
       <c r="Y18">
-        <v>0.07195442135843069</v>
+        <v>0.01866990905293878</v>
       </c>
       <c r="Z18">
-        <v>0.2238067655908471</v>
+        <v>0.4877098948955237</v>
       </c>
       <c r="AA18">
-        <v>-0.0003232583401969348</v>
+        <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.08402983773450776</v>
+        <v>0.07070453076472587</v>
       </c>
       <c r="AC18">
-        <v>-0.08435309607470469</v>
+        <v>-0.07070453076472587</v>
       </c>
       <c r="AD18">
-        <v>30936.4</v>
+        <v>3554.1</v>
       </c>
       <c r="AE18">
-        <v>996.4949572356285</v>
+        <v>0</v>
       </c>
       <c r="AF18">
-        <v>31932.89495723563</v>
+        <v>3554.1</v>
       </c>
       <c r="AG18">
-        <v>19063.59495723563</v>
+        <v>1258.1</v>
       </c>
       <c r="AH18">
-        <v>0.2254445903083826</v>
+        <v>0.2641393046657847</v>
       </c>
       <c r="AI18">
-        <v>0.496892524460323</v>
+        <v>0.5320031134928001</v>
       </c>
       <c r="AJ18">
-        <v>0.1480382474191972</v>
+        <v>0.1127390361488969</v>
       </c>
       <c r="AK18">
-        <v>0.3709166845542363</v>
+        <v>0.2869360945126123</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
         <v>0</v>
-      </c>
-      <c r="AN18">
-        <v>176.2757834757835</v>
-      </c>
-      <c r="AP18">
-        <v>108.6244726908013</v>
       </c>
     </row>
     <row r="19">
@@ -2671,7 +2656,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DCB Bank Limited (NSEI:DCBBANK)</t>
+          <t>Central Bank of India (NSEI:CENTRALBK)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2679,12 +2664,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D19">
-        <v>0.0998</v>
-      </c>
-      <c r="E19">
-        <v>0.118</v>
-      </c>
       <c r="G19">
         <v>0</v>
       </c>
@@ -2698,85 +2677,82 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>48.9</v>
+        <v>262.6</v>
       </c>
       <c r="L19">
-        <v>0.2334128878281623</v>
+        <v>0.1763955128635722</v>
       </c>
       <c r="M19">
-        <v>3.82</v>
+        <v>-0</v>
       </c>
       <c r="N19">
-        <v>0.008018471872376155</v>
+        <v>-0</v>
       </c>
       <c r="O19">
-        <v>0.07811860940695296</v>
+        <v>-0</v>
       </c>
       <c r="P19">
-        <v>3.82</v>
+        <v>-0</v>
       </c>
       <c r="Q19">
-        <v>0.008018471872376155</v>
+        <v>-0</v>
       </c>
       <c r="R19">
-        <v>0.07811860940695296</v>
+        <v>-0</v>
       </c>
       <c r="S19">
         <v>0</v>
       </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
       <c r="U19">
-        <v>286.9</v>
+        <v>2482.5</v>
       </c>
       <c r="V19">
-        <v>0.602225020990764</v>
+        <v>0.4727580887813981</v>
       </c>
       <c r="W19">
-        <v>0.09402038069601999</v>
+        <v>0.07588279489105937</v>
       </c>
       <c r="X19">
-        <v>0.109142329571603</v>
+        <v>0.07801285952639805</v>
       </c>
       <c r="Y19">
-        <v>-0.01512194887558303</v>
+        <v>-0.002130064635338685</v>
       </c>
       <c r="Z19">
-        <v>0.3826484018264841</v>
+        <v>0.3496726883245918</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.08450270378388475</v>
+        <v>0.07078142092265673</v>
       </c>
       <c r="AC19">
-        <v>-0.08450270378388475</v>
+        <v>-0.07078142092265673</v>
       </c>
       <c r="AD19">
-        <v>431.9</v>
+        <v>2061.3</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>431.9</v>
+        <v>2061.3</v>
       </c>
       <c r="AG19">
-        <v>145</v>
+        <v>-421.1999999999998</v>
       </c>
       <c r="AH19">
-        <v>0.4755036882087416</v>
+        <v>0.2818910344073081</v>
       </c>
       <c r="AI19">
-        <v>0.4538194809288641</v>
+        <v>0.3603104406649304</v>
       </c>
       <c r="AJ19">
-        <v>0.2333440617959447</v>
+        <v>-0.08720677446738023</v>
       </c>
       <c r="AK19">
-        <v>0.2181107099879663</v>
+        <v>-0.1300642292490118</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2793,7 +2769,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Canara Bank (NSEI:CANBK)</t>
+          <t>ICICI Bank Limited (NSEI:ICICIBANK)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2801,6 +2777,15 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D20">
+        <v>0.147</v>
+      </c>
+      <c r="E20">
+        <v>0.5670000000000001</v>
+      </c>
+      <c r="F20">
+        <v>0.141</v>
+      </c>
       <c r="G20">
         <v>0</v>
       </c>
@@ -2808,94 +2793,103 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>0.0003764001244170469</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>0.0003586706418995353</v>
       </c>
       <c r="K20">
-        <v>1039.8</v>
+        <v>4835.8</v>
       </c>
       <c r="L20">
-        <v>0.243415970222628</v>
+        <v>0.3055720550507413</v>
       </c>
       <c r="M20">
-        <v>-0</v>
+        <v>673.9</v>
       </c>
       <c r="N20">
-        <v>-0</v>
+        <v>0.008002137386451344</v>
       </c>
       <c r="O20">
-        <v>-0</v>
+        <v>0.1393564663551015</v>
       </c>
       <c r="P20">
-        <v>-0</v>
+        <v>673.9</v>
       </c>
       <c r="Q20">
-        <v>-0</v>
+        <v>0.008002137386451344</v>
       </c>
       <c r="R20">
-        <v>-0</v>
+        <v>0.1393564663551015</v>
       </c>
       <c r="S20">
         <v>0</v>
       </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
       <c r="U20">
-        <v>6806.4</v>
+        <v>15539</v>
       </c>
       <c r="V20">
-        <v>0.9311717627744716</v>
+        <v>0.1845158225969245</v>
       </c>
       <c r="W20">
-        <v>0.1143466690126905</v>
+        <v>0.2016563526880286</v>
       </c>
       <c r="X20">
-        <v>0.1134821341685787</v>
+        <v>0.07540546750046516</v>
       </c>
       <c r="Y20">
-        <v>0.00086453484411185</v>
+        <v>0.1262508851875634</v>
       </c>
       <c r="Z20">
-        <v>0.3310266265769816</v>
+        <v>0.5390688750608226</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>0.0001933481794461256</v>
       </c>
       <c r="AB20">
-        <v>0.08470958876437033</v>
+        <v>0.0710855243446574</v>
       </c>
       <c r="AC20">
-        <v>-0.08470958876437033</v>
+        <v>-0.07089217616521128</v>
       </c>
       <c r="AD20">
-        <v>7679.8</v>
+        <v>22833.8</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>26.71658735525234</v>
       </c>
       <c r="AF20">
-        <v>7679.8</v>
+        <v>22860.51658735525</v>
       </c>
       <c r="AG20">
-        <v>873.4000000000005</v>
+        <v>7321.516587355251</v>
       </c>
       <c r="AH20">
-        <v>0.5123521445297646</v>
+        <v>0.2134990081388493</v>
       </c>
       <c r="AI20">
-        <v>0.4524022714955584</v>
+        <v>0.4427105296132745</v>
       </c>
       <c r="AJ20">
-        <v>0.1067347761795941</v>
+        <v>0.07998465377878097</v>
       </c>
       <c r="AK20">
-        <v>0.08588679542146879</v>
+        <v>0.2028198662305485</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
         <v>0</v>
+      </c>
+      <c r="AN20">
+        <v>2020.690265486725</v>
+      </c>
+      <c r="AP20">
+        <v>647.9218218898451</v>
       </c>
     </row>
     <row r="21">
@@ -2906,7 +2900,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bank of Maharashtra (NSEI:MAHABANK)</t>
+          <t>Punjab National Bank (NSEI:PNB)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2914,6 +2908,9 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="F21">
+        <v>0.76</v>
+      </c>
       <c r="G21">
         <v>0</v>
       </c>
@@ -2927,28 +2924,28 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>203.1</v>
+        <v>710.7</v>
       </c>
       <c r="L21">
-        <v>0.2986325540361711</v>
+        <v>0.1714761376248613</v>
       </c>
       <c r="M21">
-        <v>82.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="N21">
-        <v>0.03323287120755476</v>
+        <v>0.006655021023992084</v>
       </c>
       <c r="O21">
-        <v>0.4071885770556377</v>
+        <v>0.1211481637821866</v>
       </c>
       <c r="P21">
-        <v>82.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="Q21">
-        <v>0.03323287120755476</v>
+        <v>0.006655021023992084</v>
       </c>
       <c r="R21">
-        <v>0.4071885770556377</v>
+        <v>0.1211481637821866</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -2957,55 +2954,55 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>1783.4</v>
+        <v>12613.1</v>
       </c>
       <c r="V21">
-        <v>0.7166566204540888</v>
+        <v>0.974918068266139</v>
       </c>
       <c r="W21">
-        <v>0.1141267700606878</v>
+        <v>0.05726833199033039</v>
       </c>
       <c r="X21">
-        <v>0.1159144044531887</v>
+        <v>0.08451750821620105</v>
       </c>
       <c r="Y21">
-        <v>-0.001787634392500861</v>
+        <v>-0.02724917622587066</v>
       </c>
       <c r="Z21">
-        <v>0.7023649695342353</v>
+        <v>0.6693799764200463</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.08481330871760595</v>
+        <v>0.07133589060721593</v>
       </c>
       <c r="AC21">
-        <v>-0.08481330871760595</v>
+        <v>-0.07133589060721593</v>
       </c>
       <c r="AD21">
-        <v>2815.5</v>
+        <v>8986.9</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>2815.5</v>
+        <v>8986.9</v>
       </c>
       <c r="AG21">
-        <v>1032.1</v>
+        <v>-3626.200000000001</v>
       </c>
       <c r="AH21">
-        <v>0.5308257918552036</v>
+        <v>0.4099021642454788</v>
       </c>
       <c r="AI21">
-        <v>0.6035499153250874</v>
+        <v>0.411506937130821</v>
       </c>
       <c r="AJ21">
-        <v>0.2931602567744134</v>
+        <v>-0.3894366045922204</v>
       </c>
       <c r="AK21">
-        <v>0.3581815026895714</v>
+        <v>-0.3930456649215796</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3022,7 +3019,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Karnataka Bank Limited (NSEI:KTKBANK)</t>
+          <t>Bank of Baroda Limited (NSEI:BANKBARODA)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3031,10 +3028,10 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.108</v>
-      </c>
-      <c r="E22">
-        <v>0.131</v>
+        <v>0.403</v>
+      </c>
+      <c r="F22">
+        <v>0.9229999999999999</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3043,34 +3040,34 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>0.001497295645770989</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>0.001062635261386462</v>
       </c>
       <c r="K22">
-        <v>98.59999999999999</v>
+        <v>2215.5</v>
       </c>
       <c r="L22">
-        <v>0.264626945786366</v>
+        <v>0.3192179125122471</v>
       </c>
       <c r="M22">
-        <v>15.3</v>
+        <v>340.9</v>
       </c>
       <c r="N22">
-        <v>0.02667829119442023</v>
+        <v>0.02347375814248137</v>
       </c>
       <c r="O22">
-        <v>0.1551724137931035</v>
+        <v>0.153870458135861</v>
       </c>
       <c r="P22">
-        <v>15.3</v>
+        <v>340.9</v>
       </c>
       <c r="Q22">
-        <v>0.02667829119442023</v>
+        <v>0.02347375814248137</v>
       </c>
       <c r="R22">
-        <v>0.1551724137931035</v>
+        <v>0.153870458135861</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -3079,61 +3076,67 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>616.5</v>
+        <v>6917.7</v>
       </c>
       <c r="V22">
-        <v>1.074978204010462</v>
+        <v>0.4763403247352402</v>
       </c>
       <c r="W22">
-        <v>0.1072671888598781</v>
+        <v>0.1849023535302954</v>
       </c>
       <c r="X22">
-        <v>0.120197270376677</v>
+        <v>0.09218879052910034</v>
       </c>
       <c r="Y22">
-        <v>-0.01293008151679888</v>
+        <v>0.0927135630011951</v>
       </c>
       <c r="Z22">
-        <v>0.4601704334938866</v>
+        <v>0.3479954164233207</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>0.000369792200292286</v>
       </c>
       <c r="AB22">
-        <v>0.08497803685029348</v>
+        <v>0.07177989421756564</v>
       </c>
       <c r="AC22">
-        <v>-0.08497803685029348</v>
+        <v>-0.07141010201727335</v>
       </c>
       <c r="AD22">
-        <v>730.4</v>
+        <v>15198.8</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>63.04084650045514</v>
       </c>
       <c r="AF22">
-        <v>730.4</v>
+        <v>15261.84084650045</v>
       </c>
       <c r="AG22">
-        <v>113.9</v>
+        <v>8344.140846500453</v>
       </c>
       <c r="AH22">
-        <v>0.5601656568755272</v>
+        <v>0.5124098493288873</v>
       </c>
       <c r="AI22">
-        <v>0.4403979499547784</v>
+        <v>0.5246829214767501</v>
       </c>
       <c r="AJ22">
-        <v>0.1656968286296188</v>
+        <v>0.364902934900644</v>
       </c>
       <c r="AK22">
-        <v>0.1093090211132437</v>
+        <v>0.3763701160621713</v>
       </c>
       <c r="AL22">
         <v>0</v>
       </c>
       <c r="AM22">
         <v>0</v>
+      </c>
+      <c r="AN22">
+        <v>660.8173913043478</v>
+      </c>
+      <c r="AP22">
+        <v>362.7887324565414</v>
       </c>
     </row>
     <row r="23">
@@ -3144,7 +3147,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bank of Baroda (NSEI:BANKBARODA)</t>
+          <t>Suryoday Small Finance Bank Limited (NSEI:SURYODAY)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3153,13 +3156,10 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.237</v>
+        <v>0.295</v>
       </c>
       <c r="E23">
-        <v>0.474</v>
-      </c>
-      <c r="F23">
-        <v>0.278</v>
+        <v>0.277</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3168,91 +3168,88 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>-7.721671577331875e-05</v>
+        <v>0.003072738682494725</v>
       </c>
       <c r="J23">
-        <v>-6.945612678809639e-05</v>
+        <v>0.002323836380121517</v>
       </c>
       <c r="K23">
-        <v>1209.2</v>
+        <v>18.6</v>
       </c>
       <c r="L23">
-        <v>0.258785258742456</v>
+        <v>0.1861861861861862</v>
       </c>
       <c r="M23">
-        <v>180.1</v>
+        <v>-0</v>
       </c>
       <c r="N23">
-        <v>0.01552104519287118</v>
+        <v>-0</v>
       </c>
       <c r="O23">
-        <v>0.1489414488918293</v>
+        <v>-0</v>
       </c>
       <c r="P23">
-        <v>180.1</v>
+        <v>-0</v>
       </c>
       <c r="Q23">
-        <v>0.01552104519287118</v>
+        <v>-0</v>
       </c>
       <c r="R23">
-        <v>0.1489414488918293</v>
+        <v>-0</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
       <c r="U23">
-        <v>6408</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="V23">
-        <v>0.552242407528698</v>
+        <v>0.3806903451725863</v>
       </c>
       <c r="W23">
-        <v>0.1042647489954645</v>
+        <v>0.09909429941395846</v>
       </c>
       <c r="X23">
-        <v>0.1194222391990772</v>
+        <v>0.1018308998136627</v>
       </c>
       <c r="Y23">
-        <v>-0.01515749020361272</v>
+        <v>-0.002736600399704248</v>
       </c>
       <c r="Z23">
-        <v>0.9935985734930044</v>
+        <v>0.2342375222766141</v>
       </c>
       <c r="AA23">
-        <v>-6.901150849700182e-05</v>
+        <v>0.00054432967585592</v>
       </c>
       <c r="AB23">
-        <v>0.08494977177469459</v>
+        <v>0.07215838247891768</v>
       </c>
       <c r="AC23">
-        <v>-0.0850187832831916</v>
+        <v>-0.07161405280306175</v>
       </c>
       <c r="AD23">
-        <v>14418.8</v>
+        <v>298.5</v>
       </c>
       <c r="AE23">
-        <v>60.80401413061205</v>
+        <v>1.090167028093885</v>
       </c>
       <c r="AF23">
-        <v>14479.60401413061</v>
+        <v>299.5901670280939</v>
       </c>
       <c r="AG23">
-        <v>8071.604014130611</v>
+        <v>223.4901670280939</v>
       </c>
       <c r="AH23">
-        <v>0.5551313407005621</v>
+        <v>0.599791921451866</v>
       </c>
       <c r="AI23">
-        <v>0.5449400408968467</v>
+        <v>0.5964484011317254</v>
       </c>
       <c r="AJ23">
-        <v>0.4102424558512142</v>
+        <v>0.5278586618977013</v>
       </c>
       <c r="AK23">
-        <v>0.4003175324705525</v>
+        <v>0.5243907164412869</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -3261,10 +3258,10 @@
         <v>0</v>
       </c>
       <c r="AN23">
-        <v>1221.93220338983</v>
+        <v>568.5714285714286</v>
       </c>
       <c r="AP23">
-        <v>684.034238485645</v>
+        <v>425.6955562439884</v>
       </c>
     </row>
     <row r="24">
@@ -3275,7 +3272,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Suryoday Small Finance Bank Limited (NSEI:SURYODAY)</t>
+          <t>Canara Bank (NSEI:CANBK)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3283,6 +3280,9 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="F24">
+        <v>0.254</v>
+      </c>
       <c r="G24">
         <v>0</v>
       </c>
@@ -3290,100 +3290,97 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>0.001039697267459076</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>0.0005198486337295381</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>-2.78</v>
+        <v>1673.8</v>
       </c>
       <c r="L24">
-        <v>-0.05063752276867031</v>
+        <v>0.2698763322100579</v>
       </c>
       <c r="M24">
-        <v>-0</v>
+        <v>141.9</v>
       </c>
       <c r="N24">
-        <v>-0</v>
+        <v>0.01470954098768504</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>0.08477715378181384</v>
       </c>
       <c r="P24">
-        <v>-0</v>
+        <v>141.9</v>
       </c>
       <c r="Q24">
-        <v>-0</v>
+        <v>0.01470954098768504</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>0.08477715378181384</v>
       </c>
       <c r="S24">
         <v>0</v>
       </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
       <c r="U24">
-        <v>51.1</v>
+        <v>16159.3</v>
       </c>
       <c r="V24">
-        <v>0.3271446862996159</v>
+        <v>1.675094331799146</v>
       </c>
       <c r="W24">
-        <v>-0.01331417624521073</v>
+        <v>0.1821089738010271</v>
       </c>
       <c r="X24">
-        <v>0.137549080760154</v>
+        <v>0.09133804039481166</v>
       </c>
       <c r="Y24">
-        <v>-0.1508632570053647</v>
+        <v>0.09077093340621539</v>
       </c>
       <c r="Z24">
-        <v>0.1306180006240006</v>
+        <v>0.616229159628798</v>
       </c>
       <c r="AA24">
-        <v>6.790158916487064e-05</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.08547721782579321</v>
+        <v>0.07173840839169414</v>
       </c>
       <c r="AC24">
-        <v>-0.08540931623662834</v>
+        <v>-0.07173840839169414</v>
       </c>
       <c r="AD24">
-        <v>288.8</v>
+        <v>9756.700000000001</v>
       </c>
       <c r="AE24">
-        <v>0.1096031000824836</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>288.9096031000825</v>
+        <v>9756.700000000001</v>
       </c>
       <c r="AG24">
-        <v>237.8096031000825</v>
+        <v>-6402.599999999999</v>
       </c>
       <c r="AH24">
-        <v>0.6490751965086707</v>
+        <v>0.5028319633055892</v>
       </c>
       <c r="AI24">
-        <v>0.6061766301410734</v>
+        <v>0.4839032858028519</v>
       </c>
       <c r="AJ24">
-        <v>0.6035629619912498</v>
+        <v>-1.973552801923432</v>
       </c>
       <c r="AK24">
-        <v>0.5588818709789453</v>
+        <v>-1.599370503597122</v>
       </c>
       <c r="AL24">
         <v>0</v>
       </c>
       <c r="AM24">
         <v>0</v>
-      </c>
-      <c r="AN24">
-        <v>3655.696202531646</v>
-      </c>
-      <c r="AP24">
-        <v>3010.248140507374</v>
       </c>
     </row>
     <row r="25">
@@ -3394,7 +3391,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Yes Bank Limited (NSEI:YESBANK)</t>
+          <t>Indian Bank (NSEI:INDIANB)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3409,100 +3406,97 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>-0.004621823770611334</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>-0.003433067575125113</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>136.7</v>
+        <v>829.5</v>
       </c>
       <c r="L25">
-        <v>0.1170476924394212</v>
+        <v>0.3103022594643124</v>
       </c>
       <c r="M25">
-        <v>-0</v>
+        <v>217.2</v>
       </c>
       <c r="N25">
-        <v>-0</v>
+        <v>0.03180553521745497</v>
       </c>
       <c r="O25">
-        <v>-0</v>
+        <v>0.2618444846292947</v>
       </c>
       <c r="P25">
-        <v>-0</v>
+        <v>217.2</v>
       </c>
       <c r="Q25">
-        <v>-0</v>
+        <v>0.03180553521745497</v>
       </c>
       <c r="R25">
-        <v>-0</v>
+        <v>0.2618444846292947</v>
       </c>
       <c r="S25">
         <v>0</v>
       </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
       <c r="U25">
-        <v>3858.9</v>
+        <v>1558</v>
       </c>
       <c r="V25">
-        <v>0.5391784267151041</v>
+        <v>0.2281446771123151</v>
       </c>
       <c r="W25">
-        <v>0.03022664455500276</v>
+        <v>0.141882183908046</v>
       </c>
       <c r="X25">
-        <v>0.1225304898967624</v>
+        <v>0.07902499808312416</v>
       </c>
       <c r="Y25">
-        <v>-0.09230384534175967</v>
+        <v>0.06285718582492184</v>
       </c>
       <c r="Z25">
-        <v>0.1177486014922054</v>
+        <v>0.4882378725891292</v>
       </c>
       <c r="AA25">
-        <v>-0.0004042389057992187</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>0.08505939383734587</v>
+        <v>0.07174156942053227</v>
       </c>
       <c r="AC25">
-        <v>-0.08546363274314508</v>
+        <v>-0.07174156942053227</v>
       </c>
       <c r="AD25">
-        <v>9447.4</v>
+        <v>3001.7</v>
       </c>
       <c r="AE25">
-        <v>221.9891399084849</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>9669.389139908484</v>
+        <v>3001.7</v>
       </c>
       <c r="AG25">
-        <v>5810.489139908485</v>
+        <v>1443.7</v>
       </c>
       <c r="AH25">
-        <v>0.5746562176536633</v>
+        <v>0.305339395973837</v>
       </c>
       <c r="AI25">
-        <v>0.6958302771037386</v>
+        <v>0.3182868897654494</v>
       </c>
       <c r="AJ25">
-        <v>0.4480812805947328</v>
+        <v>0.1745137621332817</v>
       </c>
       <c r="AK25">
-        <v>0.5788902819194329</v>
+        <v>0.1833782135961792</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
         <v>0</v>
-      </c>
-      <c r="AN25">
-        <v>242.2410256410256</v>
-      </c>
-      <c r="AP25">
-        <v>148.9869010232945</v>
       </c>
     </row>
     <row r="26">
@@ -3513,7 +3507,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Indian Bank (NSEI:INDIANB)</t>
+          <t>Bank of India Limited (NSEI:BANKINDIA)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3521,6 +3515,9 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="F26">
+        <v>0.326</v>
+      </c>
       <c r="G26">
         <v>0</v>
       </c>
@@ -3534,28 +3531,28 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>535.1</v>
+        <v>648.3</v>
       </c>
       <c r="L26">
-        <v>0.2662189054726368</v>
+        <v>0.2140451664025356</v>
       </c>
       <c r="M26">
-        <v>189.7</v>
+        <v>98.8</v>
       </c>
       <c r="N26">
-        <v>0.04417689387764607</v>
+        <v>0.01597826438528965</v>
       </c>
       <c r="O26">
-        <v>0.3545131751074565</v>
+        <v>0.1523985809039025</v>
       </c>
       <c r="P26">
-        <v>189.7</v>
+        <v>98.8</v>
       </c>
       <c r="Q26">
-        <v>0.04417689387764607</v>
+        <v>0.01597826438528965</v>
       </c>
       <c r="R26">
-        <v>0.3545131751074565</v>
+        <v>0.1523985809039025</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -3564,55 +3561,55 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>3083.4</v>
+        <v>9983.299999999999</v>
       </c>
       <c r="V26">
-        <v>0.7180550057055028</v>
+        <v>1.614532457871074</v>
       </c>
       <c r="W26">
-        <v>0.09125948665472841</v>
+        <v>0.091209656996539</v>
       </c>
       <c r="X26">
-        <v>0.1008590715102836</v>
+        <v>0.09697012105612704</v>
       </c>
       <c r="Y26">
-        <v>-0.009599584855555218</v>
+        <v>-0.005760464059588036</v>
       </c>
       <c r="Z26">
-        <v>0.6345498168960727</v>
+        <v>1.302149613069647</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.08560517111726795</v>
+        <v>0.07198621935008988</v>
       </c>
       <c r="AC26">
-        <v>-0.08560517111726795</v>
+        <v>-0.07198621935008988</v>
       </c>
       <c r="AD26">
-        <v>2712.2</v>
+        <v>7871.2</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>2712.2</v>
+        <v>7871.2</v>
       </c>
       <c r="AG26">
-        <v>-371.2000000000003</v>
+        <v>-2112.099999999999</v>
       </c>
       <c r="AH26">
-        <v>0.3871087449866548</v>
+        <v>0.5600443982752978</v>
       </c>
       <c r="AI26">
-        <v>0.3167828819042947</v>
+        <v>0.5108846628156033</v>
       </c>
       <c r="AJ26">
-        <v>-0.09462387519437158</v>
+        <v>-0.5187777859651707</v>
       </c>
       <c r="AK26">
-        <v>-0.06775824617125757</v>
+        <v>-0.3894205062964395</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -3629,7 +3626,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Axis Bank Limited (BSE:532215)</t>
+          <t>UCO Bank (NSEI:UCOBANK)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3637,9 +3634,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="F27">
-        <v>0.273</v>
-      </c>
       <c r="G27">
         <v>0</v>
       </c>
@@ -3647,103 +3641,94 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>-0.0008991446329888266</v>
+        <v>0</v>
       </c>
       <c r="J27">
-        <v>-0.0008327180294904683</v>
+        <v>0</v>
       </c>
       <c r="K27">
-        <v>2257.2</v>
+        <v>225.8</v>
       </c>
       <c r="L27">
-        <v>0.3881551795295088</v>
+        <v>0.2378093733543971</v>
       </c>
       <c r="M27">
-        <v>37.7</v>
+        <v>-0</v>
       </c>
       <c r="N27">
-        <v>0.001086552400934954</v>
+        <v>-0</v>
       </c>
       <c r="O27">
-        <v>0.01670210880737197</v>
+        <v>-0</v>
       </c>
       <c r="P27">
-        <v>37.7</v>
+        <v>-0</v>
       </c>
       <c r="Q27">
-        <v>0.001086552400934954</v>
+        <v>-0</v>
       </c>
       <c r="R27">
-        <v>0.01670210880737197</v>
+        <v>-0</v>
       </c>
       <c r="S27">
         <v>0</v>
       </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
       <c r="U27">
-        <v>8963.9</v>
+        <v>1431.4</v>
       </c>
       <c r="V27">
-        <v>0.2583487285607648</v>
+        <v>0.249129768866611</v>
       </c>
       <c r="W27">
-        <v>0.1527622682882261</v>
+        <v>0.07584562157804575</v>
       </c>
       <c r="X27">
-        <v>0.1036717143870875</v>
+        <v>0.08438150529930658</v>
       </c>
       <c r="Y27">
-        <v>0.04909055390113859</v>
+        <v>-0.008535883721260823</v>
       </c>
       <c r="Z27">
-        <v>0.2314107407226287</v>
+        <v>0.2577011806215226</v>
       </c>
       <c r="AA27">
-        <v>-0.0001926998960174771</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>0.08592844635785718</v>
+        <v>0.07208802409935643</v>
       </c>
       <c r="AC27">
-        <v>-0.08612114625387465</v>
+        <v>-0.07208802409935643</v>
       </c>
       <c r="AD27">
-        <v>24509</v>
+        <v>3954.8</v>
       </c>
       <c r="AE27">
-        <v>645.6435293487832</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>25154.64352934878</v>
+        <v>3954.8</v>
       </c>
       <c r="AG27">
-        <v>16190.74352934879</v>
+        <v>2523.4</v>
       </c>
       <c r="AH27">
-        <v>0.4202839567038729</v>
+        <v>0.4076945280606985</v>
       </c>
       <c r="AI27">
-        <v>0.6136784138611479</v>
+        <v>0.5557694739948567</v>
       </c>
       <c r="AJ27">
-        <v>0.318166501854443</v>
+        <v>0.3051638650380941</v>
       </c>
       <c r="AK27">
-        <v>0.5055492888002706</v>
+        <v>0.4439088750109949</v>
       </c>
       <c r="AL27">
         <v>0</v>
       </c>
       <c r="AM27">
         <v>0</v>
-      </c>
-      <c r="AN27">
-        <v>197.8127522195319</v>
-      </c>
-      <c r="AP27">
-        <v>130.675896120652</v>
       </c>
     </row>
     <row r="28">
@@ -3754,7 +3739,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>State Bank of India (NSEI:SBIN)</t>
+          <t>Union Bank of India (NSEI:UNIONBANK)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3762,14 +3747,8 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D28">
-        <v>0.192</v>
-      </c>
-      <c r="E28">
-        <v>0.59</v>
-      </c>
       <c r="F28">
-        <v>1.165</v>
+        <v>0.327</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3778,34 +3757,34 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>0.0003893983645240406</v>
+        <v>0</v>
       </c>
       <c r="J28">
-        <v>0.0003721725639166213</v>
+        <v>0</v>
       </c>
       <c r="K28">
-        <v>5060.7</v>
+        <v>1434.6</v>
       </c>
       <c r="L28">
-        <v>0.1886687643532464</v>
+        <v>0.2761926764468061</v>
       </c>
       <c r="M28">
-        <v>0.001</v>
+        <v>246.8</v>
       </c>
       <c r="N28">
-        <v>1.511053355293976e-08</v>
+        <v>0.02295130751776215</v>
       </c>
       <c r="O28">
-        <v>1.976011223743751e-07</v>
+        <v>0.1720340164505786</v>
       </c>
       <c r="P28">
-        <v>0.001</v>
+        <v>246.8</v>
       </c>
       <c r="Q28">
-        <v>1.511053355293976e-08</v>
+        <v>0.02295130751776215</v>
       </c>
       <c r="R28">
-        <v>1.976011223743751e-07</v>
+        <v>0.1720340164505786</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -3814,67 +3793,61 @@
         <v>0</v>
       </c>
       <c r="U28">
-        <v>28768.8</v>
+        <v>13218.6</v>
       </c>
       <c r="V28">
-        <v>0.4347119176778132</v>
+        <v>1.229271286686754</v>
       </c>
       <c r="W28">
-        <v>0.1283454602171426</v>
+        <v>0.1568846166464355</v>
       </c>
       <c r="X28">
-        <v>0.1107083096487222</v>
+        <v>0.08225049911242791</v>
       </c>
       <c r="Y28">
-        <v>0.01763715056842043</v>
+        <v>0.07463411753400759</v>
       </c>
       <c r="Z28">
-        <v>0.6021477797813979</v>
+        <v>0.8018710633567989</v>
       </c>
       <c r="AA28">
-        <v>0.0002241028830579439</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>0.08660219254412367</v>
+        <v>0.07220926121825029</v>
       </c>
       <c r="AC28">
-        <v>-0.08637808966106572</v>
+        <v>-0.07220926121825029</v>
       </c>
       <c r="AD28">
-        <v>63376.4</v>
+        <v>6337.4</v>
       </c>
       <c r="AE28">
-        <v>61.27544894349377</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>63437.6754489435</v>
+        <v>6337.4</v>
       </c>
       <c r="AG28">
-        <v>34668.87544894349</v>
+        <v>-6881.200000000001</v>
       </c>
       <c r="AH28">
-        <v>0.489425262831493</v>
+        <v>0.3708120253238623</v>
       </c>
       <c r="AI28">
-        <v>0.5992087413622215</v>
+        <v>0.3679550376524824</v>
       </c>
       <c r="AJ28">
-        <v>0.3437739793189336</v>
+        <v>-1.777169421487603</v>
       </c>
       <c r="AK28">
-        <v>0.4496595537055058</v>
+        <v>-1.718281019801734</v>
       </c>
       <c r="AL28">
         <v>0</v>
       </c>
       <c r="AM28">
         <v>0</v>
-      </c>
-      <c r="AN28">
-        <v>2791.911894273128</v>
-      </c>
-      <c r="AP28">
-        <v>1527.263235636277</v>
       </c>
     </row>
     <row r="29">
@@ -3885,7 +3858,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Union Bank of India (NSEI:UNIONBANK)</t>
+          <t>The Karnataka Bank Limited (NSEI:KTKBANK)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3893,6 +3866,12 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D29">
+        <v>0.179</v>
+      </c>
+      <c r="E29">
+        <v>0.294</v>
+      </c>
       <c r="G29">
         <v>0</v>
       </c>
@@ -3900,34 +3879,34 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>-0.002945106380379561</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>-0.002417447663009091</v>
       </c>
       <c r="K29">
-        <v>746</v>
+        <v>163.1</v>
       </c>
       <c r="L29">
-        <v>0.2403427945487935</v>
+        <v>0.3551055954713694</v>
       </c>
       <c r="M29">
-        <v>159.6</v>
+        <v>18.8</v>
       </c>
       <c r="N29">
-        <v>0.02403686858037892</v>
+        <v>0.01899757477768796</v>
       </c>
       <c r="O29">
-        <v>0.213941018766756</v>
+        <v>0.1152667075413857</v>
       </c>
       <c r="P29">
-        <v>159.6</v>
+        <v>18.8</v>
       </c>
       <c r="Q29">
-        <v>0.02403686858037892</v>
+        <v>0.01899757477768796</v>
       </c>
       <c r="R29">
-        <v>0.213941018766756</v>
+        <v>0.1152667075413857</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -3936,61 +3915,945 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>9626.6</v>
+        <v>828.8</v>
       </c>
       <c r="V29">
-        <v>1.449832826289948</v>
+        <v>0.8375101050929668</v>
       </c>
       <c r="W29">
-        <v>0.07943945137794438</v>
+        <v>0.1757353733433897</v>
       </c>
       <c r="X29">
-        <v>0.1134083079843638</v>
+        <v>0.08366083736626198</v>
       </c>
       <c r="Y29">
-        <v>-0.03396885660641942</v>
+        <v>0.09207453597712772</v>
       </c>
       <c r="Z29">
-        <v>0.2822445713454334</v>
+        <v>0.437746067900138</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>-0.001058228208836607</v>
       </c>
       <c r="AB29">
-        <v>0.0875722170948449</v>
+        <v>0.07127444097830643</v>
       </c>
       <c r="AC29">
-        <v>-0.0875722170948449</v>
+        <v>-0.07233266918714304</v>
       </c>
       <c r="AD29">
-        <v>6959.9</v>
+        <v>640.8</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>7.238436802541662</v>
       </c>
       <c r="AF29">
-        <v>6959.9</v>
+        <v>648.0384368025416</v>
       </c>
       <c r="AG29">
-        <v>-2666.700000000001</v>
+        <v>-180.7615631974584</v>
       </c>
       <c r="AH29">
-        <v>0.5117686419553372</v>
+        <v>0.3957152093155706</v>
       </c>
       <c r="AI29">
-        <v>0.4318359496184153</v>
+        <v>0.3806530813646712</v>
       </c>
       <c r="AJ29">
-        <v>-0.6711887443054545</v>
+        <v>-0.2234829045860328</v>
       </c>
       <c r="AK29">
-        <v>-0.4108683594231481</v>
+        <v>-0.2069066052760151</v>
       </c>
       <c r="AL29">
         <v>0</v>
       </c>
       <c r="AM29">
         <v>0</v>
+      </c>
+      <c r="AN29">
+        <v>6745.263157894737</v>
+      </c>
+      <c r="AP29">
+        <v>-1902.753296815351</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Yes Bank Limited (NSEI:YESBANK)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>-0.00519909752404294</v>
+      </c>
+      <c r="J30">
+        <v>-0.003904169430806294</v>
+      </c>
+      <c r="K30">
+        <v>100.7</v>
+      </c>
+      <c r="L30">
+        <v>0.07950418443075952</v>
+      </c>
+      <c r="M30">
+        <v>-0</v>
+      </c>
+      <c r="N30">
+        <v>-0</v>
+      </c>
+      <c r="O30">
+        <v>-0</v>
+      </c>
+      <c r="P30">
+        <v>-0</v>
+      </c>
+      <c r="Q30">
+        <v>-0</v>
+      </c>
+      <c r="R30">
+        <v>-0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>2812.8</v>
+      </c>
+      <c r="V30">
+        <v>0.3593943652973871</v>
+      </c>
+      <c r="W30">
+        <v>0.02382416958455569</v>
+      </c>
+      <c r="X30">
+        <v>0.09379806698215315</v>
+      </c>
+      <c r="Y30">
+        <v>-0.06997389739759746</v>
+      </c>
+      <c r="Z30">
+        <v>0.1259455626544492</v>
+      </c>
+      <c r="AA30">
+        <v>-0.0004917128156611993</v>
+      </c>
+      <c r="AB30">
+        <v>0.0718541508656297</v>
+      </c>
+      <c r="AC30">
+        <v>-0.0723458636812909</v>
+      </c>
+      <c r="AD30">
+        <v>8568.4</v>
+      </c>
+      <c r="AE30">
+        <v>241.425884619764</v>
+      </c>
+      <c r="AF30">
+        <v>8809.825884619764</v>
+      </c>
+      <c r="AG30">
+        <v>5997.025884619764</v>
+      </c>
+      <c r="AH30">
+        <v>0.5295535772573693</v>
+      </c>
+      <c r="AI30">
+        <v>0.6385770770726974</v>
+      </c>
+      <c r="AJ30">
+        <v>0.4338275151126337</v>
+      </c>
+      <c r="AK30">
+        <v>0.5460168030430506</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>0</v>
+      </c>
+      <c r="AN30">
+        <v>205.4772182254196</v>
+      </c>
+      <c r="AP30">
+        <v>143.8135703745747</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Axis Bank Limited (BSE:532215)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="F31">
+        <v>0.343</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>-0.0004485043176157035</v>
+      </c>
+      <c r="J31">
+        <v>-0.0004245001617014472</v>
+      </c>
+      <c r="K31">
+        <v>1579.3</v>
+      </c>
+      <c r="L31">
+        <v>0.2203325985658082</v>
+      </c>
+      <c r="M31">
+        <v>37.1</v>
+      </c>
+      <c r="N31">
+        <v>0.0009118996762879047</v>
+      </c>
+      <c r="O31">
+        <v>0.02349142024947762</v>
+      </c>
+      <c r="P31">
+        <v>37.1</v>
+      </c>
+      <c r="Q31">
+        <v>0.0009118996762879047</v>
+      </c>
+      <c r="R31">
+        <v>0.02349142024947762</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>8466.299999999999</v>
+      </c>
+      <c r="V31">
+        <v>0.2080974724893878</v>
+      </c>
+      <c r="W31">
+        <v>0.09999493472121972</v>
+      </c>
+      <c r="X31">
+        <v>0.08329142182660393</v>
+      </c>
+      <c r="Y31">
+        <v>0.01670351289461579</v>
+      </c>
+      <c r="Z31">
+        <v>0.2083936977057926</v>
+      </c>
+      <c r="AA31">
+        <v>-8.846315837367145e-05</v>
+      </c>
+      <c r="AB31">
+        <v>0.07234193222294399</v>
+      </c>
+      <c r="AC31">
+        <v>-0.07243039538131767</v>
+      </c>
+      <c r="AD31">
+        <v>25258</v>
+      </c>
+      <c r="AE31">
+        <v>686.0739462390292</v>
+      </c>
+      <c r="AF31">
+        <v>25944.07394623903</v>
+      </c>
+      <c r="AG31">
+        <v>17477.77394623903</v>
+      </c>
+      <c r="AH31">
+        <v>0.3893847682246115</v>
+      </c>
+      <c r="AI31">
+        <v>0.601454242351656</v>
+      </c>
+      <c r="AJ31">
+        <v>0.3005012160053692</v>
+      </c>
+      <c r="AK31">
+        <v>0.5041286406326673</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>0</v>
+      </c>
+      <c r="AN31">
+        <v>188.4925373134328</v>
+      </c>
+      <c r="AP31">
+        <v>130.4311488525301</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>The South Indian Bank Limited (NSEI:SOUTHBANK)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>0.161</v>
+      </c>
+      <c r="E32">
+        <v>0.232</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>110</v>
+      </c>
+      <c r="L32">
+        <v>0.2275077559462254</v>
+      </c>
+      <c r="M32">
+        <v>7.56</v>
+      </c>
+      <c r="N32">
+        <v>0.01119834098652051</v>
+      </c>
+      <c r="O32">
+        <v>0.06872727272727272</v>
+      </c>
+      <c r="P32">
+        <v>7.56</v>
+      </c>
+      <c r="Q32">
+        <v>0.01119834098652051</v>
+      </c>
+      <c r="R32">
+        <v>0.06872727272727272</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>980.7</v>
+      </c>
+      <c r="V32">
+        <v>1.452673677973634</v>
+      </c>
+      <c r="W32">
+        <v>0.1432851374234727</v>
+      </c>
+      <c r="X32">
+        <v>0.09220268165570586</v>
+      </c>
+      <c r="Y32">
+        <v>0.05108245576776685</v>
+      </c>
+      <c r="Z32">
+        <v>0.6299674267100978</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0.07273818012670738</v>
+      </c>
+      <c r="AC32">
+        <v>-0.07273818012670738</v>
+      </c>
+      <c r="AD32">
+        <v>709.9</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>709.9</v>
+      </c>
+      <c r="AG32">
+        <v>-270.8000000000001</v>
+      </c>
+      <c r="AH32">
+        <v>0.5125631768953068</v>
+      </c>
+      <c r="AI32">
+        <v>0.4541034990085077</v>
+      </c>
+      <c r="AJ32">
+        <v>-0.6697996537224835</v>
+      </c>
+      <c r="AK32">
+        <v>-0.4648129076553383</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>State Bank of India (NSEI:SBIN)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>0.266</v>
+      </c>
+      <c r="F33">
+        <v>0.266</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0.0001513414884226649</v>
+      </c>
+      <c r="J33">
+        <v>0.0001432775401942514</v>
+      </c>
+      <c r="K33">
+        <v>8209.6</v>
+      </c>
+      <c r="L33">
+        <v>0.240046783625731</v>
+      </c>
+      <c r="M33">
+        <v>1213.9</v>
+      </c>
+      <c r="N33">
+        <v>0.01765269603886822</v>
+      </c>
+      <c r="O33">
+        <v>0.1478634769050867</v>
+      </c>
+      <c r="P33">
+        <v>1213.9</v>
+      </c>
+      <c r="Q33">
+        <v>0.01765269603886822</v>
+      </c>
+      <c r="R33">
+        <v>0.1478634769050867</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>43601.7</v>
+      </c>
+      <c r="V33">
+        <v>0.6340617488079086</v>
+      </c>
+      <c r="W33">
+        <v>0.2005418068207079</v>
+      </c>
+      <c r="X33">
+        <v>0.09022588569746218</v>
+      </c>
+      <c r="Y33">
+        <v>0.1103159211232457</v>
+      </c>
+      <c r="Z33">
+        <v>0.4524059627381165</v>
+      </c>
+      <c r="AA33">
+        <v>6.481961351032951e-05</v>
+      </c>
+      <c r="AB33">
+        <v>0.07305872090646479</v>
+      </c>
+      <c r="AC33">
+        <v>-0.07299390129295445</v>
+      </c>
+      <c r="AD33">
+        <v>65946.2</v>
+      </c>
+      <c r="AE33">
+        <v>51.1206054797243</v>
+      </c>
+      <c r="AF33">
+        <v>65997.32060547972</v>
+      </c>
+      <c r="AG33">
+        <v>22395.62060547972</v>
+      </c>
+      <c r="AH33">
+        <v>0.4897287127355777</v>
+      </c>
+      <c r="AI33">
+        <v>0.5730917982586703</v>
+      </c>
+      <c r="AJ33">
+        <v>0.2456702081182172</v>
+      </c>
+      <c r="AK33">
+        <v>0.3129697443848381</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>0</v>
+      </c>
+      <c r="AN33">
+        <v>4282.220779220779</v>
+      </c>
+      <c r="AP33">
+        <v>1454.261078277904</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>HDFC Bank Limited (NSEI:HDFCBANK)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>0.228</v>
+      </c>
+      <c r="E34">
+        <v>0.214</v>
+      </c>
+      <c r="F34">
+        <v>0.173</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>-0.002629341429942053</v>
+      </c>
+      <c r="J34">
+        <v>-0.002031865521481964</v>
+      </c>
+      <c r="K34">
+        <v>6556.7</v>
+      </c>
+      <c r="L34">
+        <v>0.3480220171020016</v>
+      </c>
+      <c r="M34">
+        <v>1011.6</v>
+      </c>
+      <c r="N34">
+        <v>0.006530913701683925</v>
+      </c>
+      <c r="O34">
+        <v>0.1542849299190142</v>
+      </c>
+      <c r="P34">
+        <v>1011.6</v>
+      </c>
+      <c r="Q34">
+        <v>0.006530913701683925</v>
+      </c>
+      <c r="R34">
+        <v>0.1542849299190142</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>23486.4</v>
+      </c>
+      <c r="V34">
+        <v>0.1516287579707684</v>
+      </c>
+      <c r="W34">
+        <v>0.2033987163300316</v>
+      </c>
+      <c r="X34">
+        <v>0.08262751950421252</v>
+      </c>
+      <c r="Y34">
+        <v>0.1207711968258191</v>
+      </c>
+      <c r="Z34">
+        <v>0.3661277013330876</v>
+      </c>
+      <c r="AA34">
+        <v>-0.0007439222527981467</v>
+      </c>
+      <c r="AB34">
+        <v>0.07225823648253532</v>
+      </c>
+      <c r="AC34">
+        <v>-0.07300215873533347</v>
+      </c>
+      <c r="AD34">
+        <v>92826.3</v>
+      </c>
+      <c r="AE34">
+        <v>1172.682648029826</v>
+      </c>
+      <c r="AF34">
+        <v>93998.98264802984</v>
+      </c>
+      <c r="AG34">
+        <v>70512.58264802984</v>
+      </c>
+      <c r="AH34">
+        <v>0.3776681201741462</v>
+      </c>
+      <c r="AI34">
+        <v>0.6442024505052694</v>
+      </c>
+      <c r="AJ34">
+        <v>0.3128238338795594</v>
+      </c>
+      <c r="AK34">
+        <v>0.5759472856641688</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>0</v>
+      </c>
+      <c r="AN34">
+        <v>501.7637837837838</v>
+      </c>
+      <c r="AP34">
+        <v>381.1490953947559</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ESAF Small Finance Bank (NSEI:ESAFSFB)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>0.322</v>
+      </c>
+      <c r="E35">
+        <v>0.325</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>-0.003642077365832188</v>
+      </c>
+      <c r="J35">
+        <v>-0.002710895709515032</v>
+      </c>
+      <c r="K35">
+        <v>49.2</v>
+      </c>
+      <c r="L35">
+        <v>0.2063758389261745</v>
+      </c>
+      <c r="M35">
+        <v>-0</v>
+      </c>
+      <c r="N35">
+        <v>-0</v>
+      </c>
+      <c r="O35">
+        <v>-0</v>
+      </c>
+      <c r="P35">
+        <v>-0</v>
+      </c>
+      <c r="Q35">
+        <v>-0</v>
+      </c>
+      <c r="R35">
+        <v>-0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>116.7</v>
+      </c>
+      <c r="V35">
+        <v>0.273879371039662</v>
+      </c>
+      <c r="W35">
+        <v>0.2538699690402477</v>
+      </c>
+      <c r="X35">
+        <v>0.08640532192829606</v>
+      </c>
+      <c r="Y35">
+        <v>0.1674646471119516</v>
+      </c>
+      <c r="Z35">
+        <v>0.52448472891997</v>
+      </c>
+      <c r="AA35">
+        <v>-0.001421823401335301</v>
+      </c>
+      <c r="AB35">
+        <v>0.07228167326519887</v>
+      </c>
+      <c r="AC35">
+        <v>-0.07370349666653417</v>
+      </c>
+      <c r="AD35">
+        <v>293.9</v>
+      </c>
+      <c r="AE35">
+        <v>39.44135622007197</v>
+      </c>
+      <c r="AF35">
+        <v>333.3413562200719</v>
+      </c>
+      <c r="AG35">
+        <v>216.6413562200719</v>
+      </c>
+      <c r="AH35">
+        <v>0.4389296862620105</v>
+      </c>
+      <c r="AI35">
+        <v>0.5825188141275758</v>
+      </c>
+      <c r="AJ35">
+        <v>0.3370583736732429</v>
+      </c>
+      <c r="AK35">
+        <v>0.4755690197212578</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>0</v>
+      </c>
+      <c r="AN35">
+        <v>41.86609686609687</v>
+      </c>
+      <c r="AP35">
+        <v>30.8605920541413</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>DCB Bank Limited (NSEI:DCBBANK)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D36">
+        <v>0.114</v>
+      </c>
+      <c r="E36">
+        <v>0.141</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>-0.02003168947086388</v>
+      </c>
+      <c r="J36">
+        <v>-0.01486613274290504</v>
+      </c>
+      <c r="K36">
+        <v>61.4</v>
+      </c>
+      <c r="L36">
+        <v>0.2383540372670807</v>
+      </c>
+      <c r="M36">
+        <v>4.69</v>
+      </c>
+      <c r="N36">
+        <v>0.008608663729809106</v>
+      </c>
+      <c r="O36">
+        <v>0.07638436482084691</v>
+      </c>
+      <c r="P36">
+        <v>4.69</v>
+      </c>
+      <c r="Q36">
+        <v>0.008608663729809106</v>
+      </c>
+      <c r="R36">
+        <v>0.07638436482084691</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>324</v>
+      </c>
+      <c r="V36">
+        <v>0.5947136563876653</v>
+      </c>
+      <c r="W36">
+        <v>0.1181223547518276</v>
+      </c>
+      <c r="X36">
+        <v>0.09690664843879451</v>
+      </c>
+      <c r="Y36">
+        <v>0.02121570631303311</v>
+      </c>
+      <c r="Z36">
+        <v>0.3519121759919746</v>
+      </c>
+      <c r="AA36">
+        <v>-0.005231573122141253</v>
+      </c>
+      <c r="AB36">
+        <v>0.07198374473703259</v>
+      </c>
+      <c r="AC36">
+        <v>-0.07721531785917385</v>
+      </c>
+      <c r="AD36">
+        <v>624.7</v>
+      </c>
+      <c r="AE36">
+        <v>67.20081603847268</v>
+      </c>
+      <c r="AF36">
+        <v>691.9008160384727</v>
+      </c>
+      <c r="AG36">
+        <v>367.9008160384727</v>
+      </c>
+      <c r="AH36">
+        <v>0.5594730811732143</v>
+      </c>
+      <c r="AI36">
+        <v>0.5457918834513669</v>
+      </c>
+      <c r="AJ36">
+        <v>0.403090267449662</v>
+      </c>
+      <c r="AK36">
+        <v>0.3898489964042525</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>0</v>
+      </c>
+      <c r="AN36">
+        <v>75.44685990338165</v>
+      </c>
+      <c r="AP36">
+        <v>44.43246570512956</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/india/india_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/india/india_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.2</v>
+        <v>0.204</v>
       </c>
       <c r="E2">
-        <v>0.426</v>
+        <v>0.236</v>
       </c>
       <c r="F2">
-        <v>0.124</v>
+        <v>0.16</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,34 +603,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-0.0003204264215916764</v>
+        <v>-8.752715966162034E-06</v>
       </c>
       <c r="J2">
-        <v>-0.0002633701979225549</v>
+        <v>-7.264200032183426E-06</v>
       </c>
       <c r="K2">
-        <v>31432</v>
+        <v>44310.36</v>
       </c>
       <c r="L2">
-        <v>0.2643679417704208</v>
+        <v>0.2686904494085645</v>
       </c>
       <c r="M2">
-        <v>4726.599999999999</v>
+        <v>6540.409</v>
       </c>
       <c r="N2">
-        <v>0.01059409742059974</v>
+        <v>0.01147237496814159</v>
       </c>
       <c r="O2">
-        <v>0.1503754135912446</v>
+        <v>0.1476045105478719</v>
       </c>
       <c r="P2">
-        <v>4726.599999999999</v>
+        <v>6540.409</v>
       </c>
       <c r="Q2">
-        <v>0.01059409742059974</v>
+        <v>0.01147237496814159</v>
       </c>
       <c r="R2">
-        <v>0.1503754135912446</v>
+        <v>0.1476045105478719</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>123229.4</v>
+        <v>212919.6</v>
       </c>
       <c r="V2">
-        <v>0.2762036704358427</v>
+        <v>0.3734771769268131</v>
       </c>
       <c r="W2">
-        <v>0.1813486824008362</v>
+        <v>0.1514571846517385</v>
       </c>
       <c r="X2">
-        <v>0.08397535159092154</v>
+        <v>0.08396820144040923</v>
       </c>
       <c r="Y2">
-        <v>0.09737333080991467</v>
+        <v>0.06748898321132926</v>
       </c>
       <c r="Z2">
-        <v>0.3601716819656308</v>
+        <v>0.3786420074339238</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07528051039269536</v>
+        <v>0.07429490366926053</v>
       </c>
       <c r="AC2">
-        <v>-0.07528051039269536</v>
+        <v>-0.07432325576485892</v>
       </c>
       <c r="AD2">
-        <v>221300</v>
+        <v>314041.9</v>
       </c>
       <c r="AE2">
-        <v>2832.485336762501</v>
+        <v>3838.107152606133</v>
       </c>
       <c r="AF2">
-        <v>224132.4853367625</v>
+        <v>317880.0071526062</v>
       </c>
       <c r="AG2">
-        <v>100903.0853367625</v>
+        <v>104960.4071526061</v>
       </c>
       <c r="AH2">
-        <v>0.3343830687349275</v>
+        <v>0.3579807585819273</v>
       </c>
       <c r="AI2">
-        <v>0.5150713937805509</v>
+        <v>0.4991965924698539</v>
       </c>
       <c r="AJ2">
-        <v>0.1844470524130812</v>
+        <v>0.1554828237629138</v>
       </c>
       <c r="AK2">
-        <v>0.323491323324942</v>
+        <v>0.2476277872915299</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>418.8115064345193</v>
+        <v>409.8811242296177</v>
       </c>
       <c r="AP2">
-        <v>190.9596618788087</v>
+        <v>136.9921965295351</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank Limited (BSE:500247)</t>
+          <t>Equitas Small Finance Bank Limited (NSEI:EQUITASBNK)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.18</v>
+        <v>0.207</v>
       </c>
       <c r="E3">
-        <v>0.219</v>
+        <v>0.135</v>
       </c>
       <c r="F3">
-        <v>0.124</v>
+        <v>0.21</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,34 +734,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.002502484962749559</v>
+        <v>0.009910241927404235</v>
       </c>
       <c r="J3">
-        <v>0.001900046888016639</v>
+        <v>0.009910241927404235</v>
       </c>
       <c r="K3">
-        <v>2637.1</v>
+        <v>53.5</v>
       </c>
       <c r="L3">
-        <v>0.2949479358901229</v>
+        <v>0.110172981878089</v>
       </c>
       <c r="M3">
-        <v>11.9</v>
+        <v>13.6</v>
       </c>
       <c r="N3">
-        <v>0.0002867538976842816</v>
+        <v>0.01596244131455399</v>
       </c>
       <c r="O3">
-        <v>0.004512532706382011</v>
+        <v>0.2542056074766355</v>
       </c>
       <c r="P3">
-        <v>11.9</v>
+        <v>13.6</v>
       </c>
       <c r="Q3">
-        <v>0.0002867538976842816</v>
+        <v>0.01596244131455399</v>
       </c>
       <c r="R3">
-        <v>0.004512532706382011</v>
+        <v>0.2542056074766355</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,55 +770,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>5502.4</v>
+        <v>309.5</v>
       </c>
       <c r="V3">
-        <v>0.1325911467746211</v>
+        <v>0.3632629107981221</v>
       </c>
       <c r="W3">
-        <v>0.1813486824008362</v>
+        <v>0.08113436457385502</v>
       </c>
       <c r="X3">
-        <v>0.07900927968787748</v>
+        <v>0.07808347465864823</v>
       </c>
       <c r="Y3">
-        <v>0.1023394027129587</v>
+        <v>0.003050889915206786</v>
       </c>
       <c r="Z3">
-        <v>0.5544975386251275</v>
+        <v>0.5877953073424166</v>
       </c>
       <c r="AA3">
-        <v>0.001053571322677559</v>
+        <v>0.005825193699556276</v>
       </c>
       <c r="AB3">
-        <v>0.07490991140895015</v>
+        <v>0.07432915171901504</v>
       </c>
       <c r="AC3">
-        <v>-0.07385634008627259</v>
+        <v>-0.06850395801945876</v>
       </c>
       <c r="AD3">
-        <v>9198.9</v>
+        <v>129.5</v>
       </c>
       <c r="AE3">
-        <v>351.6276609827624</v>
+        <v>27.43793260026252</v>
       </c>
       <c r="AF3">
-        <v>9550.527660982762</v>
+        <v>156.9379326002625</v>
       </c>
       <c r="AG3">
-        <v>4048.127660982762</v>
+        <v>-152.5620673997375</v>
       </c>
       <c r="AH3">
-        <v>0.1870835656777731</v>
+        <v>0.155547658115894</v>
       </c>
       <c r="AI3">
-        <v>0.3519773392303962</v>
+        <v>0.1810464525121717</v>
       </c>
       <c r="AJ3">
-        <v>0.08887778151706649</v>
+        <v>-0.2181209515368515</v>
       </c>
       <c r="AK3">
-        <v>0.1871401652452154</v>
+        <v>-0.2737335079418666</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -827,10 +827,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>99.23300970873785</v>
+        <v>12.57281553398058</v>
       </c>
       <c r="AP3">
-        <v>43.66912255644835</v>
+        <v>-14.81185120385801</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ICICI Bank Limited (NSEI:ICICIBANK)</t>
+          <t>Fino Payments Bank Limited (NSEI:FINOPB)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -849,15 +849,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.148</v>
-      </c>
-      <c r="E4">
-        <v>0.479</v>
-      </c>
-      <c r="F4">
-        <v>0.109</v>
-      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -865,91 +856,88 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.0001034623517351131</v>
+        <v>0.002330448693050629</v>
       </c>
       <c r="J4">
-        <v>0.0001001988248201149</v>
+        <v>0.002216714829483799</v>
       </c>
       <c r="K4">
-        <v>5653.7</v>
+        <v>11.2</v>
       </c>
       <c r="L4">
-        <v>0.2890927405952947</v>
+        <v>0.05976520811099252</v>
       </c>
       <c r="M4">
-        <v>840.4</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.007949510581059657</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.1486460194209102</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>840.4</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.007949510581059657</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.1486460194209102</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>19620.4</v>
+        <v>107.7</v>
       </c>
       <c r="V4">
-        <v>0.1855932620235875</v>
+        <v>0.3489954633830201</v>
       </c>
       <c r="W4">
-        <v>0.2025689716947331</v>
+        <v>0.1570827489481066</v>
       </c>
       <c r="X4">
-        <v>0.07937851404164502</v>
+        <v>0.08083845606418216</v>
       </c>
       <c r="Y4">
-        <v>0.123190457653088</v>
+        <v>0.07624429288392442</v>
       </c>
       <c r="Z4">
-        <v>0.5549262069203064</v>
+        <v>1.741370766740776</v>
       </c>
       <c r="AA4">
-        <v>5.560295379529862E-05</v>
+        <v>0.003860122402263852</v>
       </c>
       <c r="AB4">
-        <v>0.07494253291126304</v>
+        <v>0.07429120620093109</v>
       </c>
       <c r="AC4">
-        <v>-0.07488692995746775</v>
+        <v>-0.07043108379866724</v>
       </c>
       <c r="AD4">
-        <v>26229.9</v>
+        <v>95</v>
       </c>
       <c r="AE4">
-        <v>49.38308912910957</v>
+        <v>4.316369574611561</v>
       </c>
       <c r="AF4">
-        <v>26279.28308912911</v>
+        <v>99.31636957461156</v>
       </c>
       <c r="AG4">
-        <v>6658.883089129111</v>
+        <v>-8.383630425388446</v>
       </c>
       <c r="AH4">
-        <v>0.1990907823762572</v>
+        <v>0.2434723805719831</v>
       </c>
       <c r="AI4">
-        <v>0.4268211088398172</v>
+        <v>0.5462454772745605</v>
       </c>
       <c r="AJ4">
-        <v>0.0592553406924473</v>
+        <v>-0.02792529413791641</v>
       </c>
       <c r="AK4">
-        <v>0.1587361386216598</v>
+        <v>-0.1131144236220152</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -958,10 +946,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>2204.193277310924</v>
+        <v>73.07692307692308</v>
       </c>
       <c r="AP4">
-        <v>559.5700074898413</v>
+        <v>-6.448946481068035</v>
       </c>
     </row>
     <row r="5">
@@ -972,7 +960,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Union Bank of India (NSEI:UNIONBANK)</t>
+          <t>Utkarsh Small Finance Bank Limited (NSEI:UTKARSHBNK)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -981,10 +969,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.7609999999999999</v>
-      </c>
-      <c r="F5">
-        <v>0.226</v>
+        <v>0.298</v>
+      </c>
+      <c r="E5">
+        <v>0.254</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -993,34 +981,34 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.00755566442756563</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>0.005713070514031232</v>
       </c>
       <c r="K5">
-        <v>1831.7</v>
+        <v>55.4</v>
       </c>
       <c r="L5">
-        <v>0.3069459572685379</v>
+        <v>0.2264922322158626</v>
       </c>
       <c r="M5">
-        <v>328</v>
+        <v>6.57</v>
       </c>
       <c r="N5">
-        <v>0.03054913940838984</v>
+        <v>0.01501714285714286</v>
       </c>
       <c r="O5">
-        <v>0.1790686247747994</v>
+        <v>0.1185920577617329</v>
       </c>
       <c r="P5">
-        <v>328</v>
+        <v>6.57</v>
       </c>
       <c r="Q5">
-        <v>0.03054913940838984</v>
+        <v>0.01501714285714286</v>
       </c>
       <c r="R5">
-        <v>0.1790686247747994</v>
+        <v>0.1185920577617329</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1029,61 +1017,67 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>12510</v>
+        <v>387.3</v>
       </c>
       <c r="V5">
-        <v>1.1651516280456</v>
+        <v>0.8852571428571429</v>
       </c>
       <c r="W5">
-        <v>0.168456968381555</v>
+        <v>0.1712519319938176</v>
       </c>
       <c r="X5">
-        <v>0.0801750038194244</v>
+        <v>0.0868029228754483</v>
       </c>
       <c r="Y5">
-        <v>0.0882819645621306</v>
+        <v>0.08444900911836931</v>
       </c>
       <c r="Z5">
-        <v>1.494789840188368</v>
+        <v>0.6299911499502481</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>0.003599183862881391</v>
       </c>
       <c r="AB5">
-        <v>0.07500972185060015</v>
+        <v>0.07423114710532405</v>
       </c>
       <c r="AC5">
-        <v>-0.07500972185060015</v>
+        <v>-0.07063196324244266</v>
       </c>
       <c r="AD5">
-        <v>3096.1</v>
+        <v>238.4</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>32.75942240508724</v>
       </c>
       <c r="AF5">
-        <v>3096.1</v>
+        <v>271.1594224050872</v>
       </c>
       <c r="AG5">
-        <v>-9413.9</v>
+        <v>-116.1405775949128</v>
       </c>
       <c r="AH5">
-        <v>0.2238214691062612</v>
+        <v>0.3826371509812309</v>
       </c>
       <c r="AI5">
-        <v>0.194150587261474</v>
+        <v>0.4209507972306977</v>
       </c>
       <c r="AJ5">
-        <v>-7.116108549399049</v>
+        <v>-0.3614039903535569</v>
       </c>
       <c r="AK5">
-        <v>-2.739067182635515</v>
+        <v>-0.4521561892004494</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>28.38095238095238</v>
+      </c>
+      <c r="AP5">
+        <v>-13.82625923748961</v>
       </c>
     </row>
     <row r="6">
@@ -1094,7 +1088,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Indian Bank (NSEI:INDIANB)</t>
+          <t>IDFC First Bank Limited (BSE:539437)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1103,13 +1097,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.399</v>
-      </c>
-      <c r="E6">
-        <v>0.645</v>
+        <v>0.385</v>
       </c>
       <c r="F6">
-        <v>0.19</v>
+        <v>0.214</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1118,97 +1109,100 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>0.007818744319125402</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>0.007818744319125402</v>
       </c>
       <c r="K6">
-        <v>1178.2</v>
+        <v>276.7</v>
       </c>
       <c r="L6">
-        <v>0.3466415605048692</v>
+        <v>0.1177797641850764</v>
       </c>
       <c r="M6">
-        <v>280.5</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.03362906126363745</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.2380750297063317</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>280.5</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.03362906126363745</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.2380750297063317</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>784.5</v>
+        <v>1740.6</v>
       </c>
       <c r="V6">
-        <v>0.09405347080685769</v>
+        <v>0.3222497870922353</v>
       </c>
       <c r="W6">
-        <v>0.1833546017616484</v>
+        <v>0.08280216656192955</v>
       </c>
       <c r="X6">
-        <v>0.08397535159092154</v>
+        <v>0.09580214394931896</v>
       </c>
       <c r="Y6">
-        <v>0.09937925017072682</v>
+        <v>-0.01299997738738941</v>
       </c>
       <c r="Z6">
-        <v>0.4319079992375627</v>
+        <v>0.2797799210436433</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>0.00218752766826534</v>
       </c>
       <c r="AB6">
-        <v>0.07528051039269536</v>
+        <v>0.07290720339208558</v>
       </c>
       <c r="AC6">
-        <v>-0.07528051039269536</v>
+        <v>-0.07071967572382024</v>
       </c>
       <c r="AD6">
-        <v>3988.5</v>
+        <v>5532.4</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>243.6571198553934</v>
       </c>
       <c r="AF6">
-        <v>3988.5</v>
+        <v>5776.057119855393</v>
       </c>
       <c r="AG6">
-        <v>3204</v>
+        <v>4035.457119855394</v>
       </c>
       <c r="AH6">
-        <v>0.3234924368384768</v>
+        <v>0.5167594970769274</v>
       </c>
       <c r="AI6">
-        <v>0.3352751298734049</v>
+        <v>0.5668715947348567</v>
       </c>
       <c r="AJ6">
-        <v>0.2775227371156345</v>
+        <v>0.4276272352756816</v>
       </c>
       <c r="AK6">
-        <v>0.2883447177299603</v>
+        <v>0.4776391441495791</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
         <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>82.45007451564828</v>
+      </c>
+      <c r="AP6">
+        <v>60.14094068338888</v>
       </c>
     </row>
     <row r="7">
@@ -1219,7 +1213,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>State Bank of India (NSEI:SBIN)</t>
+          <t>IndusInd Bank Limited (NSEI:INDUSINDBK)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1228,13 +1222,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.187</v>
+        <v>0.144</v>
       </c>
       <c r="E7">
-        <v>0.423</v>
+        <v>0.143</v>
       </c>
       <c r="F7">
-        <v>0.0732</v>
+        <v>0.106</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1243,34 +1237,34 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0.0002006638300458489</v>
+        <v>0.004228062448729071</v>
       </c>
       <c r="J7">
-        <v>0.0001501056046164344</v>
+        <v>0.003169499706384916</v>
       </c>
       <c r="K7">
-        <v>8540.700000000001</v>
+        <v>973.1</v>
       </c>
       <c r="L7">
-        <v>0.2129473335145149</v>
+        <v>0.3116812401908972</v>
       </c>
       <c r="M7">
-        <v>1459.3</v>
+        <v>153.4</v>
       </c>
       <c r="N7">
-        <v>0.01760298767079168</v>
+        <v>0.01755068417921377</v>
       </c>
       <c r="O7">
-        <v>0.1708642148770007</v>
+        <v>0.1576405302641044</v>
       </c>
       <c r="P7">
-        <v>1459.3</v>
+        <v>153.4</v>
       </c>
       <c r="Q7">
-        <v>0.01760298767079168</v>
+        <v>0.01755068417921377</v>
       </c>
       <c r="R7">
-        <v>0.1708642148770007</v>
+        <v>0.1576405302641044</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1279,55 +1273,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>42368.3</v>
+        <v>5492.5</v>
       </c>
       <c r="V7">
-        <v>0.5110728859949314</v>
+        <v>0.6284037343828658</v>
       </c>
       <c r="W7">
-        <v>0.1800285829918551</v>
+        <v>0.138452563883672</v>
       </c>
       <c r="X7">
-        <v>0.09190150857624615</v>
+        <v>0.08708223613501695</v>
       </c>
       <c r="Y7">
-        <v>0.08812707441560896</v>
+        <v>0.05137032774865502</v>
       </c>
       <c r="Z7">
-        <v>0.5742953687798537</v>
+        <v>0.4306940176732314</v>
       </c>
       <c r="AA7">
-        <v>8.62049535591181E-05</v>
+        <v>0.001365084562557047</v>
       </c>
       <c r="AB7">
-        <v>0.07566877010844369</v>
+        <v>0.07327849220556926</v>
       </c>
       <c r="AC7">
-        <v>-0.07558256515488458</v>
+        <v>-0.07191340764301221</v>
       </c>
       <c r="AD7">
-        <v>72409.2</v>
+        <v>5337.2</v>
       </c>
       <c r="AE7">
-        <v>51.75977850984066</v>
+        <v>201.9978311441149</v>
       </c>
       <c r="AF7">
-        <v>72460.95977850984</v>
+        <v>5539.197831144114</v>
       </c>
       <c r="AG7">
-        <v>30092.65977850984</v>
+        <v>46.69783114411439</v>
       </c>
       <c r="AH7">
-        <v>0.4664018129171204</v>
+        <v>0.38790993252366</v>
       </c>
       <c r="AI7">
-        <v>0.5580399265278486</v>
+        <v>0.4139569040629681</v>
       </c>
       <c r="AJ7">
-        <v>0.2663223736111363</v>
+        <v>0.005314363404331661</v>
       </c>
       <c r="AK7">
-        <v>0.3439917514971363</v>
+        <v>0.00591966178827773</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1336,10 +1330,10 @@
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>3935.282608695652</v>
+        <v>99.57462686567163</v>
       </c>
       <c r="AP7">
-        <v>1635.470640136405</v>
+        <v>0.8712281929872088</v>
       </c>
     </row>
     <row r="8">
@@ -1350,7 +1344,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Axis Bank Limited (BSE:532215)</t>
+          <t>RBL Bank Limited (NSEI:RBLBANK)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1359,13 +1353,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.2</v>
+        <v>0.159</v>
       </c>
       <c r="E8">
-        <v>0.429</v>
+        <v>0.0919</v>
       </c>
       <c r="F8">
-        <v>0.109</v>
+        <v>0.183</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1374,34 +1368,34 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>-0.0003388586606527946</v>
+        <v>0.007767637629231984</v>
       </c>
       <c r="J8">
-        <v>-0.0003388586606527946</v>
+        <v>0.005842150288793401</v>
       </c>
       <c r="K8">
-        <v>3333.4</v>
+        <v>142.3</v>
       </c>
       <c r="L8">
-        <v>0.4183116443083565</v>
+        <v>0.1497421866778912</v>
       </c>
       <c r="M8">
-        <v>36.9</v>
+        <v>10.9</v>
       </c>
       <c r="N8">
-        <v>0.0009579737686532289</v>
+        <v>0.0097139292398182</v>
       </c>
       <c r="O8">
-        <v>0.01106977860442791</v>
+        <v>0.07659873506676036</v>
       </c>
       <c r="P8">
-        <v>36.9</v>
+        <v>10.9</v>
       </c>
       <c r="Q8">
-        <v>0.0009579737686532289</v>
+        <v>0.0097139292398182</v>
       </c>
       <c r="R8">
-        <v>0.01106977860442791</v>
+        <v>0.07659873506676036</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1410,55 +1404,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>10648.9</v>
+        <v>1507.9</v>
       </c>
       <c r="V8">
-        <v>0.2764598066398745</v>
+        <v>1.343819623919437</v>
       </c>
       <c r="W8">
-        <v>0.1944977681827464</v>
+        <v>0.0836173463391703</v>
       </c>
       <c r="X8">
-        <v>0.08877276877077997</v>
+        <v>0.1071614482177789</v>
       </c>
       <c r="Y8">
-        <v>0.1057249994119665</v>
+        <v>-0.02354410187860859</v>
       </c>
       <c r="Z8">
-        <v>0.2167592794624918</v>
+        <v>0.3577812722696293</v>
       </c>
       <c r="AA8">
-        <v>-7.345075912272477E-05</v>
+        <v>0.002090211963114885</v>
       </c>
       <c r="AB8">
-        <v>0.07553688842932027</v>
+        <v>0.07412838196794622</v>
       </c>
       <c r="AC8">
-        <v>-0.075610339188443</v>
+        <v>-0.07203817000483133</v>
       </c>
       <c r="AD8">
-        <v>26881.2</v>
+        <v>1752.1</v>
       </c>
       <c r="AE8">
-        <v>767.5013150457197</v>
+        <v>84.59206980470422</v>
       </c>
       <c r="AF8">
-        <v>27648.70131504572</v>
+        <v>1836.692069804704</v>
       </c>
       <c r="AG8">
-        <v>16999.80131504572</v>
+        <v>328.7920698047039</v>
       </c>
       <c r="AH8">
-        <v>0.4178592324863675</v>
+        <v>0.6207573991253585</v>
       </c>
       <c r="AI8">
-        <v>0.5724866460892999</v>
+        <v>0.4982491986594025</v>
       </c>
       <c r="AJ8">
-        <v>0.30620010072982</v>
+        <v>0.2266137341621564</v>
       </c>
       <c r="AK8">
-        <v>0.4515591116725373</v>
+        <v>0.1509333762099954</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1467,10 +1461,10 @@
         <v>0</v>
       </c>
       <c r="AN8">
-        <v>178.2572944297082</v>
+        <v>72.10288065843621</v>
       </c>
       <c r="AP8">
-        <v>112.7307779512315</v>
+        <v>13.53053785204543</v>
       </c>
     </row>
     <row r="9">
@@ -1481,127 +1475,3597 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Suryoday Small Finance Bank Limited (NSEI:SURYODAY)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.233</v>
+      </c>
+      <c r="E9">
+        <v>0.119</v>
+      </c>
+      <c r="F9">
+        <v>0.27</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0.007367195870930693</v>
+      </c>
+      <c r="J9">
+        <v>0.005560336179008666</v>
+      </c>
+      <c r="K9">
+        <v>27.9</v>
+      </c>
+      <c r="L9">
+        <v>0.2051470588235294</v>
+      </c>
+      <c r="M9">
+        <v>-0</v>
+      </c>
+      <c r="N9">
+        <v>-0</v>
+      </c>
+      <c r="O9">
+        <v>-0</v>
+      </c>
+      <c r="P9">
+        <v>-0</v>
+      </c>
+      <c r="Q9">
+        <v>-0</v>
+      </c>
+      <c r="R9">
+        <v>-0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>93.3</v>
+      </c>
+      <c r="V9">
+        <v>0.5543672014260249</v>
+      </c>
+      <c r="W9">
+        <v>0.1376418352244697</v>
+      </c>
+      <c r="X9">
+        <v>0.1058247010714964</v>
+      </c>
+      <c r="Y9">
+        <v>0.0318171341529733</v>
+      </c>
+      <c r="Z9">
+        <v>0.3167650412587343</v>
+      </c>
+      <c r="AA9">
+        <v>0.001761320119156113</v>
+      </c>
+      <c r="AB9">
+        <v>0.07413263467822059</v>
+      </c>
+      <c r="AC9">
+        <v>-0.07237131455906448</v>
+      </c>
+      <c r="AD9">
+        <v>260</v>
+      </c>
+      <c r="AE9">
+        <v>4.240306807767129</v>
+      </c>
+      <c r="AF9">
+        <v>264.2403068077671</v>
+      </c>
+      <c r="AG9">
+        <v>170.9403068077671</v>
+      </c>
+      <c r="AH9">
+        <v>0.610903313862037</v>
+      </c>
+      <c r="AI9">
+        <v>0.5348557661522625</v>
+      </c>
+      <c r="AJ9">
+        <v>0.5038914992628857</v>
+      </c>
+      <c r="AK9">
+        <v>0.4265613014309694</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>140.5405405405405</v>
+      </c>
+      <c r="AP9">
+        <v>92.40016584203627</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>The Federal Bank Limited (NSEI:FEDERALBNK)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.197</v>
+      </c>
+      <c r="E10">
+        <v>0.215</v>
+      </c>
+      <c r="F10">
+        <v>0.15</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>2.859118960503125E-05</v>
+      </c>
+      <c r="J10">
+        <v>2.142427476644467E-05</v>
+      </c>
+      <c r="K10">
+        <v>492.9</v>
+      </c>
+      <c r="L10">
+        <v>0.3148917140484252</v>
+      </c>
+      <c r="M10">
+        <v>35.1</v>
+      </c>
+      <c r="N10">
+        <v>0.006121381234740147</v>
+      </c>
+      <c r="O10">
+        <v>0.07121119902617164</v>
+      </c>
+      <c r="P10">
+        <v>35.1</v>
+      </c>
+      <c r="Q10">
+        <v>0.006121381234740147</v>
+      </c>
+      <c r="R10">
+        <v>0.07121119902617164</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>2782.9</v>
+      </c>
+      <c r="V10">
+        <v>0.4853331008022323</v>
+      </c>
+      <c r="W10">
+        <v>0.1527945689575002</v>
+      </c>
+      <c r="X10">
+        <v>0.08786543808311111</v>
+      </c>
+      <c r="Y10">
+        <v>0.0649291308743891</v>
+      </c>
+      <c r="Z10">
+        <v>0.4033393466553099</v>
+      </c>
+      <c r="AA10">
+        <v>8.641252986861634E-06</v>
+      </c>
+      <c r="AB10">
+        <v>0.07323723996458567</v>
+      </c>
+      <c r="AC10">
+        <v>-0.07322859871159881</v>
+      </c>
+      <c r="AD10">
+        <v>3858.2</v>
+      </c>
+      <c r="AE10">
+        <v>0.05123105455622288</v>
+      </c>
+      <c r="AF10">
+        <v>3858.251231054556</v>
+      </c>
+      <c r="AG10">
+        <v>1075.351231054556</v>
+      </c>
+      <c r="AH10">
+        <v>0.4022258318843455</v>
+      </c>
+      <c r="AI10">
+        <v>0.491813284419349</v>
+      </c>
+      <c r="AJ10">
+        <v>0.1579227145972933</v>
+      </c>
+      <c r="AK10">
+        <v>0.2124338893406522</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>70149.09090909091</v>
+      </c>
+      <c r="AP10">
+        <v>19551.84056462829</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bank of Maharashtra (NSEI:MAHABANK)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>584.4</v>
+      </c>
+      <c r="L11">
+        <v>0.4855837141670128</v>
+      </c>
+      <c r="M11">
+        <v>118.3</v>
+      </c>
+      <c r="N11">
+        <v>0.02522065407410565</v>
+      </c>
+      <c r="O11">
+        <v>0.2024298425735797</v>
+      </c>
+      <c r="P11">
+        <v>118.3</v>
+      </c>
+      <c r="Q11">
+        <v>0.02522065407410565</v>
+      </c>
+      <c r="R11">
+        <v>0.2024298425735797</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>1980.8</v>
+      </c>
+      <c r="V11">
+        <v>0.4222913912932247</v>
+      </c>
+      <c r="W11">
+        <v>0.2611260053619303</v>
+      </c>
+      <c r="X11">
+        <v>0.07973542009502112</v>
+      </c>
+      <c r="Y11">
+        <v>0.1813905852669092</v>
+      </c>
+      <c r="Z11">
+        <v>0.8009450286170638</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.07378953055035543</v>
+      </c>
+      <c r="AC11">
+        <v>-0.07378953055035543</v>
+      </c>
+      <c r="AD11">
+        <v>1251.1</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>1251.1</v>
+      </c>
+      <c r="AG11">
+        <v>-729.7</v>
+      </c>
+      <c r="AH11">
+        <v>0.2105626335897133</v>
+      </c>
+      <c r="AI11">
+        <v>0.3140941956216108</v>
+      </c>
+      <c r="AJ11">
+        <v>-0.1842258072660254</v>
+      </c>
+      <c r="AK11">
+        <v>-0.3644127047542949</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kotak Mahindra Bank Limited (BSE:500247)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.18</v>
+      </c>
+      <c r="E12">
+        <v>0.219</v>
+      </c>
+      <c r="F12">
+        <v>0.124</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0.002502484962749559</v>
+      </c>
+      <c r="J12">
+        <v>0.001900046888016639</v>
+      </c>
+      <c r="K12">
+        <v>2637.1</v>
+      </c>
+      <c r="L12">
+        <v>0.2949479358901229</v>
+      </c>
+      <c r="M12">
+        <v>11.9</v>
+      </c>
+      <c r="N12">
+        <v>0.0002867538976842816</v>
+      </c>
+      <c r="O12">
+        <v>0.004512532706382011</v>
+      </c>
+      <c r="P12">
+        <v>11.9</v>
+      </c>
+      <c r="Q12">
+        <v>0.0002867538976842816</v>
+      </c>
+      <c r="R12">
+        <v>0.004512532706382011</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>5502.4</v>
+      </c>
+      <c r="V12">
+        <v>0.1325911467746211</v>
+      </c>
+      <c r="W12">
+        <v>0.1813486824008362</v>
+      </c>
+      <c r="X12">
+        <v>0.07900305967055535</v>
+      </c>
+      <c r="Y12">
+        <v>0.1023456227302809</v>
+      </c>
+      <c r="Z12">
+        <v>0.5544975386251275</v>
+      </c>
+      <c r="AA12">
+        <v>0.001053571322677559</v>
+      </c>
+      <c r="AB12">
+        <v>0.07490485505464722</v>
+      </c>
+      <c r="AC12">
+        <v>-0.07385128373196967</v>
+      </c>
+      <c r="AD12">
+        <v>9198.9</v>
+      </c>
+      <c r="AE12">
+        <v>351.6276609827624</v>
+      </c>
+      <c r="AF12">
+        <v>9550.527660982762</v>
+      </c>
+      <c r="AG12">
+        <v>4048.127660982762</v>
+      </c>
+      <c r="AH12">
+        <v>0.1870835656777731</v>
+      </c>
+      <c r="AI12">
+        <v>0.3519773392303962</v>
+      </c>
+      <c r="AJ12">
+        <v>0.08887778151706649</v>
+      </c>
+      <c r="AK12">
+        <v>0.1871401652452154</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>99.23300970873785</v>
+      </c>
+      <c r="AP12">
+        <v>43.66912255644835</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ESAF Small Finance Bank (NSEI:ESAFSFB)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.204</v>
+      </c>
+      <c r="E13">
+        <v>-0.292</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0.0007447351233759866</v>
+      </c>
+      <c r="J13">
+        <v>0.0005428004369942115</v>
+      </c>
+      <c r="K13">
+        <v>3.36</v>
+      </c>
+      <c r="L13">
+        <v>0.01462140992167102</v>
+      </c>
+      <c r="M13">
+        <v>4.3</v>
+      </c>
+      <c r="N13">
+        <v>0.01700276789244761</v>
+      </c>
+      <c r="O13">
+        <v>1.279761904761905</v>
+      </c>
+      <c r="P13">
+        <v>4.3</v>
+      </c>
+      <c r="Q13">
+        <v>0.01700276789244761</v>
+      </c>
+      <c r="R13">
+        <v>1.279761904761905</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>133.2</v>
+      </c>
+      <c r="V13">
+        <v>0.5266903914590747</v>
+      </c>
+      <c r="W13">
+        <v>0.01406446211804102</v>
+      </c>
+      <c r="X13">
+        <v>0.09801461683092011</v>
+      </c>
+      <c r="Y13">
+        <v>-0.08395015471287909</v>
+      </c>
+      <c r="Z13">
+        <v>0.5007689141680002</v>
+      </c>
+      <c r="AA13">
+        <v>0.0002718175854435073</v>
+      </c>
+      <c r="AB13">
+        <v>0.07416268993621918</v>
+      </c>
+      <c r="AC13">
+        <v>-0.07389087235077567</v>
+      </c>
+      <c r="AD13">
+        <v>255.6</v>
+      </c>
+      <c r="AE13">
+        <v>42.79429934324099</v>
+      </c>
+      <c r="AF13">
+        <v>298.394299343241</v>
+      </c>
+      <c r="AG13">
+        <v>165.194299343241</v>
+      </c>
+      <c r="AH13">
+        <v>0.5412613547767848</v>
+      </c>
+      <c r="AI13">
+        <v>0.5165263006446044</v>
+      </c>
+      <c r="AJ13">
+        <v>0.3951125370585887</v>
+      </c>
+      <c r="AK13">
+        <v>0.371645484739225</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>29.27835051546392</v>
+      </c>
+      <c r="AP13">
+        <v>18.92260015386494</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bank of India Limited (NSEI:BANKINDIA)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.339</v>
+      </c>
+      <c r="F14">
+        <v>0.208</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>932.6</v>
+      </c>
+      <c r="L14">
+        <v>0.2991499599037691</v>
+      </c>
+      <c r="M14">
+        <v>152.2</v>
+      </c>
+      <c r="N14">
+        <v>0.02806926949818343</v>
+      </c>
+      <c r="O14">
+        <v>0.1631996568732575</v>
+      </c>
+      <c r="P14">
+        <v>152.2</v>
+      </c>
+      <c r="Q14">
+        <v>0.02806926949818343</v>
+      </c>
+      <c r="R14">
+        <v>0.1631996568732575</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>9762.1</v>
+      </c>
+      <c r="V14">
+        <v>1.800361470224812</v>
+      </c>
+      <c r="W14">
+        <v>0.1240803076063384</v>
+      </c>
+      <c r="X14">
+        <v>0.1267657161824507</v>
+      </c>
+      <c r="Y14">
+        <v>-0.002685408576112297</v>
+      </c>
+      <c r="Z14">
+        <v>0.5768874907475944</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0.07408405605819199</v>
+      </c>
+      <c r="AC14">
+        <v>-0.07408405605819199</v>
+      </c>
+      <c r="AD14">
+        <v>14185.8</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>14185.8</v>
+      </c>
+      <c r="AG14">
+        <v>4423.699999999999</v>
+      </c>
+      <c r="AH14">
+        <v>0.723466322591174</v>
+      </c>
+      <c r="AI14">
+        <v>0.6162701791579057</v>
+      </c>
+      <c r="AJ14">
+        <v>0.4492890513914279</v>
+      </c>
+      <c r="AK14">
+        <v>0.3336954143942308</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Bank of Baroda Limited (NSEI:BANKBARODA)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>0.272</v>
+      </c>
+      <c r="E15">
+        <v>0.6729999999999999</v>
+      </c>
+      <c r="F15">
+        <v>0.0551</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0.0002252681092639055</v>
+      </c>
+      <c r="J15">
+        <v>0.0001639559590431701</v>
+      </c>
+      <c r="K15">
+        <v>2387.6</v>
+      </c>
+      <c r="L15">
+        <v>0.3180455835142731</v>
+      </c>
+      <c r="M15">
+        <v>470.5</v>
+      </c>
+      <c r="N15">
+        <v>0.03236835949861721</v>
+      </c>
+      <c r="O15">
+        <v>0.1970598090132351</v>
+      </c>
+      <c r="P15">
+        <v>470.5</v>
+      </c>
+      <c r="Q15">
+        <v>0.03236835949861721</v>
+      </c>
+      <c r="R15">
+        <v>0.1970598090132351</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>12451.7</v>
+      </c>
+      <c r="V15">
+        <v>0.856622958488697</v>
+      </c>
+      <c r="W15">
+        <v>0.1742036218243372</v>
+      </c>
+      <c r="X15">
+        <v>0.09333787190825449</v>
+      </c>
+      <c r="Y15">
+        <v>0.08086574991608267</v>
+      </c>
+      <c r="Z15">
+        <v>0.3428949451863981</v>
+      </c>
+      <c r="AA15">
+        <v>5.621966958909112E-05</v>
+      </c>
+      <c r="AB15">
+        <v>0.07418645564819858</v>
+      </c>
+      <c r="AC15">
+        <v>-0.07413023597860949</v>
+      </c>
+      <c r="AD15">
+        <v>13738.6</v>
+      </c>
+      <c r="AE15">
+        <v>15.99444888472467</v>
+      </c>
+      <c r="AF15">
+        <v>13754.59444888473</v>
+      </c>
+      <c r="AG15">
+        <v>1302.894448884725</v>
+      </c>
+      <c r="AH15">
+        <v>0.4861930954598961</v>
+      </c>
+      <c r="AI15">
+        <v>0.4580880298068742</v>
+      </c>
+      <c r="AJ15">
+        <v>0.0822602174118251</v>
+      </c>
+      <c r="AK15">
+        <v>0.07413595118023578</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>2809.529652351739</v>
+      </c>
+      <c r="AP15">
+        <v>266.4405825940132</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Canara Bank (NSEI:CANBK)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>0.419</v>
+      </c>
+      <c r="E16">
+        <v>0.86</v>
+      </c>
+      <c r="F16">
+        <v>0.17</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>1909.4</v>
+      </c>
+      <c r="L16">
+        <v>0.2611323851203501</v>
+      </c>
+      <c r="M16">
+        <v>348.6</v>
+      </c>
+      <c r="N16">
+        <v>0.03285022333628602</v>
+      </c>
+      <c r="O16">
+        <v>0.1825704409762229</v>
+      </c>
+      <c r="P16">
+        <v>348.6</v>
+      </c>
+      <c r="Q16">
+        <v>0.03285022333628602</v>
+      </c>
+      <c r="R16">
+        <v>0.1825704409762229</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>19443.5</v>
+      </c>
+      <c r="V16">
+        <v>1.8322527752125</v>
+      </c>
+      <c r="W16">
+        <v>0.1854776822575162</v>
+      </c>
+      <c r="X16">
+        <v>0.09573335706511754</v>
+      </c>
+      <c r="Y16">
+        <v>0.08974432519239861</v>
+      </c>
+      <c r="Z16">
+        <v>1.878773863665561</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0.07417361105326126</v>
+      </c>
+      <c r="AC16">
+        <v>-0.07417361105326126</v>
+      </c>
+      <c r="AD16">
+        <v>11311.4</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>11311.4</v>
+      </c>
+      <c r="AG16">
+        <v>-8132.1</v>
+      </c>
+      <c r="AH16">
+        <v>0.5159556998978252</v>
+      </c>
+      <c r="AI16">
+        <v>0.4777358713693822</v>
+      </c>
+      <c r="AJ16">
+        <v>-3.279469290639998</v>
+      </c>
+      <c r="AK16">
+        <v>-1.920847505668934</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Punjab National Bank (NSEI:PNB)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>0.299</v>
+      </c>
+      <c r="F17">
+        <v>0.238</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>1726.5</v>
+      </c>
+      <c r="L17">
+        <v>0.3083586354706198</v>
+      </c>
+      <c r="M17">
+        <v>197.1</v>
+      </c>
+      <c r="N17">
+        <v>0.01427971136291187</v>
+      </c>
+      <c r="O17">
+        <v>0.1141615986099044</v>
+      </c>
+      <c r="P17">
+        <v>197.1</v>
+      </c>
+      <c r="Q17">
+        <v>0.01427971136291187</v>
+      </c>
+      <c r="R17">
+        <v>0.1141615986099044</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>14157.4</v>
+      </c>
+      <c r="V17">
+        <v>1.025690439620947</v>
+      </c>
+      <c r="W17">
+        <v>0.1350231099501826</v>
+      </c>
+      <c r="X17">
+        <v>0.09075312275579099</v>
+      </c>
+      <c r="Y17">
+        <v>0.04426998719439161</v>
+      </c>
+      <c r="Z17">
+        <v>0.6112111784291252</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0.07420221266177812</v>
+      </c>
+      <c r="AC17">
+        <v>-0.07420221266177812</v>
+      </c>
+      <c r="AD17">
+        <v>11278.7</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>11278.7</v>
+      </c>
+      <c r="AG17">
+        <v>-2878.699999999999</v>
+      </c>
+      <c r="AH17">
+        <v>0.4496820365608118</v>
+      </c>
+      <c r="AI17">
+        <v>0.4261291078215794</v>
+      </c>
+      <c r="AJ17">
+        <v>-0.2635182761051252</v>
+      </c>
+      <c r="AK17">
+        <v>-0.2338429295554977</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>UCO Bank (NSEI:UCOBANK)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>261.1</v>
+      </c>
+      <c r="L18">
+        <v>0.2028906674955319</v>
+      </c>
+      <c r="M18">
+        <v>-0</v>
+      </c>
+      <c r="N18">
+        <v>-0</v>
+      </c>
+      <c r="O18">
+        <v>-0</v>
+      </c>
+      <c r="P18">
+        <v>-0</v>
+      </c>
+      <c r="Q18">
+        <v>-0</v>
+      </c>
+      <c r="R18">
+        <v>-0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>1230.1</v>
+      </c>
+      <c r="V18">
+        <v>0.2007048573153421</v>
+      </c>
+      <c r="W18">
+        <v>0.08259782986934928</v>
+      </c>
+      <c r="X18">
+        <v>0.08286617217842322</v>
+      </c>
+      <c r="Y18">
+        <v>-0.0002683423090739379</v>
+      </c>
+      <c r="Z18">
+        <v>0.2263875450787229</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0.07426796651163417</v>
+      </c>
+      <c r="AC18">
+        <v>-0.07426796651163417</v>
+      </c>
+      <c r="AD18">
+        <v>2593.3</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>2593.3</v>
+      </c>
+      <c r="AG18">
+        <v>1363.2</v>
+      </c>
+      <c r="AH18">
+        <v>0.2973217766159914</v>
+      </c>
+      <c r="AI18">
+        <v>0.4368251722337325</v>
+      </c>
+      <c r="AJ18">
+        <v>0.1819516557440504</v>
+      </c>
+      <c r="AK18">
+        <v>0.2896358305358433</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Punjab &amp; Sind Bank (BSE:533295)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>0.314</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>80.5</v>
+      </c>
+      <c r="L19">
+        <v>0.1834130781499203</v>
+      </c>
+      <c r="M19">
+        <v>16.2</v>
+      </c>
+      <c r="N19">
+        <v>0.004258787034359473</v>
+      </c>
+      <c r="O19">
+        <v>0.2012422360248447</v>
+      </c>
+      <c r="P19">
+        <v>16.2</v>
+      </c>
+      <c r="Q19">
+        <v>0.004258787034359473</v>
+      </c>
+      <c r="R19">
+        <v>0.2012422360248447</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>818.2</v>
+      </c>
+      <c r="V19">
+        <v>0.2150950340440075</v>
+      </c>
+      <c r="W19">
+        <v>0.04422590924074277</v>
+      </c>
+      <c r="X19">
+        <v>0.08054216240938264</v>
+      </c>
+      <c r="Y19">
+        <v>-0.03631625316863987</v>
+      </c>
+      <c r="Z19">
+        <v>0.223006961028403</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0.07429490366926053</v>
+      </c>
+      <c r="AC19">
+        <v>-0.07429490366926053</v>
+      </c>
+      <c r="AD19">
+        <v>1167.9</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>1167.9</v>
+      </c>
+      <c r="AG19">
+        <v>349.7</v>
+      </c>
+      <c r="AH19">
+        <v>0.2349048634297438</v>
+      </c>
+      <c r="AI19">
+        <v>0.4580538886927875</v>
+      </c>
+      <c r="AJ19">
+        <v>0.08419202619414484</v>
+      </c>
+      <c r="AK19">
+        <v>0.2019636153624026</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>City Union Bank Limited (NSEI:CUB)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>0.08</v>
+      </c>
+      <c r="E20">
+        <v>0.0762</v>
+      </c>
+      <c r="F20">
+        <v>0.09449999999999999</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>126.2</v>
+      </c>
+      <c r="L20">
+        <v>0.378978978978979</v>
+      </c>
+      <c r="M20">
+        <v>4.48</v>
+      </c>
+      <c r="N20">
+        <v>0.003002479726559882</v>
+      </c>
+      <c r="O20">
+        <v>0.03549920760697306</v>
+      </c>
+      <c r="P20">
+        <v>4.48</v>
+      </c>
+      <c r="Q20">
+        <v>0.003002479726559882</v>
+      </c>
+      <c r="R20">
+        <v>0.03549920760697306</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>462.1</v>
+      </c>
+      <c r="V20">
+        <v>0.3096977414382414</v>
+      </c>
+      <c r="W20">
+        <v>0.1328700779111392</v>
+      </c>
+      <c r="X20">
+        <v>0.07847327792422987</v>
+      </c>
+      <c r="Y20">
+        <v>0.05439679998690933</v>
+      </c>
+      <c r="Z20">
+        <v>0.4407677035076109</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0.07432325576485892</v>
+      </c>
+      <c r="AC20">
+        <v>-0.07432325576485892</v>
+      </c>
+      <c r="AD20">
+        <v>303.9</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>303.9</v>
+      </c>
+      <c r="AG20">
+        <v>-158.2</v>
+      </c>
+      <c r="AH20">
+        <v>0.1692093541202672</v>
+      </c>
+      <c r="AI20">
+        <v>0.2228332600087989</v>
+      </c>
+      <c r="AJ20">
+        <v>-0.1185995951720519</v>
+      </c>
+      <c r="AK20">
+        <v>-0.1754463790617722</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>IDBI Bank Limited (NSEI:IDBI)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>-7.286214497334327E-05</v>
+      </c>
+      <c r="J21">
+        <v>-7.286214497334327E-05</v>
+      </c>
+      <c r="K21">
+        <v>807.9</v>
+      </c>
+      <c r="L21">
+        <v>0.4413548210871346</v>
+      </c>
+      <c r="M21">
+        <v>192.5</v>
+      </c>
+      <c r="N21">
+        <v>0.02003059217714328</v>
+      </c>
+      <c r="O21">
+        <v>0.23827206337418</v>
+      </c>
+      <c r="P21">
+        <v>192.5</v>
+      </c>
+      <c r="Q21">
+        <v>0.02003059217714328</v>
+      </c>
+      <c r="R21">
+        <v>0.23827206337418</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>1952.8</v>
+      </c>
+      <c r="V21">
+        <v>0.2031986514468851</v>
+      </c>
+      <c r="W21">
+        <v>0.140119324291512</v>
+      </c>
+      <c r="X21">
+        <v>0.07944789549042591</v>
+      </c>
+      <c r="Y21">
+        <v>0.06067142880108609</v>
+      </c>
+      <c r="Z21">
+        <v>0.2782224883032396</v>
+      </c>
+      <c r="AA21">
+        <v>-2.027188727759495E-05</v>
+      </c>
+      <c r="AB21">
+        <v>0.0743093165564947</v>
+      </c>
+      <c r="AC21">
+        <v>-0.0743295884437723</v>
+      </c>
+      <c r="AD21">
+        <v>2424</v>
+      </c>
+      <c r="AE21">
+        <v>1.266870781868524</v>
+      </c>
+      <c r="AF21">
+        <v>2425.266870781868</v>
+      </c>
+      <c r="AG21">
+        <v>472.4668707818685</v>
+      </c>
+      <c r="AH21">
+        <v>0.2015083208643512</v>
+      </c>
+      <c r="AI21">
+        <v>0.2703884040022169</v>
+      </c>
+      <c r="AJ21">
+        <v>0.04685885103135693</v>
+      </c>
+      <c r="AK21">
+        <v>0.06733398436668057</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <v>20200</v>
+      </c>
+      <c r="AP21">
+        <v>3937.223923182237</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>The Karur Vysya Bank Limited (NSEI:KARURVYSYA)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>0.208</v>
+      </c>
+      <c r="E22">
+        <v>0.526</v>
+      </c>
+      <c r="F22">
+        <v>0.173</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>214.8</v>
+      </c>
+      <c r="L22">
+        <v>0.3479669528592257</v>
+      </c>
+      <c r="M22">
+        <v>22.9</v>
+      </c>
+      <c r="N22">
+        <v>0.01121449559255632</v>
+      </c>
+      <c r="O22">
+        <v>0.1066108007448789</v>
+      </c>
+      <c r="P22">
+        <v>22.9</v>
+      </c>
+      <c r="Q22">
+        <v>0.01121449559255632</v>
+      </c>
+      <c r="R22">
+        <v>0.1066108007448789</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>678.8</v>
+      </c>
+      <c r="V22">
+        <v>0.3324191968658178</v>
+      </c>
+      <c r="W22">
+        <v>0.1947592710127845</v>
+      </c>
+      <c r="X22">
+        <v>0.07605492147154944</v>
+      </c>
+      <c r="Y22">
+        <v>0.118704349541235</v>
+      </c>
+      <c r="Z22">
+        <v>0.7475175587309275</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0.07436325774652192</v>
+      </c>
+      <c r="AC22">
+        <v>-0.07436325774652192</v>
+      </c>
+      <c r="AD22">
+        <v>169.2</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>169.2</v>
+      </c>
+      <c r="AG22">
+        <v>-509.6</v>
+      </c>
+      <c r="AH22">
+        <v>0.07651953690303907</v>
+      </c>
+      <c r="AI22">
+        <v>0.1150785553968578</v>
+      </c>
+      <c r="AJ22">
+        <v>-0.3325502479770295</v>
+      </c>
+      <c r="AK22">
+        <v>-0.6438408085912823</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Yes Bank Limited (NSEI:YESBANK)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>0.161</v>
+      </c>
+      <c r="F23">
+        <v>0.6</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>-0.003353884512828021</v>
+      </c>
+      <c r="J23">
+        <v>-0.002785142746391915</v>
+      </c>
+      <c r="K23">
+        <v>213.9</v>
+      </c>
+      <c r="L23">
+        <v>0.1408719704952582</v>
+      </c>
+      <c r="M23">
+        <v>-0</v>
+      </c>
+      <c r="N23">
+        <v>-0</v>
+      </c>
+      <c r="O23">
+        <v>-0</v>
+      </c>
+      <c r="P23">
+        <v>-0</v>
+      </c>
+      <c r="Q23">
+        <v>-0</v>
+      </c>
+      <c r="R23">
+        <v>-0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>3466.7</v>
+      </c>
+      <c r="V23">
+        <v>0.4831031647598211</v>
+      </c>
+      <c r="W23">
+        <v>0.04289839958284866</v>
+      </c>
+      <c r="X23">
+        <v>0.1014175287688724</v>
+      </c>
+      <c r="Y23">
+        <v>-0.05851912918602374</v>
+      </c>
+      <c r="Z23">
+        <v>0.1379703549658281</v>
+      </c>
+      <c r="AA23">
+        <v>-0.000384267133350194</v>
+      </c>
+      <c r="AB23">
+        <v>0.07414836770366771</v>
+      </c>
+      <c r="AC23">
+        <v>-0.07453263483701791</v>
+      </c>
+      <c r="AD23">
+        <v>9423.200000000001</v>
+      </c>
+      <c r="AE23">
+        <v>263.4626912213903</v>
+      </c>
+      <c r="AF23">
+        <v>9686.662691221391</v>
+      </c>
+      <c r="AG23">
+        <v>6219.962691221391</v>
+      </c>
+      <c r="AH23">
+        <v>0.5744478385995412</v>
+      </c>
+      <c r="AI23">
+        <v>0.6360225094020646</v>
+      </c>
+      <c r="AJ23">
+        <v>0.4643196809786257</v>
+      </c>
+      <c r="AK23">
+        <v>0.5287571976219982</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>197.9663865546219</v>
+      </c>
+      <c r="AP23">
+        <v>130.6714851096931</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Jana Small Finance Bank Limited (NSEI:JSFB)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0.001440580369985545</v>
+      </c>
+      <c r="J24">
+        <v>0.001440580369985545</v>
+      </c>
+      <c r="K24">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="L24">
+        <v>0.2966014418125644</v>
+      </c>
+      <c r="M24">
+        <v>-0</v>
+      </c>
+      <c r="N24">
+        <v>-0</v>
+      </c>
+      <c r="O24">
+        <v>-0</v>
+      </c>
+      <c r="P24">
+        <v>-0</v>
+      </c>
+      <c r="Q24">
+        <v>-0</v>
+      </c>
+      <c r="R24">
+        <v>-0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>224.6</v>
+      </c>
+      <c r="V24">
+        <v>0.4646255688870501</v>
+      </c>
+      <c r="W24">
+        <v>0.312251535959523</v>
+      </c>
+      <c r="X24">
+        <v>0.09196665242715672</v>
+      </c>
+      <c r="Y24">
+        <v>0.2202848835323662</v>
+      </c>
+      <c r="Z24">
+        <v>0.3093122433728847</v>
+      </c>
+      <c r="AA24">
+        <v>0.0004455891459991693</v>
+      </c>
+      <c r="AB24">
+        <v>0.07501258098873279</v>
+      </c>
+      <c r="AC24">
+        <v>-0.07456699184273362</v>
+      </c>
+      <c r="AD24">
+        <v>423.4</v>
+      </c>
+      <c r="AE24">
+        <v>0.9067946911160529</v>
+      </c>
+      <c r="AF24">
+        <v>424.306794691116</v>
+      </c>
+      <c r="AG24">
+        <v>199.706794691116</v>
+      </c>
+      <c r="AH24">
+        <v>0.4674491776119221</v>
+      </c>
+      <c r="AI24">
+        <v>0.4793848575517832</v>
+      </c>
+      <c r="AJ24">
+        <v>0.2923507660049239</v>
+      </c>
+      <c r="AK24">
+        <v>0.3023538838605109</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+      <c r="AN24">
+        <v>704.4925124792013</v>
+      </c>
+      <c r="AP24">
+        <v>332.2908397522729</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>The Jammu and Kashmir Bank Limited (NSEI:J&amp;KBANK)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>242</v>
+      </c>
+      <c r="L25">
+        <v>0.3467048710601719</v>
+      </c>
+      <c r="M25">
+        <v>28.3</v>
+      </c>
+      <c r="N25">
+        <v>0.02181453788637941</v>
+      </c>
+      <c r="O25">
+        <v>0.1169421487603306</v>
+      </c>
+      <c r="P25">
+        <v>28.3</v>
+      </c>
+      <c r="Q25">
+        <v>0.02181453788637941</v>
+      </c>
+      <c r="R25">
+        <v>0.1169421487603306</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>901.2</v>
+      </c>
+      <c r="V25">
+        <v>0.6946735527634318</v>
+      </c>
+      <c r="W25">
+        <v>0.1894769808957094</v>
+      </c>
+      <c r="X25">
+        <v>0.07970884548975668</v>
+      </c>
+      <c r="Y25">
+        <v>0.1097681354059527</v>
+      </c>
+      <c r="Z25">
+        <v>0.8369304556354916</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0.07467280164916236</v>
+      </c>
+      <c r="AC25">
+        <v>-0.07467280164916236</v>
+      </c>
+      <c r="AD25">
+        <v>344.3</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>344.3</v>
+      </c>
+      <c r="AG25">
+        <v>-556.9000000000001</v>
+      </c>
+      <c r="AH25">
+        <v>0.2097344054580897</v>
+      </c>
+      <c r="AI25">
+        <v>0.1781630012936611</v>
+      </c>
+      <c r="AJ25">
+        <v>-0.7521609940572666</v>
+      </c>
+      <c r="AK25">
+        <v>-0.5399980607000874</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tamilnad Mercantile Bank Limited (NSEI:TMB)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>0.179</v>
+      </c>
+      <c r="E26">
+        <v>0.266</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>134.6</v>
+      </c>
+      <c r="L26">
+        <v>0.3924198250728863</v>
+      </c>
+      <c r="M26">
+        <v>0.019</v>
+      </c>
+      <c r="N26">
+        <v>2.272183688112892E-05</v>
+      </c>
+      <c r="O26">
+        <v>0.0001411589895988113</v>
+      </c>
+      <c r="P26">
+        <v>0.019</v>
+      </c>
+      <c r="Q26">
+        <v>2.272183688112892E-05</v>
+      </c>
+      <c r="R26">
+        <v>0.0001411589895988113</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>375.6</v>
+      </c>
+      <c r="V26">
+        <v>0.4491748385553695</v>
+      </c>
+      <c r="W26">
+        <v>0.1514571846517385</v>
+      </c>
+      <c r="X26">
+        <v>0.07982553921515614</v>
+      </c>
+      <c r="Y26">
+        <v>0.07163164543658235</v>
+      </c>
+      <c r="Z26">
+        <v>0.6023884791008077</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0.07467757966444771</v>
+      </c>
+      <c r="AC26">
+        <v>-0.07467757966444771</v>
+      </c>
+      <c r="AD26">
+        <v>226.8</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>226.8</v>
+      </c>
+      <c r="AG26">
+        <v>-148.8</v>
+      </c>
+      <c r="AH26">
+        <v>0.2133584195672625</v>
+      </c>
+      <c r="AI26">
+        <v>0.1839416058394161</v>
+      </c>
+      <c r="AJ26">
+        <v>-0.2164678498690719</v>
+      </c>
+      <c r="AK26">
+        <v>-0.1735479356193142</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Central Bank of India (NSEI:CENTRALBK)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>407.8</v>
+      </c>
+      <c r="L27">
+        <v>0.2373275912238841</v>
+      </c>
+      <c r="M27">
+        <v>-0</v>
+      </c>
+      <c r="N27">
+        <v>-0</v>
+      </c>
+      <c r="O27">
+        <v>-0</v>
+      </c>
+      <c r="P27">
+        <v>-0</v>
+      </c>
+      <c r="Q27">
+        <v>-0</v>
+      </c>
+      <c r="R27">
+        <v>-0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>3870.2</v>
+      </c>
+      <c r="V27">
+        <v>0.7156964272505362</v>
+      </c>
+      <c r="W27">
+        <v>0.1116954259107094</v>
+      </c>
+      <c r="X27">
+        <v>0.08029311395973172</v>
+      </c>
+      <c r="Y27">
+        <v>0.03140231195097767</v>
+      </c>
+      <c r="Z27">
+        <v>0.5321906755907121</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0.0746962928315785</v>
+      </c>
+      <c r="AC27">
+        <v>-0.0746962928315785</v>
+      </c>
+      <c r="AD27">
+        <v>1593</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>1593</v>
+      </c>
+      <c r="AG27">
+        <v>-2277.2</v>
+      </c>
+      <c r="AH27">
+        <v>0.2275519241207896</v>
+      </c>
+      <c r="AI27">
+        <v>0.2844185755860665</v>
+      </c>
+      <c r="AJ27">
+        <v>-0.727446971633018</v>
+      </c>
+      <c r="AK27">
+        <v>-1.315768186283007</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Indian Overseas Bank (NSEI:IOB)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>353.6</v>
+      </c>
+      <c r="L28">
+        <v>0.2275125466477931</v>
+      </c>
+      <c r="M28">
+        <v>-0</v>
+      </c>
+      <c r="N28">
+        <v>-0</v>
+      </c>
+      <c r="O28">
+        <v>-0</v>
+      </c>
+      <c r="P28">
+        <v>-0</v>
+      </c>
+      <c r="Q28">
+        <v>-0</v>
+      </c>
+      <c r="R28">
+        <v>-0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>2744.7</v>
+      </c>
+      <c r="V28">
+        <v>0.2400787229389897</v>
+      </c>
+      <c r="W28">
+        <v>0.1130977130977131</v>
+      </c>
+      <c r="X28">
+        <v>0.0804075408651088</v>
+      </c>
+      <c r="Y28">
+        <v>0.0326901722326043</v>
+      </c>
+      <c r="Z28">
+        <v>0.3544679104137207</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0.07470076999916636</v>
+      </c>
+      <c r="AC28">
+        <v>-0.07470076999916636</v>
+      </c>
+      <c r="AD28">
+        <v>3433.2</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>3433.2</v>
+      </c>
+      <c r="AG28">
+        <v>688.5</v>
+      </c>
+      <c r="AH28">
+        <v>0.2309477522081032</v>
+      </c>
+      <c r="AI28">
+        <v>0.5057972509097338</v>
+      </c>
+      <c r="AJ28">
+        <v>0.05680224403927069</v>
+      </c>
+      <c r="AK28">
+        <v>0.1702943358891912</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>The South Indian Bank Limited (NSEI:SOUTHBANK)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>0.184</v>
+      </c>
+      <c r="E29">
+        <v>0.312</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>144.6</v>
+      </c>
+      <c r="L29">
+        <v>0.2524882137244631</v>
+      </c>
+      <c r="M29">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="N29">
+        <v>0.01224996731598902</v>
+      </c>
+      <c r="O29">
+        <v>0.06479944674965421</v>
+      </c>
+      <c r="P29">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="Q29">
+        <v>0.01224996731598902</v>
+      </c>
+      <c r="R29">
+        <v>0.06479944674965421</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>1306.3</v>
+      </c>
+      <c r="V29">
+        <v>1.70780494182246</v>
+      </c>
+      <c r="W29">
+        <v>0.1694398875087884</v>
+      </c>
+      <c r="X29">
+        <v>0.0825456044129131</v>
+      </c>
+      <c r="Y29">
+        <v>0.08689428309587528</v>
+      </c>
+      <c r="Z29">
+        <v>0.983007209062822</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0.07477773580705586</v>
+      </c>
+      <c r="AC29">
+        <v>-0.07477773580705586</v>
+      </c>
+      <c r="AD29">
+        <v>311.4</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>311.4</v>
+      </c>
+      <c r="AG29">
+        <v>-994.9</v>
+      </c>
+      <c r="AH29">
+        <v>0.2893245377682802</v>
+      </c>
+      <c r="AI29">
+        <v>0.2172608665317798</v>
+      </c>
+      <c r="AJ29">
+        <v>4.325652173913044</v>
+      </c>
+      <c r="AK29">
+        <v>-7.833858267716528</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ICICI Bank Limited (NSEI:ICICIBANK)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D30">
+        <v>0.148</v>
+      </c>
+      <c r="E30">
+        <v>0.479</v>
+      </c>
+      <c r="F30">
+        <v>0.109</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0.0001034623517351131</v>
+      </c>
+      <c r="J30">
+        <v>0.0001001988248201149</v>
+      </c>
+      <c r="K30">
+        <v>5653.7</v>
+      </c>
+      <c r="L30">
+        <v>0.2890927405952947</v>
+      </c>
+      <c r="M30">
+        <v>840.4</v>
+      </c>
+      <c r="N30">
+        <v>0.007949510581059657</v>
+      </c>
+      <c r="O30">
+        <v>0.1486460194209102</v>
+      </c>
+      <c r="P30">
+        <v>840.4</v>
+      </c>
+      <c r="Q30">
+        <v>0.007949510581059657</v>
+      </c>
+      <c r="R30">
+        <v>0.1486460194209102</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>19620.4</v>
+      </c>
+      <c r="V30">
+        <v>0.1855932620235875</v>
+      </c>
+      <c r="W30">
+        <v>0.2025689716947331</v>
+      </c>
+      <c r="X30">
+        <v>0.07937222486762639</v>
+      </c>
+      <c r="Y30">
+        <v>0.1231967468271067</v>
+      </c>
+      <c r="Z30">
+        <v>0.5549262069203064</v>
+      </c>
+      <c r="AA30">
+        <v>5.560295379529862E-05</v>
+      </c>
+      <c r="AB30">
+        <v>0.07493749585382029</v>
+      </c>
+      <c r="AC30">
+        <v>-0.07488189290002499</v>
+      </c>
+      <c r="AD30">
+        <v>26229.9</v>
+      </c>
+      <c r="AE30">
+        <v>49.38308912910957</v>
+      </c>
+      <c r="AF30">
+        <v>26279.28308912911</v>
+      </c>
+      <c r="AG30">
+        <v>6658.883089129111</v>
+      </c>
+      <c r="AH30">
+        <v>0.1990907823762572</v>
+      </c>
+      <c r="AI30">
+        <v>0.4268211088398172</v>
+      </c>
+      <c r="AJ30">
+        <v>0.0592553406924473</v>
+      </c>
+      <c r="AK30">
+        <v>0.1587361386216598</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>0</v>
+      </c>
+      <c r="AN30">
+        <v>2204.193277310924</v>
+      </c>
+      <c r="AP30">
+        <v>559.5700074898413</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Union Bank of India (NSEI:UNIONBANK)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>0.7609999999999999</v>
+      </c>
+      <c r="F31">
+        <v>0.226</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>1831.7</v>
+      </c>
+      <c r="L31">
+        <v>0.3069459572685379</v>
+      </c>
+      <c r="M31">
+        <v>328</v>
+      </c>
+      <c r="N31">
+        <v>0.03054913940838984</v>
+      </c>
+      <c r="O31">
+        <v>0.1790686247747994</v>
+      </c>
+      <c r="P31">
+        <v>328</v>
+      </c>
+      <c r="Q31">
+        <v>0.03054913940838984</v>
+      </c>
+      <c r="R31">
+        <v>0.1790686247747994</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>12510</v>
+      </c>
+      <c r="V31">
+        <v>1.1651516280456</v>
+      </c>
+      <c r="W31">
+        <v>0.168456968381555</v>
+      </c>
+      <c r="X31">
+        <v>0.08016856546480741</v>
+      </c>
+      <c r="Y31">
+        <v>0.08828840291674758</v>
+      </c>
+      <c r="Z31">
+        <v>1.494789840188368</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0.07500472453797216</v>
+      </c>
+      <c r="AC31">
+        <v>-0.07500472453797216</v>
+      </c>
+      <c r="AD31">
+        <v>3096.1</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>3096.1</v>
+      </c>
+      <c r="AG31">
+        <v>-9413.9</v>
+      </c>
+      <c r="AH31">
+        <v>0.2238214691062612</v>
+      </c>
+      <c r="AI31">
+        <v>0.194150587261474</v>
+      </c>
+      <c r="AJ31">
+        <v>-7.116108549399049</v>
+      </c>
+      <c r="AK31">
+        <v>-2.739067182635515</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Indian Bank (NSEI:INDIANB)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>0.399</v>
+      </c>
+      <c r="E32">
+        <v>0.645</v>
+      </c>
+      <c r="F32">
+        <v>0.19</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>1178.2</v>
+      </c>
+      <c r="L32">
+        <v>0.3466415605048692</v>
+      </c>
+      <c r="M32">
+        <v>280.5</v>
+      </c>
+      <c r="N32">
+        <v>0.03362906126363745</v>
+      </c>
+      <c r="O32">
+        <v>0.2380750297063317</v>
+      </c>
+      <c r="P32">
+        <v>280.5</v>
+      </c>
+      <c r="Q32">
+        <v>0.03362906126363745</v>
+      </c>
+      <c r="R32">
+        <v>0.2380750297063317</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>784.5</v>
+      </c>
+      <c r="V32">
+        <v>0.09405347080685769</v>
+      </c>
+      <c r="W32">
+        <v>0.1833546017616484</v>
+      </c>
+      <c r="X32">
+        <v>0.08396820144040923</v>
+      </c>
+      <c r="Y32">
+        <v>0.09938640032123913</v>
+      </c>
+      <c r="Z32">
+        <v>0.4319079992375627</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0.07527567326179603</v>
+      </c>
+      <c r="AC32">
+        <v>-0.07527567326179603</v>
+      </c>
+      <c r="AD32">
+        <v>3988.5</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>3988.5</v>
+      </c>
+      <c r="AG32">
+        <v>3204</v>
+      </c>
+      <c r="AH32">
+        <v>0.3234924368384768</v>
+      </c>
+      <c r="AI32">
+        <v>0.3352751298734049</v>
+      </c>
+      <c r="AJ32">
+        <v>0.2775227371156345</v>
+      </c>
+      <c r="AK32">
+        <v>0.2883447177299603</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>The Karnataka Bank Limited (NSEI:KTKBANK)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>0.141</v>
+      </c>
+      <c r="E33">
+        <v>0.227</v>
+      </c>
+      <c r="F33">
+        <v>0.11</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>-0.002585367742546018</v>
+      </c>
+      <c r="J33">
+        <v>-0.002091797537150869</v>
+      </c>
+      <c r="K33">
+        <v>160.2</v>
+      </c>
+      <c r="L33">
+        <v>0.3127073980089791</v>
+      </c>
+      <c r="M33">
+        <v>24.8</v>
+      </c>
+      <c r="N33">
+        <v>0.02617966853161617</v>
+      </c>
+      <c r="O33">
+        <v>0.1548064918851436</v>
+      </c>
+      <c r="P33">
+        <v>24.8</v>
+      </c>
+      <c r="Q33">
+        <v>0.02617966853161617</v>
+      </c>
+      <c r="R33">
+        <v>0.1548064918851436</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>935.5</v>
+      </c>
+      <c r="V33">
+        <v>0.9875435448115698</v>
+      </c>
+      <c r="W33">
+        <v>0.1519347496206373</v>
+      </c>
+      <c r="X33">
+        <v>0.08069083471309095</v>
+      </c>
+      <c r="Y33">
+        <v>0.07124391490754635</v>
+      </c>
+      <c r="Z33">
+        <v>0.5861673971762323</v>
+      </c>
+      <c r="AA33">
+        <v>-0.001226143517771378</v>
+      </c>
+      <c r="AB33">
+        <v>0.07429303796865838</v>
+      </c>
+      <c r="AC33">
+        <v>-0.07551918148642976</v>
+      </c>
+      <c r="AD33">
+        <v>290.3</v>
+      </c>
+      <c r="AE33">
+        <v>7.582419472531624</v>
+      </c>
+      <c r="AF33">
+        <v>297.8824194725316</v>
+      </c>
+      <c r="AG33">
+        <v>-637.6175805274684</v>
+      </c>
+      <c r="AH33">
+        <v>0.2392279354527964</v>
+      </c>
+      <c r="AI33">
+        <v>0.1777678252220958</v>
+      </c>
+      <c r="AJ33">
+        <v>-2.05894019303225</v>
+      </c>
+      <c r="AK33">
+        <v>-0.8614330248235929</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>0</v>
+      </c>
+      <c r="AN33">
+        <v>1511.979166666667</v>
+      </c>
+      <c r="AP33">
+        <v>-3320.924898580564</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>State Bank of India (NSEI:SBIN)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>0.187</v>
+      </c>
+      <c r="E34">
+        <v>0.423</v>
+      </c>
+      <c r="F34">
+        <v>0.0732</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0.0002006638300458489</v>
+      </c>
+      <c r="J34">
+        <v>0.0001501056046164344</v>
+      </c>
+      <c r="K34">
+        <v>8540.700000000001</v>
+      </c>
+      <c r="L34">
+        <v>0.2129473335145149</v>
+      </c>
+      <c r="M34">
+        <v>1459.3</v>
+      </c>
+      <c r="N34">
+        <v>0.01760298767079168</v>
+      </c>
+      <c r="O34">
+        <v>0.1708642148770007</v>
+      </c>
+      <c r="P34">
+        <v>1459.3</v>
+      </c>
+      <c r="Q34">
+        <v>0.01760298767079168</v>
+      </c>
+      <c r="R34">
+        <v>0.1708642148770007</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>42368.3</v>
+      </c>
+      <c r="V34">
+        <v>0.5110728859949314</v>
+      </c>
+      <c r="W34">
+        <v>0.1800285829918551</v>
+      </c>
+      <c r="X34">
+        <v>0.09189287387580654</v>
+      </c>
+      <c r="Y34">
+        <v>0.08813570911604858</v>
+      </c>
+      <c r="Z34">
+        <v>0.5742953687798537</v>
+      </c>
+      <c r="AA34">
+        <v>8.62049535591181E-05</v>
+      </c>
+      <c r="AB34">
+        <v>0.07566416264794311</v>
+      </c>
+      <c r="AC34">
+        <v>-0.075577957694384</v>
+      </c>
+      <c r="AD34">
+        <v>72409.2</v>
+      </c>
+      <c r="AE34">
+        <v>51.75977850984066</v>
+      </c>
+      <c r="AF34">
+        <v>72460.95977850984</v>
+      </c>
+      <c r="AG34">
+        <v>30092.65977850984</v>
+      </c>
+      <c r="AH34">
+        <v>0.4664018129171204</v>
+      </c>
+      <c r="AI34">
+        <v>0.5580399265278486</v>
+      </c>
+      <c r="AJ34">
+        <v>0.2663223736111363</v>
+      </c>
+      <c r="AK34">
+        <v>0.3439917514971363</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>0</v>
+      </c>
+      <c r="AN34">
+        <v>3935.282608695652</v>
+      </c>
+      <c r="AP34">
+        <v>1635.470640136405</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Axis Bank Limited (BSE:532215)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>0.2</v>
+      </c>
+      <c r="E35">
+        <v>0.429</v>
+      </c>
+      <c r="F35">
+        <v>0.109</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>-0.0003388586606527946</v>
+      </c>
+      <c r="J35">
+        <v>-0.0003388586606527946</v>
+      </c>
+      <c r="K35">
+        <v>3333.4</v>
+      </c>
+      <c r="L35">
+        <v>0.4183116443083565</v>
+      </c>
+      <c r="M35">
+        <v>36.9</v>
+      </c>
+      <c r="N35">
+        <v>0.0009579737686532289</v>
+      </c>
+      <c r="O35">
+        <v>0.01106977860442791</v>
+      </c>
+      <c r="P35">
+        <v>36.9</v>
+      </c>
+      <c r="Q35">
+        <v>0.0009579737686532289</v>
+      </c>
+      <c r="R35">
+        <v>0.01106977860442791</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>10648.9</v>
+      </c>
+      <c r="V35">
+        <v>0.2764598066398745</v>
+      </c>
+      <c r="W35">
+        <v>0.1944977681827464</v>
+      </c>
+      <c r="X35">
+        <v>0.08876472007569697</v>
+      </c>
+      <c r="Y35">
+        <v>0.1057330481070495</v>
+      </c>
+      <c r="Z35">
+        <v>0.2167592794624918</v>
+      </c>
+      <c r="AA35">
+        <v>-7.345075912272477E-05</v>
+      </c>
+      <c r="AB35">
+        <v>0.07553220295578716</v>
+      </c>
+      <c r="AC35">
+        <v>-0.07560565371490989</v>
+      </c>
+      <c r="AD35">
+        <v>26881.2</v>
+      </c>
+      <c r="AE35">
+        <v>767.5013150457197</v>
+      </c>
+      <c r="AF35">
+        <v>27648.70131504572</v>
+      </c>
+      <c r="AG35">
+        <v>16999.80131504572</v>
+      </c>
+      <c r="AH35">
+        <v>0.4178592324863675</v>
+      </c>
+      <c r="AI35">
+        <v>0.5724866460892999</v>
+      </c>
+      <c r="AJ35">
+        <v>0.30620010072982</v>
+      </c>
+      <c r="AK35">
+        <v>0.4515591116725373</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>0</v>
+      </c>
+      <c r="AN35">
+        <v>178.2572944297082</v>
+      </c>
+      <c r="AP35">
+        <v>112.7307779512315</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>HDFC Bank Limited (NSEI:HDFCBANK)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D9">
+      <c r="D36">
         <v>0.329</v>
       </c>
-      <c r="E9">
+      <c r="E36">
         <v>0.236</v>
       </c>
-      <c r="F9">
+      <c r="F36">
         <v>0.142</v>
       </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
         <v>-0.002058640350629</v>
       </c>
-      <c r="J9">
+      <c r="J36">
         <v>-0.001718636341561297</v>
       </c>
-      <c r="K9">
+      <c r="K36">
         <v>8257.200000000001</v>
       </c>
-      <c r="L9">
+      <c r="L36">
         <v>0.2505590940400728</v>
       </c>
-      <c r="M9">
+      <c r="M36">
         <v>1769.6</v>
       </c>
-      <c r="N9">
+      <c r="N36">
         <v>0.01116885444766051</v>
       </c>
-      <c r="O9">
+      <c r="O36">
         <v>0.2143099355713801</v>
       </c>
-      <c r="P9">
+      <c r="P36">
         <v>1769.6</v>
       </c>
-      <c r="Q9">
+      <c r="Q36">
         <v>0.01116885444766051</v>
       </c>
-      <c r="R9">
+      <c r="R36">
         <v>0.2143099355713801</v>
       </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
         <v>31794.9</v>
       </c>
-      <c r="V9">
+      <c r="V36">
         <v>0.2006739434210676</v>
       </c>
-      <c r="W9">
+      <c r="W36">
         <v>0.1054524370838261</v>
       </c>
-      <c r="X9">
-        <v>0.08465080060579008</v>
-      </c>
-      <c r="Y9">
-        <v>0.020801636478036</v>
-      </c>
-      <c r="Z9">
+      <c r="X36">
+        <v>0.08464352394531996</v>
+      </c>
+      <c r="Y36">
+        <v>0.02080891313850612</v>
+      </c>
+      <c r="Z36">
         <v>0.2056118500560884</v>
       </c>
-      <c r="AA9">
+      <c r="AA36">
         <v>-0.0003533719977620457</v>
       </c>
-      <c r="AB9">
-        <v>0.0753215223013535</v>
-      </c>
-      <c r="AC9">
-        <v>-0.07567489429911554</v>
-      </c>
-      <c r="AD9">
+      <c r="AB36">
+        <v>0.07531670943055904</v>
+      </c>
+      <c r="AC36">
+        <v>-0.07567008142832109</v>
+      </c>
+      <c r="AD36">
         <v>79496.2</v>
       </c>
-      <c r="AE9">
+      <c r="AE36">
         <v>1612.213493095069</v>
       </c>
-      <c r="AF9">
+      <c r="AF36">
         <v>81108.41349309507</v>
       </c>
-      <c r="AG9">
+      <c r="AG36">
         <v>49313.51349309507</v>
       </c>
-      <c r="AH9">
+      <c r="AH36">
         <v>0.3385879670735233</v>
       </c>
-      <c r="AI9">
+      <c r="AI36">
         <v>0.5774619914987716</v>
       </c>
-      <c r="AJ9">
+      <c r="AJ36">
         <v>0.2373647994928103</v>
       </c>
-      <c r="AK9">
+      <c r="AK36">
         <v>0.4538256072472847</v>
       </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>0</v>
-      </c>
-      <c r="AN9">
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>0</v>
+      </c>
+      <c r="AN36">
         <v>312.2395915161037</v>
       </c>
-      <c r="AP9">
+      <c r="AP36">
         <v>193.6901551182053</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>DCB Bank Limited (NSEI:DCBBANK)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D37">
+        <v>0.113</v>
+      </c>
+      <c r="E37">
+        <v>0.099</v>
+      </c>
+      <c r="F37">
+        <v>-0.005</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>-0.02105902982071792</v>
+      </c>
+      <c r="J37">
+        <v>-0.01562741120029232</v>
+      </c>
+      <c r="K37">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="L37">
+        <v>0.2316615489593995</v>
+      </c>
+      <c r="M37">
+        <v>4.67</v>
+      </c>
+      <c r="N37">
+        <v>0.01052275799909869</v>
+      </c>
+      <c r="O37">
+        <v>0.06877761413843887</v>
+      </c>
+      <c r="P37">
+        <v>4.67</v>
+      </c>
+      <c r="Q37">
+        <v>0.01052275799909869</v>
+      </c>
+      <c r="R37">
+        <v>0.06877761413843887</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>373</v>
+      </c>
+      <c r="V37">
+        <v>0.8404686795853988</v>
+      </c>
+      <c r="W37">
+        <v>0.1179228898923237</v>
+      </c>
+      <c r="X37">
+        <v>0.114474465698558</v>
+      </c>
+      <c r="Y37">
+        <v>0.003448424193765759</v>
+      </c>
+      <c r="Z37">
+        <v>0.3081817983183138</v>
+      </c>
+      <c r="AA37">
+        <v>-0.004816083686765844</v>
+      </c>
+      <c r="AB37">
+        <v>0.07410846511724981</v>
+      </c>
+      <c r="AC37">
+        <v>-0.07892454880401564</v>
+      </c>
+      <c r="AD37">
+        <v>814</v>
+      </c>
+      <c r="AE37">
+        <v>74.56200820226212</v>
+      </c>
+      <c r="AF37">
+        <v>888.5620082022622</v>
+      </c>
+      <c r="AG37">
+        <v>515.5620082022622</v>
+      </c>
+      <c r="AH37">
+        <v>0.6669073440492248</v>
+      </c>
+      <c r="AI37">
+        <v>0.5818006363218496</v>
+      </c>
+      <c r="AJ37">
+        <v>0.5374009016350023</v>
+      </c>
+      <c r="AK37">
+        <v>0.4466594278756854</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
+        <v>0</v>
+      </c>
+      <c r="AN37">
+        <v>93.13501144164759</v>
+      </c>
+      <c r="AP37">
+        <v>58.98878812382862</v>
       </c>
     </row>
   </sheetData>
